--- a/ontology/Ontology.xlsx
+++ b/ontology/Ontology.xlsx
@@ -1473,7 +1473,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="140">
+  <cellXfs count="141">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1892,6 +1892,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3712,7 +3715,7 @@
       <c r="D93" s="109"/>
       <c r="E93" s="86"/>
       <c r="F93" s="91"/>
-      <c r="G93" s="139" t="inlineStr">
+      <c r="G93" s="140" t="inlineStr">
         <is>
           <t xml:space="preserve">Equal =</t>
         </is>
@@ -3728,7 +3731,7 @@
       <c r="D94" s="109"/>
       <c r="E94" s="86"/>
       <c r="F94" s="91"/>
-      <c r="G94" s="139" t="inlineStr">
+      <c r="G94" s="140" t="inlineStr">
         <is>
           <t xml:space="preserve">GreaterEqual ≧</t>
         </is>
@@ -3744,7 +3747,7 @@
       <c r="D95" s="109"/>
       <c r="E95" s="86"/>
       <c r="F95" s="91"/>
-      <c r="G95" s="139" t="inlineStr">
+      <c r="G95" s="140" t="inlineStr">
         <is>
           <t xml:space="preserve">GreaterThan &gt;</t>
         </is>
@@ -3760,7 +3763,7 @@
       <c r="D96" s="109"/>
       <c r="E96" s="86"/>
       <c r="F96" s="91"/>
-      <c r="G96" s="139" t="inlineStr">
+      <c r="G96" s="140" t="inlineStr">
         <is>
           <t xml:space="preserve">Times ×</t>
         </is>
@@ -3776,7 +3779,7 @@
       <c r="D97" s="109"/>
       <c r="E97" s="86"/>
       <c r="F97" s="91"/>
-      <c r="G97" s="139" t="inlineStr">
+      <c r="G97" s="140" t="inlineStr">
         <is>
           <t xml:space="preserve">Plus +</t>
         </is>
@@ -3792,7 +3795,7 @@
       <c r="D98" s="109"/>
       <c r="E98" s="86"/>
       <c r="F98" s="91"/>
-      <c r="G98" s="139" t="inlineStr">
+      <c r="G98" s="140" t="inlineStr">
         <is>
           <t xml:space="preserve">Divide ÷</t>
         </is>
@@ -3808,7 +3811,7 @@
       <c r="D99" s="109"/>
       <c r="E99" s="86"/>
       <c r="F99" s="91"/>
-      <c r="G99" s="139" t="inlineStr">
+      <c r="G99" s="140" t="inlineStr">
         <is>
           <t xml:space="preserve">SubsetOf ⊆</t>
         </is>

--- a/ontology/Ontology.xlsx
+++ b/ontology/Ontology.xlsx
@@ -1894,7 +1894,7 @@
     <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>

--- a/ontology/Ontology.xlsx
+++ b/ontology/Ontology.xlsx
@@ -1473,7 +1473,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="141">
+  <cellXfs count="143">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1896,6 +1896,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf applyFill="1" numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3720,8 +3726,16 @@
           <t xml:space="preserve">Equal =</t>
         </is>
       </c>
-      <c r="H93" s="27"/>
-      <c r="I93" s="6"/>
+      <c r="H93" s="141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">| builtInFunction</t>
+        </is>
+      </c>
+      <c r="I93" s="142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">equal</t>
+        </is>
+      </c>
       <c r="J93" s="6"/>
     </row>
     <row r="94" spans="1:11" ht="34.799999999999997" customHeight="1">
@@ -3736,8 +3750,16 @@
           <t xml:space="preserve">GreaterEqual ≧</t>
         </is>
       </c>
-      <c r="H94" s="27"/>
-      <c r="I94" s="6"/>
+      <c r="H94" s="141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">| builtInFunction</t>
+        </is>
+      </c>
+      <c r="I94" s="142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">greaterEqual</t>
+        </is>
+      </c>
       <c r="J94" s="6"/>
     </row>
     <row r="95" spans="1:11" ht="34.799999999999997" customHeight="1">
@@ -3752,8 +3774,16 @@
           <t xml:space="preserve">GreaterThan &gt;</t>
         </is>
       </c>
-      <c r="H95" s="27"/>
-      <c r="I95" s="6"/>
+      <c r="H95" s="141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">| builtInFunction</t>
+        </is>
+      </c>
+      <c r="I95" s="142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">greaterThan</t>
+        </is>
+      </c>
       <c r="J95" s="6"/>
     </row>
     <row r="96" spans="1:11" ht="34.799999999999997" customHeight="1">
@@ -3768,8 +3798,16 @@
           <t xml:space="preserve">Times ×</t>
         </is>
       </c>
-      <c r="H96" s="27"/>
-      <c r="I96" s="6"/>
+      <c r="H96" s="141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">| builtInFunction</t>
+        </is>
+      </c>
+      <c r="I96" s="142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">times</t>
+        </is>
+      </c>
       <c r="J96" s="6"/>
     </row>
     <row r="97" spans="1:11" ht="34.799999999999997" customHeight="1">
@@ -3784,8 +3822,16 @@
           <t xml:space="preserve">Plus +</t>
         </is>
       </c>
-      <c r="H97" s="27"/>
-      <c r="I97" s="6"/>
+      <c r="H97" s="141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">| builtInFunction</t>
+        </is>
+      </c>
+      <c r="I97" s="142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">plus</t>
+        </is>
+      </c>
       <c r="J97" s="6"/>
     </row>
     <row r="98" spans="1:11" ht="34.799999999999997" customHeight="1">
@@ -3800,8 +3846,16 @@
           <t xml:space="preserve">Divide ÷</t>
         </is>
       </c>
-      <c r="H98" s="27"/>
-      <c r="I98" s="6"/>
+      <c r="H98" s="141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">| builtInFunction</t>
+        </is>
+      </c>
+      <c r="I98" s="142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">divide</t>
+        </is>
+      </c>
       <c r="J98" s="6"/>
     </row>
     <row r="99" spans="1:11" ht="34.799999999999997" customHeight="1">
@@ -3816,8 +3870,16 @@
           <t xml:space="preserve">SubsetOf ⊆</t>
         </is>
       </c>
-      <c r="H99" s="27"/>
-      <c r="I99" s="6"/>
+      <c r="H99" s="141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">| builtInFunction</t>
+        </is>
+      </c>
+      <c r="I99" s="142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">subsetOf</t>
+        </is>
+      </c>
       <c r="J99" s="6"/>
     </row>
     <row r="100" spans="1:11" ht="34.799999999999997" customHeight="1">

--- a/ontology/Ontology.xlsx
+++ b/ontology/Ontology.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\home\doc\PLR\dist\schemata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{761B63B3-A233-4B74-8CCE-FD603836C039}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DB8C890-6679-473C-A671-711CF3B3AEAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="15576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -782,10 +782,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>refersTo ja:参照;refers to</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>agent</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1055,6 +1051,10 @@
   </si>
   <si>
     <t>\最初に成功した節以外の節を無視する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>retrieve</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1525,109 +1525,109 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1873,22 +1873,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="69" customHeight="1">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="83" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="63" t="s">
+      <c r="B1" s="83"/>
+      <c r="C1" s="83"/>
+      <c r="D1" s="54" t="s">
         <v>164</v>
       </c>
-      <c r="E1" s="63"/>
-      <c r="F1" s="63"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
       <c r="I1" s="5"/>
     </row>
     <row r="2" spans="1:13" ht="34.799999999999997">
-      <c r="A2" s="64" t="s">
+      <c r="A2" s="57" t="s">
         <v>19</v>
       </c>
       <c r="B2" s="10" t="s">
@@ -1905,7 +1905,7 @@
       <c r="I2" s="5"/>
     </row>
     <row r="3" spans="1:13" ht="34.799999999999997">
-      <c r="A3" s="65"/>
+      <c r="A3" s="58"/>
       <c r="B3" s="10" t="s">
         <v>16</v>
       </c>
@@ -1920,7 +1920,7 @@
       <c r="I3" s="5"/>
     </row>
     <row r="4" spans="1:13" ht="34.799999999999997">
-      <c r="A4" s="65"/>
+      <c r="A4" s="58"/>
       <c r="B4" s="10" t="s">
         <v>9</v>
       </c>
@@ -1935,7 +1935,7 @@
       <c r="I4" s="5"/>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="65"/>
+      <c r="A5" s="58"/>
       <c r="B5" s="2" t="s">
         <v>31</v>
       </c>
@@ -1948,8 +1948,8 @@
       <c r="I5" s="5"/>
     </row>
     <row r="6" spans="1:13">
-      <c r="A6" s="65"/>
-      <c r="B6" s="67" t="s">
+      <c r="A6" s="58"/>
+      <c r="B6" s="82" t="s">
         <v>36</v>
       </c>
       <c r="C6" s="13" t="s">
@@ -1963,18 +1963,18 @@
       <c r="I6" s="5"/>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1">
-      <c r="A7" s="65"/>
-      <c r="B7" s="67"/>
-      <c r="C7" s="68" t="s">
+      <c r="A7" s="58"/>
+      <c r="B7" s="82"/>
+      <c r="C7" s="85" t="s">
         <v>135</v>
       </c>
-      <c r="D7" s="70" t="s">
+      <c r="D7" s="62" t="s">
         <v>136</v>
       </c>
-      <c r="E7" s="73" t="s">
+      <c r="E7" s="59" t="s">
         <v>153</v>
       </c>
-      <c r="F7" s="70" t="s">
+      <c r="F7" s="62" t="s">
         <v>120</v>
       </c>
       <c r="G7" s="14" t="s">
@@ -1986,16 +1986,16 @@
       <c r="K7" s="5"/>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="65"/>
-      <c r="B8" s="67"/>
-      <c r="C8" s="69"/>
-      <c r="D8" s="71"/>
-      <c r="E8" s="74"/>
-      <c r="F8" s="71"/>
-      <c r="G8" s="57" t="s">
+      <c r="A8" s="58"/>
+      <c r="B8" s="82"/>
+      <c r="C8" s="86"/>
+      <c r="D8" s="63"/>
+      <c r="E8" s="60"/>
+      <c r="F8" s="63"/>
+      <c r="G8" s="68" t="s">
         <v>33</v>
       </c>
-      <c r="H8" s="70" t="s">
+      <c r="H8" s="62" t="s">
         <v>34</v>
       </c>
       <c r="I8" s="10" t="s">
@@ -2004,58 +2004,58 @@
       <c r="J8" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="K8" s="78" t="s">
+      <c r="K8" s="70" t="s">
         <v>89</v>
       </c>
       <c r="L8" s="4"/>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" s="65"/>
-      <c r="B9" s="67"/>
-      <c r="C9" s="69"/>
-      <c r="D9" s="71"/>
-      <c r="E9" s="74"/>
-      <c r="F9" s="71"/>
-      <c r="G9" s="58"/>
-      <c r="H9" s="71"/>
+      <c r="A9" s="58"/>
+      <c r="B9" s="82"/>
+      <c r="C9" s="86"/>
+      <c r="D9" s="63"/>
+      <c r="E9" s="60"/>
+      <c r="F9" s="63"/>
+      <c r="G9" s="69"/>
+      <c r="H9" s="63"/>
       <c r="I9" s="10" t="s">
         <v>87</v>
       </c>
       <c r="J9" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="K9" s="78"/>
+      <c r="K9" s="70"/>
       <c r="L9" s="4"/>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="65"/>
-      <c r="B10" s="67"/>
-      <c r="C10" s="69"/>
-      <c r="D10" s="71"/>
-      <c r="E10" s="74"/>
-      <c r="F10" s="71"/>
-      <c r="G10" s="59"/>
-      <c r="H10" s="72"/>
+      <c r="A10" s="58"/>
+      <c r="B10" s="82"/>
+      <c r="C10" s="86"/>
+      <c r="D10" s="63"/>
+      <c r="E10" s="60"/>
+      <c r="F10" s="63"/>
+      <c r="G10" s="81"/>
+      <c r="H10" s="64"/>
       <c r="I10" s="10" t="s">
         <v>35</v>
       </c>
       <c r="J10" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="K10" s="78"/>
+      <c r="K10" s="70"/>
       <c r="L10" s="4"/>
     </row>
     <row r="11" spans="1:13" ht="15" customHeight="1">
-      <c r="A11" s="65"/>
-      <c r="B11" s="67"/>
-      <c r="C11" s="69"/>
-      <c r="D11" s="71"/>
-      <c r="E11" s="74"/>
-      <c r="F11" s="71"/>
-      <c r="G11" s="73" t="s">
+      <c r="A11" s="58"/>
+      <c r="B11" s="82"/>
+      <c r="C11" s="86"/>
+      <c r="D11" s="63"/>
+      <c r="E11" s="60"/>
+      <c r="F11" s="63"/>
+      <c r="G11" s="59" t="s">
         <v>67</v>
       </c>
-      <c r="H11" s="70" t="s">
+      <c r="H11" s="62" t="s">
         <v>21</v>
       </c>
       <c r="I11" s="15" t="s">
@@ -2065,58 +2065,58 @@
       <c r="K11" s="5"/>
     </row>
     <row r="12" spans="1:13">
-      <c r="A12" s="65"/>
-      <c r="B12" s="67"/>
-      <c r="C12" s="69"/>
-      <c r="D12" s="71"/>
-      <c r="E12" s="74"/>
-      <c r="F12" s="71"/>
-      <c r="G12" s="74"/>
-      <c r="H12" s="71"/>
-      <c r="I12" s="60" t="s">
+      <c r="A12" s="58"/>
+      <c r="B12" s="82"/>
+      <c r="C12" s="86"/>
+      <c r="D12" s="63"/>
+      <c r="E12" s="60"/>
+      <c r="F12" s="63"/>
+      <c r="G12" s="60"/>
+      <c r="H12" s="63"/>
+      <c r="I12" s="76" t="s">
         <v>88</v>
       </c>
-      <c r="J12" s="73" t="s">
+      <c r="J12" s="59" t="s">
         <v>121</v>
       </c>
-      <c r="K12" s="67" t="s">
+      <c r="K12" s="82" t="s">
         <v>92</v>
       </c>
       <c r="L12" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="M12" s="78" t="s">
+      <c r="M12" s="70" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="13" spans="1:13">
-      <c r="A13" s="65"/>
-      <c r="B13" s="67"/>
-      <c r="C13" s="69"/>
-      <c r="D13" s="71"/>
-      <c r="E13" s="74"/>
-      <c r="F13" s="71"/>
-      <c r="G13" s="74"/>
-      <c r="H13" s="71"/>
-      <c r="I13" s="60"/>
-      <c r="J13" s="79"/>
-      <c r="K13" s="67"/>
+      <c r="A13" s="58"/>
+      <c r="B13" s="82"/>
+      <c r="C13" s="86"/>
+      <c r="D13" s="63"/>
+      <c r="E13" s="60"/>
+      <c r="F13" s="63"/>
+      <c r="G13" s="60"/>
+      <c r="H13" s="63"/>
+      <c r="I13" s="76"/>
+      <c r="J13" s="61"/>
+      <c r="K13" s="82"/>
       <c r="L13" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="M13" s="78"/>
+      <c r="M13" s="70"/>
     </row>
     <row r="14" spans="1:13" s="17" customFormat="1" ht="15" customHeight="1">
-      <c r="A14" s="65"/>
-      <c r="B14" s="67"/>
-      <c r="C14" s="69"/>
-      <c r="D14" s="71"/>
-      <c r="E14" s="74"/>
-      <c r="F14" s="71"/>
-      <c r="G14" s="74"/>
-      <c r="H14" s="71"/>
-      <c r="I14" s="60"/>
-      <c r="J14" s="70" t="s">
+      <c r="A14" s="58"/>
+      <c r="B14" s="82"/>
+      <c r="C14" s="86"/>
+      <c r="D14" s="63"/>
+      <c r="E14" s="60"/>
+      <c r="F14" s="63"/>
+      <c r="G14" s="60"/>
+      <c r="H14" s="63"/>
+      <c r="I14" s="76"/>
+      <c r="J14" s="62" t="s">
         <v>27</v>
       </c>
       <c r="K14" s="2" t="s">
@@ -2127,16 +2127,16 @@
       </c>
     </row>
     <row r="15" spans="1:13" s="17" customFormat="1" ht="15" customHeight="1">
-      <c r="A15" s="65"/>
-      <c r="B15" s="67"/>
-      <c r="C15" s="69"/>
-      <c r="D15" s="71"/>
-      <c r="E15" s="74"/>
-      <c r="F15" s="71"/>
-      <c r="G15" s="74"/>
-      <c r="H15" s="71"/>
-      <c r="I15" s="60"/>
-      <c r="J15" s="71"/>
+      <c r="A15" s="58"/>
+      <c r="B15" s="82"/>
+      <c r="C15" s="86"/>
+      <c r="D15" s="63"/>
+      <c r="E15" s="60"/>
+      <c r="F15" s="63"/>
+      <c r="G15" s="60"/>
+      <c r="H15" s="63"/>
+      <c r="I15" s="76"/>
+      <c r="J15" s="63"/>
       <c r="K15" s="2" t="s">
         <v>11</v>
       </c>
@@ -2145,16 +2145,16 @@
       </c>
     </row>
     <row r="16" spans="1:13" s="17" customFormat="1" ht="34.799999999999997">
-      <c r="A16" s="65"/>
-      <c r="B16" s="67"/>
-      <c r="C16" s="69"/>
-      <c r="D16" s="71"/>
-      <c r="E16" s="74"/>
-      <c r="F16" s="71"/>
-      <c r="G16" s="74"/>
-      <c r="H16" s="71"/>
-      <c r="I16" s="60"/>
-      <c r="J16" s="72"/>
+      <c r="A16" s="58"/>
+      <c r="B16" s="82"/>
+      <c r="C16" s="86"/>
+      <c r="D16" s="63"/>
+      <c r="E16" s="60"/>
+      <c r="F16" s="63"/>
+      <c r="G16" s="60"/>
+      <c r="H16" s="63"/>
+      <c r="I16" s="76"/>
+      <c r="J16" s="64"/>
       <c r="K16" s="2" t="s">
         <v>39</v>
       </c>
@@ -2163,16 +2163,16 @@
       </c>
     </row>
     <row r="17" spans="1:13" s="17" customFormat="1">
-      <c r="A17" s="65"/>
-      <c r="B17" s="67"/>
-      <c r="C17" s="69"/>
-      <c r="D17" s="71"/>
-      <c r="E17" s="74"/>
-      <c r="F17" s="71"/>
-      <c r="G17" s="74"/>
-      <c r="H17" s="71"/>
-      <c r="I17" s="60"/>
-      <c r="J17" s="70" t="s">
+      <c r="A17" s="58"/>
+      <c r="B17" s="82"/>
+      <c r="C17" s="86"/>
+      <c r="D17" s="63"/>
+      <c r="E17" s="60"/>
+      <c r="F17" s="63"/>
+      <c r="G17" s="60"/>
+      <c r="H17" s="63"/>
+      <c r="I17" s="76"/>
+      <c r="J17" s="62" t="s">
         <v>133</v>
       </c>
       <c r="K17" s="2" t="s">
@@ -2183,16 +2183,16 @@
       </c>
     </row>
     <row r="18" spans="1:13" s="17" customFormat="1">
-      <c r="A18" s="65"/>
-      <c r="B18" s="67"/>
-      <c r="C18" s="69"/>
-      <c r="D18" s="71"/>
-      <c r="E18" s="74"/>
-      <c r="F18" s="71"/>
-      <c r="G18" s="74"/>
-      <c r="H18" s="71"/>
-      <c r="I18" s="60"/>
-      <c r="J18" s="71"/>
+      <c r="A18" s="58"/>
+      <c r="B18" s="82"/>
+      <c r="C18" s="86"/>
+      <c r="D18" s="63"/>
+      <c r="E18" s="60"/>
+      <c r="F18" s="63"/>
+      <c r="G18" s="60"/>
+      <c r="H18" s="63"/>
+      <c r="I18" s="76"/>
+      <c r="J18" s="63"/>
       <c r="K18" s="2" t="s">
         <v>127</v>
       </c>
@@ -2201,16 +2201,16 @@
       </c>
     </row>
     <row r="19" spans="1:13" s="17" customFormat="1" ht="34.799999999999997">
-      <c r="A19" s="65"/>
-      <c r="B19" s="67"/>
-      <c r="C19" s="69"/>
-      <c r="D19" s="71"/>
-      <c r="E19" s="74"/>
-      <c r="F19" s="71"/>
-      <c r="G19" s="74"/>
-      <c r="H19" s="71"/>
-      <c r="I19" s="60"/>
-      <c r="J19" s="72"/>
+      <c r="A19" s="58"/>
+      <c r="B19" s="82"/>
+      <c r="C19" s="86"/>
+      <c r="D19" s="63"/>
+      <c r="E19" s="60"/>
+      <c r="F19" s="63"/>
+      <c r="G19" s="60"/>
+      <c r="H19" s="63"/>
+      <c r="I19" s="76"/>
+      <c r="J19" s="64"/>
       <c r="K19" s="2" t="s">
         <v>128</v>
       </c>
@@ -2219,16 +2219,16 @@
       </c>
     </row>
     <row r="20" spans="1:13" s="17" customFormat="1">
-      <c r="A20" s="65"/>
-      <c r="B20" s="67"/>
-      <c r="C20" s="69"/>
-      <c r="D20" s="71"/>
-      <c r="E20" s="74"/>
-      <c r="F20" s="71"/>
-      <c r="G20" s="74"/>
-      <c r="H20" s="71"/>
-      <c r="I20" s="60"/>
-      <c r="J20" s="70" t="s">
+      <c r="A20" s="58"/>
+      <c r="B20" s="82"/>
+      <c r="C20" s="86"/>
+      <c r="D20" s="63"/>
+      <c r="E20" s="60"/>
+      <c r="F20" s="63"/>
+      <c r="G20" s="60"/>
+      <c r="H20" s="63"/>
+      <c r="I20" s="76"/>
+      <c r="J20" s="62" t="s">
         <v>134</v>
       </c>
       <c r="K20" s="2" t="s">
@@ -2239,16 +2239,16 @@
       </c>
     </row>
     <row r="21" spans="1:13" s="17" customFormat="1">
-      <c r="A21" s="65"/>
-      <c r="B21" s="67"/>
-      <c r="C21" s="69"/>
-      <c r="D21" s="71"/>
-      <c r="E21" s="74"/>
-      <c r="F21" s="71"/>
-      <c r="G21" s="74"/>
-      <c r="H21" s="71"/>
-      <c r="I21" s="60"/>
-      <c r="J21" s="71"/>
+      <c r="A21" s="58"/>
+      <c r="B21" s="82"/>
+      <c r="C21" s="86"/>
+      <c r="D21" s="63"/>
+      <c r="E21" s="60"/>
+      <c r="F21" s="63"/>
+      <c r="G21" s="60"/>
+      <c r="H21" s="63"/>
+      <c r="I21" s="76"/>
+      <c r="J21" s="63"/>
       <c r="K21" s="2" t="s">
         <v>131</v>
       </c>
@@ -2257,16 +2257,16 @@
       </c>
     </row>
     <row r="22" spans="1:13" s="17" customFormat="1" ht="34.799999999999997">
-      <c r="A22" s="65"/>
-      <c r="B22" s="67"/>
-      <c r="C22" s="69"/>
-      <c r="D22" s="71"/>
-      <c r="E22" s="74"/>
-      <c r="F22" s="71"/>
-      <c r="G22" s="74"/>
-      <c r="H22" s="71"/>
-      <c r="I22" s="60"/>
-      <c r="J22" s="72"/>
+      <c r="A22" s="58"/>
+      <c r="B22" s="82"/>
+      <c r="C22" s="86"/>
+      <c r="D22" s="63"/>
+      <c r="E22" s="60"/>
+      <c r="F22" s="63"/>
+      <c r="G22" s="60"/>
+      <c r="H22" s="63"/>
+      <c r="I22" s="76"/>
+      <c r="J22" s="64"/>
       <c r="K22" s="2" t="s">
         <v>132</v>
       </c>
@@ -2275,16 +2275,16 @@
       </c>
     </row>
     <row r="23" spans="1:13" s="17" customFormat="1" ht="15" customHeight="1">
-      <c r="A23" s="65"/>
-      <c r="B23" s="67"/>
-      <c r="C23" s="69"/>
-      <c r="D23" s="71"/>
-      <c r="E23" s="74"/>
-      <c r="F23" s="71"/>
-      <c r="G23" s="74"/>
-      <c r="H23" s="71"/>
-      <c r="I23" s="60"/>
-      <c r="J23" s="70" t="s">
+      <c r="A23" s="58"/>
+      <c r="B23" s="82"/>
+      <c r="C23" s="86"/>
+      <c r="D23" s="63"/>
+      <c r="E23" s="60"/>
+      <c r="F23" s="63"/>
+      <c r="G23" s="60"/>
+      <c r="H23" s="63"/>
+      <c r="I23" s="76"/>
+      <c r="J23" s="62" t="s">
         <v>28</v>
       </c>
       <c r="K23" s="2" t="s">
@@ -2295,16 +2295,16 @@
       </c>
     </row>
     <row r="24" spans="1:13" s="17" customFormat="1" ht="15" customHeight="1">
-      <c r="A24" s="65"/>
-      <c r="B24" s="67"/>
-      <c r="C24" s="69"/>
-      <c r="D24" s="71"/>
-      <c r="E24" s="74"/>
-      <c r="F24" s="71"/>
-      <c r="G24" s="74"/>
-      <c r="H24" s="71"/>
-      <c r="I24" s="60"/>
-      <c r="J24" s="71"/>
+      <c r="A24" s="58"/>
+      <c r="B24" s="82"/>
+      <c r="C24" s="86"/>
+      <c r="D24" s="63"/>
+      <c r="E24" s="60"/>
+      <c r="F24" s="63"/>
+      <c r="G24" s="60"/>
+      <c r="H24" s="63"/>
+      <c r="I24" s="76"/>
+      <c r="J24" s="63"/>
       <c r="K24" s="2" t="s">
         <v>13</v>
       </c>
@@ -2313,16 +2313,16 @@
       </c>
     </row>
     <row r="25" spans="1:13" s="17" customFormat="1" ht="34.799999999999997">
-      <c r="A25" s="65"/>
-      <c r="B25" s="67"/>
-      <c r="C25" s="69"/>
-      <c r="D25" s="71"/>
-      <c r="E25" s="74"/>
-      <c r="F25" s="71"/>
-      <c r="G25" s="74"/>
-      <c r="H25" s="71"/>
-      <c r="I25" s="60"/>
-      <c r="J25" s="72"/>
+      <c r="A25" s="58"/>
+      <c r="B25" s="82"/>
+      <c r="C25" s="86"/>
+      <c r="D25" s="63"/>
+      <c r="E25" s="60"/>
+      <c r="F25" s="63"/>
+      <c r="G25" s="60"/>
+      <c r="H25" s="63"/>
+      <c r="I25" s="76"/>
+      <c r="J25" s="64"/>
       <c r="K25" s="2" t="s">
         <v>40</v>
       </c>
@@ -2331,16 +2331,16 @@
       </c>
     </row>
     <row r="26" spans="1:13" s="17" customFormat="1">
-      <c r="A26" s="65"/>
-      <c r="B26" s="67"/>
-      <c r="C26" s="69"/>
-      <c r="D26" s="71"/>
-      <c r="E26" s="74"/>
-      <c r="F26" s="71"/>
-      <c r="G26" s="74"/>
-      <c r="H26" s="71"/>
-      <c r="I26" s="60"/>
-      <c r="J26" s="70" t="s">
+      <c r="A26" s="58"/>
+      <c r="B26" s="82"/>
+      <c r="C26" s="86"/>
+      <c r="D26" s="63"/>
+      <c r="E26" s="60"/>
+      <c r="F26" s="63"/>
+      <c r="G26" s="60"/>
+      <c r="H26" s="63"/>
+      <c r="I26" s="76"/>
+      <c r="J26" s="62" t="s">
         <v>26</v>
       </c>
       <c r="K26" s="2" t="s">
@@ -2352,16 +2352,16 @@
       <c r="M26" s="1"/>
     </row>
     <row r="27" spans="1:13" s="17" customFormat="1">
-      <c r="A27" s="65"/>
-      <c r="B27" s="67"/>
-      <c r="C27" s="69"/>
-      <c r="D27" s="71"/>
-      <c r="E27" s="74"/>
-      <c r="F27" s="71"/>
-      <c r="G27" s="74"/>
-      <c r="H27" s="71"/>
-      <c r="I27" s="60"/>
-      <c r="J27" s="71"/>
+      <c r="A27" s="58"/>
+      <c r="B27" s="82"/>
+      <c r="C27" s="86"/>
+      <c r="D27" s="63"/>
+      <c r="E27" s="60"/>
+      <c r="F27" s="63"/>
+      <c r="G27" s="60"/>
+      <c r="H27" s="63"/>
+      <c r="I27" s="76"/>
+      <c r="J27" s="63"/>
       <c r="K27" s="2" t="s">
         <v>15</v>
       </c>
@@ -2371,16 +2371,16 @@
       <c r="M27" s="1"/>
     </row>
     <row r="28" spans="1:13" ht="34.799999999999997">
-      <c r="A28" s="65"/>
-      <c r="B28" s="67"/>
-      <c r="C28" s="69"/>
-      <c r="D28" s="71"/>
-      <c r="E28" s="74"/>
-      <c r="F28" s="71"/>
-      <c r="G28" s="74"/>
-      <c r="H28" s="71"/>
-      <c r="I28" s="60"/>
-      <c r="J28" s="72"/>
+      <c r="A28" s="58"/>
+      <c r="B28" s="82"/>
+      <c r="C28" s="86"/>
+      <c r="D28" s="63"/>
+      <c r="E28" s="60"/>
+      <c r="F28" s="63"/>
+      <c r="G28" s="60"/>
+      <c r="H28" s="63"/>
+      <c r="I28" s="76"/>
+      <c r="J28" s="64"/>
       <c r="K28" s="2" t="s">
         <v>41</v>
       </c>
@@ -2389,16 +2389,16 @@
       </c>
     </row>
     <row r="29" spans="1:13">
-      <c r="A29" s="65"/>
-      <c r="B29" s="67"/>
-      <c r="C29" s="69"/>
-      <c r="D29" s="71"/>
-      <c r="E29" s="74"/>
-      <c r="F29" s="71"/>
-      <c r="G29" s="74"/>
-      <c r="H29" s="71"/>
-      <c r="I29" s="60"/>
-      <c r="J29" s="70" t="s">
+      <c r="A29" s="58"/>
+      <c r="B29" s="82"/>
+      <c r="C29" s="86"/>
+      <c r="D29" s="63"/>
+      <c r="E29" s="60"/>
+      <c r="F29" s="63"/>
+      <c r="G29" s="60"/>
+      <c r="H29" s="63"/>
+      <c r="I29" s="76"/>
+      <c r="J29" s="62" t="s">
         <v>25</v>
       </c>
       <c r="K29" s="2" t="s">
@@ -2409,16 +2409,16 @@
       </c>
     </row>
     <row r="30" spans="1:13">
-      <c r="A30" s="65"/>
-      <c r="B30" s="67"/>
-      <c r="C30" s="69"/>
-      <c r="D30" s="71"/>
-      <c r="E30" s="74"/>
-      <c r="F30" s="71"/>
-      <c r="G30" s="74"/>
-      <c r="H30" s="71"/>
-      <c r="I30" s="60"/>
-      <c r="J30" s="71"/>
+      <c r="A30" s="58"/>
+      <c r="B30" s="82"/>
+      <c r="C30" s="86"/>
+      <c r="D30" s="63"/>
+      <c r="E30" s="60"/>
+      <c r="F30" s="63"/>
+      <c r="G30" s="60"/>
+      <c r="H30" s="63"/>
+      <c r="I30" s="76"/>
+      <c r="J30" s="63"/>
       <c r="K30" s="2" t="s">
         <v>80</v>
       </c>
@@ -2427,16 +2427,16 @@
       </c>
     </row>
     <row r="31" spans="1:13" ht="34.799999999999997">
-      <c r="A31" s="65"/>
-      <c r="B31" s="67"/>
-      <c r="C31" s="69"/>
-      <c r="D31" s="71"/>
-      <c r="E31" s="74"/>
-      <c r="F31" s="71"/>
-      <c r="G31" s="74"/>
-      <c r="H31" s="71"/>
-      <c r="I31" s="60"/>
-      <c r="J31" s="72"/>
+      <c r="A31" s="58"/>
+      <c r="B31" s="82"/>
+      <c r="C31" s="86"/>
+      <c r="D31" s="63"/>
+      <c r="E31" s="60"/>
+      <c r="F31" s="63"/>
+      <c r="G31" s="60"/>
+      <c r="H31" s="63"/>
+      <c r="I31" s="76"/>
+      <c r="J31" s="64"/>
       <c r="K31" s="2" t="s">
         <v>42</v>
       </c>
@@ -2445,16 +2445,16 @@
       </c>
     </row>
     <row r="32" spans="1:13">
-      <c r="A32" s="65"/>
-      <c r="B32" s="67"/>
-      <c r="C32" s="69"/>
-      <c r="D32" s="71"/>
-      <c r="E32" s="74"/>
-      <c r="F32" s="71"/>
-      <c r="G32" s="74"/>
-      <c r="H32" s="71"/>
-      <c r="I32" s="60"/>
-      <c r="J32" s="70" t="s">
+      <c r="A32" s="58"/>
+      <c r="B32" s="82"/>
+      <c r="C32" s="86"/>
+      <c r="D32" s="63"/>
+      <c r="E32" s="60"/>
+      <c r="F32" s="63"/>
+      <c r="G32" s="60"/>
+      <c r="H32" s="63"/>
+      <c r="I32" s="76"/>
+      <c r="J32" s="62" t="s">
         <v>29</v>
       </c>
       <c r="K32" s="2" t="s">
@@ -2465,16 +2465,16 @@
       </c>
     </row>
     <row r="33" spans="1:12">
-      <c r="A33" s="65"/>
-      <c r="B33" s="67"/>
-      <c r="C33" s="69"/>
-      <c r="D33" s="71"/>
-      <c r="E33" s="74"/>
-      <c r="F33" s="71"/>
-      <c r="G33" s="74"/>
-      <c r="H33" s="71"/>
-      <c r="I33" s="60"/>
-      <c r="J33" s="71"/>
+      <c r="A33" s="58"/>
+      <c r="B33" s="82"/>
+      <c r="C33" s="86"/>
+      <c r="D33" s="63"/>
+      <c r="E33" s="60"/>
+      <c r="F33" s="63"/>
+      <c r="G33" s="60"/>
+      <c r="H33" s="63"/>
+      <c r="I33" s="76"/>
+      <c r="J33" s="63"/>
       <c r="K33" s="2" t="s">
         <v>76</v>
       </c>
@@ -2483,16 +2483,16 @@
       </c>
     </row>
     <row r="34" spans="1:12" ht="34.799999999999997">
-      <c r="A34" s="65"/>
-      <c r="B34" s="67"/>
-      <c r="C34" s="69"/>
-      <c r="D34" s="71"/>
-      <c r="E34" s="74"/>
-      <c r="F34" s="71"/>
-      <c r="G34" s="74"/>
-      <c r="H34" s="71"/>
-      <c r="I34" s="60"/>
-      <c r="J34" s="72"/>
+      <c r="A34" s="58"/>
+      <c r="B34" s="82"/>
+      <c r="C34" s="86"/>
+      <c r="D34" s="63"/>
+      <c r="E34" s="60"/>
+      <c r="F34" s="63"/>
+      <c r="G34" s="60"/>
+      <c r="H34" s="63"/>
+      <c r="I34" s="76"/>
+      <c r="J34" s="64"/>
       <c r="K34" s="2" t="s">
         <v>43</v>
       </c>
@@ -2501,16 +2501,16 @@
       </c>
     </row>
     <row r="35" spans="1:12">
-      <c r="A35" s="65"/>
-      <c r="B35" s="67"/>
-      <c r="C35" s="69"/>
-      <c r="D35" s="71"/>
-      <c r="E35" s="74"/>
-      <c r="F35" s="71"/>
-      <c r="G35" s="74"/>
-      <c r="H35" s="71"/>
-      <c r="I35" s="60"/>
-      <c r="J35" s="70" t="s">
+      <c r="A35" s="58"/>
+      <c r="B35" s="82"/>
+      <c r="C35" s="86"/>
+      <c r="D35" s="63"/>
+      <c r="E35" s="60"/>
+      <c r="F35" s="63"/>
+      <c r="G35" s="60"/>
+      <c r="H35" s="63"/>
+      <c r="I35" s="76"/>
+      <c r="J35" s="62" t="s">
         <v>30</v>
       </c>
       <c r="K35" s="2" t="s">
@@ -2521,16 +2521,16 @@
       </c>
     </row>
     <row r="36" spans="1:12">
-      <c r="A36" s="65"/>
-      <c r="B36" s="67"/>
-      <c r="C36" s="69"/>
-      <c r="D36" s="71"/>
-      <c r="E36" s="74"/>
-      <c r="F36" s="71"/>
-      <c r="G36" s="74"/>
-      <c r="H36" s="71"/>
-      <c r="I36" s="60"/>
-      <c r="J36" s="71"/>
+      <c r="A36" s="58"/>
+      <c r="B36" s="82"/>
+      <c r="C36" s="86"/>
+      <c r="D36" s="63"/>
+      <c r="E36" s="60"/>
+      <c r="F36" s="63"/>
+      <c r="G36" s="60"/>
+      <c r="H36" s="63"/>
+      <c r="I36" s="76"/>
+      <c r="J36" s="63"/>
       <c r="K36" s="2" t="s">
         <v>78</v>
       </c>
@@ -2539,16 +2539,16 @@
       </c>
     </row>
     <row r="37" spans="1:12" ht="34.799999999999997">
-      <c r="A37" s="65"/>
-      <c r="B37" s="67"/>
-      <c r="C37" s="69"/>
-      <c r="D37" s="71"/>
-      <c r="E37" s="74"/>
-      <c r="F37" s="71"/>
-      <c r="G37" s="79"/>
-      <c r="H37" s="72"/>
-      <c r="I37" s="60"/>
-      <c r="J37" s="72"/>
+      <c r="A37" s="58"/>
+      <c r="B37" s="82"/>
+      <c r="C37" s="86"/>
+      <c r="D37" s="63"/>
+      <c r="E37" s="60"/>
+      <c r="F37" s="63"/>
+      <c r="G37" s="61"/>
+      <c r="H37" s="64"/>
+      <c r="I37" s="76"/>
+      <c r="J37" s="64"/>
       <c r="K37" s="2" t="s">
         <v>44</v>
       </c>
@@ -2557,12 +2557,12 @@
       </c>
     </row>
     <row r="38" spans="1:12">
-      <c r="A38" s="65"/>
-      <c r="B38" s="67"/>
-      <c r="C38" s="69"/>
-      <c r="D38" s="71"/>
-      <c r="E38" s="74"/>
-      <c r="F38" s="71"/>
+      <c r="A38" s="58"/>
+      <c r="B38" s="82"/>
+      <c r="C38" s="86"/>
+      <c r="D38" s="63"/>
+      <c r="E38" s="60"/>
+      <c r="F38" s="63"/>
       <c r="G38" s="2" t="s">
         <v>188</v>
       </c>
@@ -2575,13 +2575,13 @@
       <c r="L38" s="4"/>
     </row>
     <row r="39" spans="1:12">
-      <c r="A39" s="65"/>
-      <c r="B39" s="67"/>
-      <c r="C39" s="69"/>
-      <c r="D39" s="71"/>
-      <c r="E39" s="74"/>
-      <c r="F39" s="71"/>
-      <c r="G39" s="57" t="s">
+      <c r="A39" s="58"/>
+      <c r="B39" s="82"/>
+      <c r="C39" s="86"/>
+      <c r="D39" s="63"/>
+      <c r="E39" s="60"/>
+      <c r="F39" s="63"/>
+      <c r="G39" s="68" t="s">
         <v>173</v>
       </c>
       <c r="H39" s="36" t="s">
@@ -2593,13 +2593,13 @@
       <c r="L39" s="4"/>
     </row>
     <row r="40" spans="1:12">
-      <c r="A40" s="65"/>
-      <c r="B40" s="67"/>
-      <c r="C40" s="69"/>
-      <c r="D40" s="71"/>
-      <c r="E40" s="74"/>
-      <c r="F40" s="71"/>
-      <c r="G40" s="58"/>
+      <c r="A40" s="58"/>
+      <c r="B40" s="82"/>
+      <c r="C40" s="86"/>
+      <c r="D40" s="63"/>
+      <c r="E40" s="60"/>
+      <c r="F40" s="63"/>
+      <c r="G40" s="69"/>
       <c r="H40" s="36" t="s">
         <v>175</v>
       </c>
@@ -2609,13 +2609,13 @@
       <c r="L40" s="4"/>
     </row>
     <row r="41" spans="1:12">
-      <c r="A41" s="65"/>
-      <c r="B41" s="67"/>
-      <c r="C41" s="69"/>
-      <c r="D41" s="71"/>
-      <c r="E41" s="74"/>
-      <c r="F41" s="71"/>
-      <c r="G41" s="59"/>
+      <c r="A41" s="58"/>
+      <c r="B41" s="82"/>
+      <c r="C41" s="86"/>
+      <c r="D41" s="63"/>
+      <c r="E41" s="60"/>
+      <c r="F41" s="63"/>
+      <c r="G41" s="81"/>
       <c r="H41" s="36" t="s">
         <v>178</v>
       </c>
@@ -2625,12 +2625,12 @@
       <c r="L41" s="4"/>
     </row>
     <row r="42" spans="1:12" ht="34.799999999999997">
-      <c r="A42" s="65"/>
-      <c r="B42" s="67"/>
-      <c r="C42" s="69"/>
-      <c r="D42" s="71"/>
-      <c r="E42" s="74"/>
-      <c r="F42" s="71"/>
+      <c r="A42" s="58"/>
+      <c r="B42" s="82"/>
+      <c r="C42" s="86"/>
+      <c r="D42" s="63"/>
+      <c r="E42" s="60"/>
+      <c r="F42" s="63"/>
       <c r="G42" s="28" t="s">
         <v>176</v>
       </c>
@@ -2645,10 +2645,10 @@
       <c r="L42" s="5"/>
     </row>
     <row r="43" spans="1:12" ht="34.799999999999997">
-      <c r="A43" s="65"/>
-      <c r="B43" s="67"/>
-      <c r="C43" s="69"/>
-      <c r="D43" s="71"/>
+      <c r="A43" s="58"/>
+      <c r="B43" s="82"/>
+      <c r="C43" s="86"/>
+      <c r="D43" s="63"/>
       <c r="E43" s="2" t="s">
         <v>125</v>
       </c>
@@ -2661,10 +2661,10 @@
       <c r="L43" s="5"/>
     </row>
     <row r="44" spans="1:12" ht="34.799999999999997">
-      <c r="A44" s="65"/>
-      <c r="B44" s="67"/>
-      <c r="C44" s="69"/>
-      <c r="D44" s="72"/>
+      <c r="A44" s="58"/>
+      <c r="B44" s="82"/>
+      <c r="C44" s="86"/>
+      <c r="D44" s="64"/>
       <c r="E44" s="2" t="s">
         <v>124</v>
       </c>
@@ -2679,8 +2679,8 @@
       <c r="L44" s="5"/>
     </row>
     <row r="45" spans="1:12" ht="34.799999999999997">
-      <c r="A45" s="65"/>
-      <c r="B45" s="67"/>
+      <c r="A45" s="58"/>
+      <c r="B45" s="82"/>
       <c r="C45" s="13" t="s">
         <v>56</v>
       </c>
@@ -2694,8 +2694,8 @@
       <c r="I45" s="5"/>
     </row>
     <row r="46" spans="1:12" ht="34.799999999999997">
-      <c r="A46" s="65"/>
-      <c r="B46" s="67"/>
+      <c r="A46" s="58"/>
+      <c r="B46" s="82"/>
       <c r="C46" s="13" t="s">
         <v>122</v>
       </c>
@@ -2709,10 +2709,10 @@
       <c r="I46" s="5"/>
     </row>
     <row r="47" spans="1:12" ht="34.799999999999997">
-      <c r="A47" s="65"/>
-      <c r="B47" s="67"/>
+      <c r="A47" s="58"/>
+      <c r="B47" s="82"/>
       <c r="C47" s="28" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D47" s="30" t="s">
         <v>32</v>
@@ -2724,8 +2724,8 @@
       <c r="I47" s="5"/>
     </row>
     <row r="48" spans="1:12" ht="34.799999999999997">
-      <c r="A48" s="65"/>
-      <c r="B48" s="67"/>
+      <c r="A48" s="58"/>
+      <c r="B48" s="82"/>
       <c r="C48" s="10" t="s">
         <v>157</v>
       </c>
@@ -2739,7 +2739,7 @@
       <c r="I48" s="5"/>
     </row>
     <row r="49" spans="1:9">
-      <c r="A49" s="65"/>
+      <c r="A49" s="58"/>
       <c r="B49" s="3" t="s">
         <v>95</v>
       </c>
@@ -2752,7 +2752,7 @@
       <c r="I49" s="5"/>
     </row>
     <row r="50" spans="1:9">
-      <c r="A50" s="65"/>
+      <c r="A50" s="58"/>
       <c r="B50" s="3" t="s">
         <v>94</v>
       </c>
@@ -2765,7 +2765,7 @@
       <c r="I50" s="5"/>
     </row>
     <row r="51" spans="1:9">
-      <c r="A51" s="65"/>
+      <c r="A51" s="58"/>
       <c r="B51" s="25" t="s">
         <v>154</v>
       </c>
@@ -2778,45 +2778,45 @@
       <c r="I51" s="5"/>
     </row>
     <row r="52" spans="1:9">
-      <c r="A52" s="65"/>
-      <c r="B52" s="54" t="s">
+      <c r="A52" s="58"/>
+      <c r="B52" s="55" t="s">
         <v>59</v>
       </c>
-      <c r="C52" s="57" t="s">
+      <c r="C52" s="68" t="s">
         <v>69</v>
       </c>
-      <c r="D52" s="54" t="s">
+      <c r="D52" s="55" t="s">
         <v>70</v>
       </c>
-      <c r="E52" s="73" t="s">
+      <c r="E52" s="59" t="s">
         <v>61</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G52" s="78" t="s">
+      <c r="G52" s="70" t="s">
         <v>182</v>
       </c>
       <c r="H52" s="5"/>
     </row>
     <row r="53" spans="1:9">
-      <c r="A53" s="65"/>
-      <c r="B53" s="55"/>
-      <c r="C53" s="58"/>
-      <c r="D53" s="55"/>
-      <c r="E53" s="79"/>
+      <c r="A53" s="58"/>
+      <c r="B53" s="67"/>
+      <c r="C53" s="69"/>
+      <c r="D53" s="67"/>
+      <c r="E53" s="61"/>
       <c r="F53" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G53" s="78"/>
+      <c r="G53" s="70"/>
       <c r="H53" s="5"/>
     </row>
     <row r="54" spans="1:9" ht="34.799999999999997">
-      <c r="A54" s="65"/>
-      <c r="B54" s="55"/>
-      <c r="C54" s="58"/>
-      <c r="D54" s="55"/>
-      <c r="E54" s="80" t="s">
+      <c r="A54" s="58"/>
+      <c r="B54" s="67"/>
+      <c r="C54" s="69"/>
+      <c r="D54" s="67"/>
+      <c r="E54" s="71" t="s">
         <v>60</v>
       </c>
       <c r="F54" s="18" t="s">
@@ -2829,11 +2829,11 @@
       <c r="I54" s="5"/>
     </row>
     <row r="55" spans="1:9" ht="52.2">
-      <c r="A55" s="65"/>
-      <c r="B55" s="55"/>
-      <c r="C55" s="58"/>
-      <c r="D55" s="55"/>
-      <c r="E55" s="80"/>
+      <c r="A55" s="58"/>
+      <c r="B55" s="67"/>
+      <c r="C55" s="69"/>
+      <c r="D55" s="67"/>
+      <c r="E55" s="71"/>
       <c r="F55" s="16" t="s">
         <v>114</v>
       </c>
@@ -2844,11 +2844,11 @@
       <c r="I55" s="5"/>
     </row>
     <row r="56" spans="1:9" ht="52.2">
-      <c r="A56" s="65"/>
-      <c r="B56" s="55"/>
-      <c r="C56" s="58"/>
-      <c r="D56" s="55"/>
-      <c r="E56" s="80"/>
+      <c r="A56" s="58"/>
+      <c r="B56" s="67"/>
+      <c r="C56" s="69"/>
+      <c r="D56" s="67"/>
+      <c r="E56" s="71"/>
       <c r="F56" s="16" t="s">
         <v>113</v>
       </c>
@@ -2859,11 +2859,11 @@
       <c r="I56" s="5"/>
     </row>
     <row r="57" spans="1:9">
-      <c r="A57" s="65"/>
-      <c r="B57" s="55"/>
-      <c r="C57" s="58"/>
-      <c r="D57" s="55"/>
-      <c r="E57" s="80"/>
+      <c r="A57" s="58"/>
+      <c r="B57" s="67"/>
+      <c r="C57" s="69"/>
+      <c r="D57" s="67"/>
+      <c r="E57" s="71"/>
       <c r="F57" s="16" t="s">
         <v>100</v>
       </c>
@@ -2874,11 +2874,11 @@
       <c r="I57" s="5"/>
     </row>
     <row r="58" spans="1:9">
-      <c r="A58" s="65"/>
-      <c r="B58" s="55"/>
-      <c r="C58" s="58"/>
-      <c r="D58" s="55"/>
-      <c r="E58" s="80"/>
+      <c r="A58" s="58"/>
+      <c r="B58" s="67"/>
+      <c r="C58" s="69"/>
+      <c r="D58" s="67"/>
+      <c r="E58" s="71"/>
       <c r="F58" s="16" t="s">
         <v>101</v>
       </c>
@@ -2889,11 +2889,11 @@
       <c r="I58" s="5"/>
     </row>
     <row r="59" spans="1:9">
-      <c r="A59" s="65"/>
-      <c r="B59" s="55"/>
-      <c r="C59" s="58"/>
-      <c r="D59" s="55"/>
-      <c r="E59" s="80"/>
+      <c r="A59" s="58"/>
+      <c r="B59" s="67"/>
+      <c r="C59" s="69"/>
+      <c r="D59" s="67"/>
+      <c r="E59" s="71"/>
       <c r="F59" s="16" t="s">
         <v>102</v>
       </c>
@@ -2904,11 +2904,11 @@
       <c r="I59" s="5"/>
     </row>
     <row r="60" spans="1:9">
-      <c r="A60" s="65"/>
-      <c r="B60" s="55"/>
-      <c r="C60" s="58"/>
-      <c r="D60" s="55"/>
-      <c r="E60" s="80"/>
+      <c r="A60" s="58"/>
+      <c r="B60" s="67"/>
+      <c r="C60" s="69"/>
+      <c r="D60" s="67"/>
+      <c r="E60" s="71"/>
       <c r="F60" s="16" t="s">
         <v>103</v>
       </c>
@@ -2919,26 +2919,26 @@
       <c r="I60" s="5"/>
     </row>
     <row r="61" spans="1:9">
-      <c r="A61" s="65"/>
-      <c r="B61" s="55"/>
-      <c r="C61" s="58"/>
-      <c r="D61" s="55"/>
-      <c r="E61" s="80"/>
+      <c r="A61" s="58"/>
+      <c r="B61" s="67"/>
+      <c r="C61" s="69"/>
+      <c r="D61" s="67"/>
+      <c r="E61" s="71"/>
       <c r="F61" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="G61" s="78" t="s">
+      <c r="G61" s="70" t="s">
         <v>81</v>
       </c>
-      <c r="H61" s="63"/>
+      <c r="H61" s="54"/>
       <c r="I61" s="5"/>
     </row>
     <row r="62" spans="1:9">
-      <c r="A62" s="65"/>
-      <c r="B62" s="55"/>
-      <c r="C62" s="58"/>
-      <c r="D62" s="55"/>
-      <c r="E62" s="80"/>
+      <c r="A62" s="58"/>
+      <c r="B62" s="67"/>
+      <c r="C62" s="69"/>
+      <c r="D62" s="67"/>
+      <c r="E62" s="71"/>
       <c r="F62" s="16" t="s">
         <v>105</v>
       </c>
@@ -2949,11 +2949,11 @@
       <c r="I62" s="5"/>
     </row>
     <row r="63" spans="1:9">
-      <c r="A63" s="65"/>
-      <c r="B63" s="55"/>
-      <c r="C63" s="58"/>
-      <c r="D63" s="55"/>
-      <c r="E63" s="80"/>
+      <c r="A63" s="58"/>
+      <c r="B63" s="67"/>
+      <c r="C63" s="69"/>
+      <c r="D63" s="67"/>
+      <c r="E63" s="71"/>
       <c r="F63" s="16" t="s">
         <v>106</v>
       </c>
@@ -2964,11 +2964,11 @@
       <c r="I63" s="5"/>
     </row>
     <row r="64" spans="1:9">
-      <c r="A64" s="65"/>
-      <c r="B64" s="55"/>
-      <c r="C64" s="58"/>
-      <c r="D64" s="55"/>
-      <c r="E64" s="80"/>
+      <c r="A64" s="58"/>
+      <c r="B64" s="67"/>
+      <c r="C64" s="69"/>
+      <c r="D64" s="67"/>
+      <c r="E64" s="71"/>
       <c r="F64" s="16" t="s">
         <v>107</v>
       </c>
@@ -2979,11 +2979,11 @@
       <c r="I64" s="5"/>
     </row>
     <row r="65" spans="1:12">
-      <c r="A65" s="65"/>
-      <c r="B65" s="55"/>
-      <c r="C65" s="58"/>
-      <c r="D65" s="55"/>
-      <c r="E65" s="80"/>
+      <c r="A65" s="58"/>
+      <c r="B65" s="67"/>
+      <c r="C65" s="69"/>
+      <c r="D65" s="67"/>
+      <c r="E65" s="71"/>
       <c r="F65" s="16" t="s">
         <v>108</v>
       </c>
@@ -2994,11 +2994,11 @@
       <c r="I65" s="5"/>
     </row>
     <row r="66" spans="1:12">
-      <c r="A66" s="65"/>
-      <c r="B66" s="55"/>
-      <c r="C66" s="58"/>
-      <c r="D66" s="55"/>
-      <c r="E66" s="80"/>
+      <c r="A66" s="58"/>
+      <c r="B66" s="67"/>
+      <c r="C66" s="69"/>
+      <c r="D66" s="67"/>
+      <c r="E66" s="71"/>
       <c r="F66" s="16" t="s">
         <v>109</v>
       </c>
@@ -3009,11 +3009,11 @@
       <c r="I66" s="5"/>
     </row>
     <row r="67" spans="1:12" ht="69.599999999999994">
-      <c r="A67" s="65"/>
-      <c r="B67" s="55"/>
-      <c r="C67" s="58"/>
-      <c r="D67" s="55"/>
-      <c r="E67" s="80"/>
+      <c r="A67" s="58"/>
+      <c r="B67" s="67"/>
+      <c r="C67" s="69"/>
+      <c r="D67" s="67"/>
+      <c r="E67" s="71"/>
       <c r="F67" s="16" t="s">
         <v>110</v>
       </c>
@@ -3024,11 +3024,11 @@
       <c r="I67" s="5"/>
     </row>
     <row r="68" spans="1:12" ht="34.799999999999997">
-      <c r="A68" s="65"/>
+      <c r="A68" s="58"/>
       <c r="B68" s="56"/>
-      <c r="C68" s="59"/>
+      <c r="C68" s="81"/>
       <c r="D68" s="56"/>
-      <c r="E68" s="80"/>
+      <c r="E68" s="71"/>
       <c r="F68" s="16" t="s">
         <v>111</v>
       </c>
@@ -3039,8 +3039,8 @@
       <c r="I68" s="5"/>
     </row>
     <row r="69" spans="1:12" ht="52.2">
-      <c r="A69" s="65"/>
-      <c r="B69" s="54" t="s">
+      <c r="A69" s="58"/>
+      <c r="B69" s="55" t="s">
         <v>180</v>
       </c>
       <c r="C69" s="9" t="s">
@@ -3061,8 +3061,8 @@
       <c r="L69" s="19"/>
     </row>
     <row r="70" spans="1:12" ht="52.2">
-      <c r="A70" s="65"/>
-      <c r="B70" s="55"/>
+      <c r="A70" s="58"/>
+      <c r="B70" s="67"/>
       <c r="C70" s="13" t="s">
         <v>24</v>
       </c>
@@ -3081,8 +3081,8 @@
       <c r="L70" s="19"/>
     </row>
     <row r="71" spans="1:12" ht="34.799999999999997" customHeight="1">
-      <c r="A71" s="65"/>
-      <c r="B71" s="55"/>
+      <c r="A71" s="58"/>
+      <c r="B71" s="67"/>
       <c r="C71" s="22" t="s">
         <v>57</v>
       </c>
@@ -3099,8 +3099,8 @@
       <c r="L71" s="19"/>
     </row>
     <row r="72" spans="1:12" ht="34.799999999999997">
-      <c r="A72" s="65"/>
-      <c r="B72" s="55"/>
+      <c r="A72" s="58"/>
+      <c r="B72" s="67"/>
       <c r="C72" s="11" t="s">
         <v>58</v>
       </c>
@@ -3116,15 +3116,15 @@
       <c r="L72" s="19"/>
     </row>
     <row r="73" spans="1:12">
-      <c r="A73" s="65"/>
-      <c r="B73" s="55"/>
-      <c r="C73" s="75" t="s">
+      <c r="A73" s="58"/>
+      <c r="B73" s="67"/>
+      <c r="C73" s="72" t="s">
         <v>115</v>
       </c>
-      <c r="D73" s="87" t="s">
+      <c r="D73" s="65" t="s">
         <v>156</v>
       </c>
-      <c r="E73" s="54" t="s">
+      <c r="E73" s="55" t="s">
         <v>172</v>
       </c>
       <c r="F73" s="13" t="s">
@@ -3134,256 +3134,256 @@
         <v>171</v>
       </c>
       <c r="H73" s="12" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="I73" s="4"/>
     </row>
     <row r="74" spans="1:12" ht="52.2">
-      <c r="A74" s="65"/>
-      <c r="B74" s="55"/>
-      <c r="C74" s="75"/>
-      <c r="D74" s="88"/>
-      <c r="E74" s="55"/>
+      <c r="A74" s="58"/>
+      <c r="B74" s="67"/>
+      <c r="C74" s="72"/>
+      <c r="D74" s="66"/>
+      <c r="E74" s="67"/>
       <c r="F74" s="13" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G74" s="16" t="s">
+        <v>232</v>
+      </c>
+      <c r="H74" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="I74" s="4"/>
+    </row>
+    <row r="75" spans="1:12">
+      <c r="A75" s="58"/>
+      <c r="B75" s="67"/>
+      <c r="C75" s="73"/>
+      <c r="D75" s="66"/>
+      <c r="E75" s="67"/>
+      <c r="F75" s="55" t="s">
+        <v>142</v>
+      </c>
+      <c r="G75" s="51" t="s">
+        <v>215</v>
+      </c>
+      <c r="H75" s="23" t="s">
+        <v>248</v>
+      </c>
+      <c r="I75" s="4"/>
+    </row>
+    <row r="76" spans="1:12" ht="69.599999999999994">
+      <c r="A76" s="58"/>
+      <c r="B76" s="67"/>
+      <c r="C76" s="73"/>
+      <c r="D76" s="66"/>
+      <c r="E76" s="67"/>
+      <c r="F76" s="55"/>
+      <c r="G76" s="68" t="s">
+        <v>249</v>
+      </c>
+      <c r="H76" s="52" t="s">
+        <v>250</v>
+      </c>
+      <c r="I76" s="4" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" ht="34.799999999999997">
+      <c r="A77" s="58"/>
+      <c r="B77" s="67"/>
+      <c r="C77" s="73"/>
+      <c r="D77" s="66"/>
+      <c r="E77" s="67"/>
+      <c r="F77" s="55"/>
+      <c r="G77" s="88"/>
+      <c r="H77" s="52" t="s">
+        <v>252</v>
+      </c>
+      <c r="I77" s="4"/>
+    </row>
+    <row r="78" spans="1:12">
+      <c r="A78" s="58"/>
+      <c r="B78" s="67"/>
+      <c r="C78" s="73"/>
+      <c r="D78" s="66"/>
+      <c r="E78" s="67"/>
+      <c r="F78" s="55"/>
+      <c r="G78" s="88"/>
+      <c r="H78" s="52" t="s">
+        <v>253</v>
+      </c>
+      <c r="I78" s="4"/>
+    </row>
+    <row r="79" spans="1:12" ht="87">
+      <c r="A79" s="58"/>
+      <c r="B79" s="67"/>
+      <c r="C79" s="73"/>
+      <c r="D79" s="66"/>
+      <c r="E79" s="67"/>
+      <c r="F79" s="67"/>
+      <c r="G79" s="68" t="s">
+        <v>191</v>
+      </c>
+      <c r="H79" s="52" t="s">
+        <v>238</v>
+      </c>
+      <c r="I79" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="H74" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="I74" s="4"/>
-    </row>
-    <row r="75" spans="1:12">
-      <c r="A75" s="65"/>
-      <c r="B75" s="55"/>
-      <c r="C75" s="76"/>
-      <c r="D75" s="88"/>
-      <c r="E75" s="55"/>
-      <c r="F75" s="54" t="s">
-        <v>142</v>
-      </c>
-      <c r="G75" s="51" t="s">
-        <v>216</v>
-      </c>
-      <c r="H75" s="23" t="s">
-        <v>249</v>
-      </c>
-      <c r="I75" s="4"/>
-    </row>
-    <row r="76" spans="1:12" ht="69.599999999999994">
-      <c r="A76" s="65"/>
-      <c r="B76" s="55"/>
-      <c r="C76" s="76"/>
-      <c r="D76" s="88"/>
-      <c r="E76" s="55"/>
-      <c r="F76" s="54"/>
-      <c r="G76" s="57" t="s">
-        <v>250</v>
-      </c>
-      <c r="H76" s="52" t="s">
-        <v>251</v>
-      </c>
-      <c r="I76" s="4" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12" ht="34.799999999999997">
-      <c r="A77" s="65"/>
-      <c r="B77" s="55"/>
-      <c r="C77" s="76"/>
-      <c r="D77" s="88"/>
-      <c r="E77" s="55"/>
-      <c r="F77" s="54"/>
-      <c r="G77" s="61"/>
-      <c r="H77" s="52" t="s">
-        <v>253</v>
-      </c>
-      <c r="I77" s="4"/>
-    </row>
-    <row r="78" spans="1:12">
-      <c r="A78" s="65"/>
-      <c r="B78" s="55"/>
-      <c r="C78" s="76"/>
-      <c r="D78" s="88"/>
-      <c r="E78" s="55"/>
-      <c r="F78" s="54"/>
-      <c r="G78" s="61"/>
-      <c r="H78" s="52" t="s">
+    </row>
+    <row r="80" spans="1:12" ht="139.19999999999999">
+      <c r="A80" s="58"/>
+      <c r="B80" s="67"/>
+      <c r="C80" s="73"/>
+      <c r="D80" s="66"/>
+      <c r="E80" s="67"/>
+      <c r="F80" s="67"/>
+      <c r="G80" s="68"/>
+      <c r="H80" s="52" t="s">
         <v>254</v>
       </c>
-      <c r="I78" s="4"/>
-    </row>
-    <row r="79" spans="1:12" ht="87">
-      <c r="A79" s="65"/>
-      <c r="B79" s="55"/>
-      <c r="C79" s="76"/>
-      <c r="D79" s="88"/>
-      <c r="E79" s="55"/>
-      <c r="F79" s="55"/>
-      <c r="G79" s="57" t="s">
-        <v>192</v>
-      </c>
-      <c r="H79" s="52" t="s">
-        <v>239</v>
-      </c>
-      <c r="I79" s="4" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" ht="139.19999999999999">
-      <c r="A80" s="65"/>
-      <c r="B80" s="55"/>
-      <c r="C80" s="76"/>
-      <c r="D80" s="88"/>
-      <c r="E80" s="55"/>
-      <c r="F80" s="55"/>
-      <c r="G80" s="57"/>
-      <c r="H80" s="52" t="s">
+      <c r="I80" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="I80" s="4" t="s">
-        <v>256</v>
-      </c>
     </row>
     <row r="81" spans="1:11" ht="34.799999999999997">
-      <c r="A81" s="65"/>
-      <c r="B81" s="55"/>
-      <c r="C81" s="76"/>
-      <c r="D81" s="88"/>
-      <c r="E81" s="55"/>
-      <c r="F81" s="55"/>
+      <c r="A81" s="58"/>
+      <c r="B81" s="67"/>
+      <c r="C81" s="73"/>
+      <c r="D81" s="66"/>
+      <c r="E81" s="67"/>
+      <c r="F81" s="67"/>
       <c r="G81" s="39" t="s">
+        <v>217</v>
+      </c>
+      <c r="H81" s="29" t="s">
         <v>218</v>
       </c>
-      <c r="H81" s="29" t="s">
+      <c r="I81" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="I81" s="4" t="s">
-        <v>220</v>
-      </c>
     </row>
     <row r="82" spans="1:11" ht="34.799999999999997" customHeight="1">
-      <c r="A82" s="65"/>
-      <c r="B82" s="55"/>
-      <c r="C82" s="76"/>
-      <c r="D82" s="88"/>
-      <c r="E82" s="55"/>
-      <c r="F82" s="55"/>
-      <c r="G82" s="83" t="s">
+      <c r="A82" s="58"/>
+      <c r="B82" s="67"/>
+      <c r="C82" s="73"/>
+      <c r="D82" s="66"/>
+      <c r="E82" s="67"/>
+      <c r="F82" s="67"/>
+      <c r="G82" s="77" t="s">
         <v>158</v>
       </c>
-      <c r="H82" s="60" t="s">
-        <v>207</v>
+      <c r="H82" s="76" t="s">
+        <v>206</v>
       </c>
       <c r="I82" s="28" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J82" s="3" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="83" spans="1:11">
-      <c r="A83" s="65"/>
-      <c r="B83" s="55"/>
-      <c r="C83" s="76"/>
-      <c r="D83" s="88"/>
-      <c r="E83" s="55"/>
-      <c r="F83" s="55"/>
-      <c r="G83" s="84"/>
-      <c r="H83" s="60"/>
+      <c r="A83" s="58"/>
+      <c r="B83" s="67"/>
+      <c r="C83" s="73"/>
+      <c r="D83" s="66"/>
+      <c r="E83" s="67"/>
+      <c r="F83" s="67"/>
+      <c r="G83" s="78"/>
+      <c r="H83" s="76"/>
       <c r="I83" s="28" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="J83" s="3" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="84" spans="1:11" ht="33.6" customHeight="1">
-      <c r="A84" s="65"/>
-      <c r="B84" s="55"/>
-      <c r="C84" s="76"/>
-      <c r="D84" s="88"/>
-      <c r="E84" s="55"/>
-      <c r="F84" s="55"/>
-      <c r="G84" s="84"/>
-      <c r="H84" s="60"/>
-      <c r="I84" s="57" t="s">
-        <v>212</v>
-      </c>
-      <c r="J84" s="54" t="s">
-        <v>217</v>
+      <c r="A84" s="58"/>
+      <c r="B84" s="67"/>
+      <c r="C84" s="73"/>
+      <c r="D84" s="66"/>
+      <c r="E84" s="67"/>
+      <c r="F84" s="67"/>
+      <c r="G84" s="78"/>
+      <c r="H84" s="76"/>
+      <c r="I84" s="68" t="s">
+        <v>211</v>
+      </c>
+      <c r="J84" s="55" t="s">
+        <v>216</v>
       </c>
       <c r="K84" s="21" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="85" spans="1:11">
-      <c r="A85" s="65"/>
-      <c r="B85" s="55"/>
-      <c r="C85" s="76"/>
-      <c r="D85" s="88"/>
-      <c r="E85" s="55"/>
-      <c r="F85" s="55"/>
-      <c r="G85" s="84"/>
-      <c r="H85" s="60"/>
-      <c r="I85" s="58"/>
-      <c r="J85" s="55"/>
+      <c r="A85" s="58"/>
+      <c r="B85" s="67"/>
+      <c r="C85" s="73"/>
+      <c r="D85" s="66"/>
+      <c r="E85" s="67"/>
+      <c r="F85" s="67"/>
+      <c r="G85" s="78"/>
+      <c r="H85" s="76"/>
+      <c r="I85" s="69"/>
+      <c r="J85" s="67"/>
       <c r="K85" s="21" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="86" spans="1:11">
-      <c r="A86" s="65"/>
-      <c r="B86" s="55"/>
-      <c r="C86" s="76"/>
-      <c r="D86" s="88"/>
-      <c r="E86" s="55"/>
-      <c r="F86" s="55"/>
-      <c r="G86" s="84"/>
-      <c r="H86" s="60"/>
-      <c r="I86" s="59"/>
+      <c r="A86" s="58"/>
+      <c r="B86" s="67"/>
+      <c r="C86" s="73"/>
+      <c r="D86" s="66"/>
+      <c r="E86" s="67"/>
+      <c r="F86" s="67"/>
+      <c r="G86" s="78"/>
+      <c r="H86" s="76"/>
+      <c r="I86" s="81"/>
       <c r="J86" s="56"/>
       <c r="K86" s="21" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="87" spans="1:11" ht="34.799999999999997">
-      <c r="A87" s="65"/>
-      <c r="B87" s="55"/>
-      <c r="C87" s="76"/>
-      <c r="D87" s="88"/>
-      <c r="E87" s="55"/>
-      <c r="F87" s="55"/>
-      <c r="G87" s="85"/>
-      <c r="H87" s="60"/>
+      <c r="A87" s="58"/>
+      <c r="B87" s="67"/>
+      <c r="C87" s="73"/>
+      <c r="D87" s="66"/>
+      <c r="E87" s="67"/>
+      <c r="F87" s="67"/>
+      <c r="G87" s="79"/>
+      <c r="H87" s="76"/>
       <c r="I87" s="28" t="s">
+        <v>213</v>
+      </c>
+      <c r="J87" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="J87" s="3" t="s">
-        <v>215</v>
-      </c>
     </row>
     <row r="88" spans="1:11" ht="34.799999999999997">
-      <c r="A88" s="65"/>
-      <c r="B88" s="55"/>
-      <c r="C88" s="76"/>
-      <c r="D88" s="88"/>
-      <c r="E88" s="55"/>
-      <c r="F88" s="55"/>
+      <c r="A88" s="58"/>
+      <c r="B88" s="67"/>
+      <c r="C88" s="73"/>
+      <c r="D88" s="66"/>
+      <c r="E88" s="67"/>
+      <c r="F88" s="67"/>
       <c r="G88" s="31" t="s">
         <v>159</v>
       </c>
       <c r="J88" s="4"/>
     </row>
     <row r="89" spans="1:11" ht="34.799999999999997">
-      <c r="A89" s="65"/>
-      <c r="B89" s="55"/>
-      <c r="C89" s="76"/>
-      <c r="D89" s="88"/>
-      <c r="E89" s="55"/>
-      <c r="F89" s="55"/>
+      <c r="A89" s="58"/>
+      <c r="B89" s="67"/>
+      <c r="C89" s="73"/>
+      <c r="D89" s="66"/>
+      <c r="E89" s="67"/>
+      <c r="F89" s="67"/>
       <c r="G89" s="45" t="s">
         <v>169</v>
       </c>
@@ -3392,337 +3392,337 @@
       <c r="J89" s="4"/>
     </row>
     <row r="90" spans="1:11" ht="34.799999999999997">
-      <c r="A90" s="65"/>
-      <c r="B90" s="55"/>
-      <c r="C90" s="76"/>
-      <c r="D90" s="88"/>
-      <c r="E90" s="55"/>
-      <c r="F90" s="54" t="s">
+      <c r="A90" s="58"/>
+      <c r="B90" s="67"/>
+      <c r="C90" s="73"/>
+      <c r="D90" s="66"/>
+      <c r="E90" s="67"/>
+      <c r="F90" s="55" t="s">
         <v>143</v>
       </c>
-      <c r="G90" s="82" t="s">
-        <v>213</v>
-      </c>
-      <c r="H90" s="60" t="s">
+      <c r="G90" s="75" t="s">
+        <v>212</v>
+      </c>
+      <c r="H90" s="76" t="s">
+        <v>192</v>
+      </c>
+      <c r="I90" s="28" t="s">
         <v>193</v>
-      </c>
-      <c r="I90" s="28" t="s">
-        <v>194</v>
       </c>
       <c r="J90" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="91" spans="1:11">
-      <c r="A91" s="65"/>
-      <c r="B91" s="55"/>
-      <c r="C91" s="76"/>
-      <c r="D91" s="88"/>
-      <c r="E91" s="55"/>
-      <c r="F91" s="55"/>
-      <c r="G91" s="82"/>
-      <c r="H91" s="60"/>
+      <c r="A91" s="58"/>
+      <c r="B91" s="67"/>
+      <c r="C91" s="73"/>
+      <c r="D91" s="66"/>
+      <c r="E91" s="67"/>
+      <c r="F91" s="67"/>
+      <c r="G91" s="75"/>
+      <c r="H91" s="76"/>
       <c r="I91" s="28" t="s">
+        <v>194</v>
+      </c>
+      <c r="J91" s="44"/>
+    </row>
+    <row r="92" spans="1:11" ht="34.799999999999997">
+      <c r="A92" s="58"/>
+      <c r="B92" s="67"/>
+      <c r="C92" s="73"/>
+      <c r="D92" s="66"/>
+      <c r="E92" s="67"/>
+      <c r="F92" s="56"/>
+      <c r="G92" s="75"/>
+      <c r="H92" s="76"/>
+      <c r="I92" s="28" t="s">
         <v>195</v>
-      </c>
-      <c r="J91" s="44"/>
-    </row>
-    <row r="92" spans="1:11" ht="34.799999999999997">
-      <c r="A92" s="65"/>
-      <c r="B92" s="55"/>
-      <c r="C92" s="76"/>
-      <c r="D92" s="88"/>
-      <c r="E92" s="55"/>
-      <c r="F92" s="56"/>
-      <c r="G92" s="82"/>
-      <c r="H92" s="60"/>
-      <c r="I92" s="28" t="s">
-        <v>196</v>
       </c>
       <c r="J92" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="93" spans="1:11">
-      <c r="A93" s="65"/>
-      <c r="B93" s="55"/>
-      <c r="C93" s="76"/>
-      <c r="D93" s="88"/>
-      <c r="E93" s="55"/>
-      <c r="F93" s="60"/>
+      <c r="A93" s="58"/>
+      <c r="B93" s="67"/>
+      <c r="C93" s="73"/>
+      <c r="D93" s="66"/>
+      <c r="E93" s="67"/>
+      <c r="F93" s="76"/>
       <c r="G93" s="53" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H93" s="14"/>
       <c r="I93" s="4"/>
       <c r="J93" s="4"/>
     </row>
     <row r="94" spans="1:11">
-      <c r="A94" s="65"/>
-      <c r="B94" s="55"/>
-      <c r="C94" s="76"/>
-      <c r="D94" s="88"/>
-      <c r="E94" s="55"/>
-      <c r="F94" s="60"/>
+      <c r="A94" s="58"/>
+      <c r="B94" s="67"/>
+      <c r="C94" s="73"/>
+      <c r="D94" s="66"/>
+      <c r="E94" s="67"/>
+      <c r="F94" s="76"/>
       <c r="G94" s="53" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H94" s="14"/>
       <c r="I94" s="4"/>
       <c r="J94" s="4"/>
     </row>
     <row r="95" spans="1:11">
-      <c r="A95" s="65"/>
-      <c r="B95" s="55"/>
-      <c r="C95" s="76"/>
-      <c r="D95" s="88"/>
-      <c r="E95" s="55"/>
-      <c r="F95" s="60"/>
+      <c r="A95" s="58"/>
+      <c r="B95" s="67"/>
+      <c r="C95" s="73"/>
+      <c r="D95" s="66"/>
+      <c r="E95" s="67"/>
+      <c r="F95" s="76"/>
       <c r="G95" s="53" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H95" s="14"/>
       <c r="I95" s="4"/>
       <c r="J95" s="4"/>
     </row>
     <row r="96" spans="1:11">
-      <c r="A96" s="65"/>
-      <c r="B96" s="55"/>
-      <c r="C96" s="76"/>
-      <c r="D96" s="88"/>
-      <c r="E96" s="55"/>
-      <c r="F96" s="60"/>
+      <c r="A96" s="58"/>
+      <c r="B96" s="67"/>
+      <c r="C96" s="73"/>
+      <c r="D96" s="66"/>
+      <c r="E96" s="67"/>
+      <c r="F96" s="76"/>
       <c r="G96" s="53" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H96" s="14"/>
       <c r="I96" s="4"/>
       <c r="J96" s="4"/>
     </row>
     <row r="97" spans="1:12">
-      <c r="A97" s="65"/>
-      <c r="B97" s="55"/>
-      <c r="C97" s="76"/>
-      <c r="D97" s="88"/>
-      <c r="E97" s="55"/>
-      <c r="F97" s="60"/>
+      <c r="A97" s="58"/>
+      <c r="B97" s="67"/>
+      <c r="C97" s="73"/>
+      <c r="D97" s="66"/>
+      <c r="E97" s="67"/>
+      <c r="F97" s="76"/>
       <c r="G97" s="53" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H97" s="14"/>
       <c r="I97" s="4"/>
       <c r="J97" s="4"/>
     </row>
     <row r="98" spans="1:12">
-      <c r="A98" s="65"/>
-      <c r="B98" s="55"/>
-      <c r="C98" s="76"/>
-      <c r="D98" s="88"/>
-      <c r="E98" s="55"/>
-      <c r="F98" s="60"/>
+      <c r="A98" s="58"/>
+      <c r="B98" s="67"/>
+      <c r="C98" s="73"/>
+      <c r="D98" s="66"/>
+      <c r="E98" s="67"/>
+      <c r="F98" s="76"/>
       <c r="G98" s="53" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H98" s="14"/>
       <c r="I98" s="4"/>
       <c r="J98" s="4"/>
     </row>
     <row r="99" spans="1:12">
-      <c r="A99" s="65"/>
-      <c r="B99" s="55"/>
-      <c r="C99" s="76"/>
-      <c r="D99" s="88"/>
-      <c r="E99" s="55"/>
-      <c r="F99" s="60"/>
+      <c r="A99" s="58"/>
+      <c r="B99" s="67"/>
+      <c r="C99" s="73"/>
+      <c r="D99" s="66"/>
+      <c r="E99" s="67"/>
+      <c r="F99" s="76"/>
       <c r="G99" s="53" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H99" s="14"/>
       <c r="I99" s="4"/>
       <c r="J99" s="4"/>
     </row>
     <row r="100" spans="1:12">
-      <c r="A100" s="65"/>
-      <c r="B100" s="55"/>
-      <c r="C100" s="76"/>
-      <c r="D100" s="88"/>
-      <c r="E100" s="55"/>
-      <c r="F100" s="60" t="s">
+      <c r="A100" s="58"/>
+      <c r="B100" s="67"/>
+      <c r="C100" s="73"/>
+      <c r="D100" s="66"/>
+      <c r="E100" s="67"/>
+      <c r="F100" s="76" t="s">
         <v>155</v>
       </c>
-      <c r="G100" s="60" t="s">
-        <v>200</v>
+      <c r="G100" s="76" t="s">
+        <v>199</v>
       </c>
       <c r="H100" s="14" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I100" s="4"/>
       <c r="J100" s="4"/>
     </row>
     <row r="101" spans="1:12">
-      <c r="A101" s="65"/>
-      <c r="B101" s="55"/>
+      <c r="A101" s="58"/>
+      <c r="B101" s="67"/>
       <c r="C101" s="38"/>
-      <c r="D101" s="88"/>
-      <c r="E101" s="55"/>
-      <c r="F101" s="60"/>
-      <c r="G101" s="60"/>
+      <c r="D101" s="66"/>
+      <c r="E101" s="67"/>
+      <c r="F101" s="76"/>
+      <c r="G101" s="76"/>
       <c r="H101" s="14" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I101" s="46"/>
       <c r="J101" s="4"/>
     </row>
     <row r="102" spans="1:12">
-      <c r="A102" s="65"/>
-      <c r="B102" s="55"/>
+      <c r="A102" s="58"/>
+      <c r="B102" s="67"/>
       <c r="C102" s="38"/>
-      <c r="D102" s="88"/>
-      <c r="E102" s="55"/>
-      <c r="F102" s="60"/>
-      <c r="G102" s="60"/>
+      <c r="D102" s="66"/>
+      <c r="E102" s="67"/>
+      <c r="F102" s="76"/>
+      <c r="G102" s="76"/>
       <c r="H102" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I102" s="20" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J102" s="4"/>
     </row>
     <row r="103" spans="1:12" ht="87">
-      <c r="A103" s="65"/>
-      <c r="B103" s="55"/>
+      <c r="A103" s="58"/>
+      <c r="B103" s="67"/>
       <c r="C103" s="38"/>
-      <c r="D103" s="88"/>
-      <c r="E103" s="55"/>
-      <c r="F103" s="73" t="s">
-        <v>231</v>
+      <c r="D103" s="66"/>
+      <c r="E103" s="67"/>
+      <c r="F103" s="59" t="s">
+        <v>230</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I103" s="5"/>
       <c r="J103" s="5"/>
       <c r="K103" s="4"/>
     </row>
     <row r="104" spans="1:12" ht="34.799999999999997">
-      <c r="A104" s="65"/>
-      <c r="B104" s="55"/>
+      <c r="A104" s="58"/>
+      <c r="B104" s="67"/>
       <c r="C104" s="38"/>
-      <c r="D104" s="88"/>
-      <c r="E104" s="55"/>
-      <c r="F104" s="74"/>
+      <c r="D104" s="66"/>
+      <c r="E104" s="67"/>
+      <c r="F104" s="60"/>
       <c r="G104" s="43" t="s">
+        <v>221</v>
+      </c>
+      <c r="H104" s="36" t="s">
         <v>222</v>
       </c>
-      <c r="H104" s="36" t="s">
+      <c r="I104" s="4" t="s">
         <v>223</v>
-      </c>
-      <c r="I104" s="4" t="s">
-        <v>224</v>
       </c>
       <c r="J104" s="5"/>
       <c r="K104" s="5"/>
       <c r="L104" s="4"/>
     </row>
     <row r="105" spans="1:12" ht="87">
-      <c r="A105" s="65"/>
-      <c r="B105" s="55"/>
+      <c r="A105" s="58"/>
+      <c r="B105" s="67"/>
       <c r="C105" s="38"/>
-      <c r="D105" s="88"/>
-      <c r="E105" s="55"/>
-      <c r="F105" s="74"/>
-      <c r="G105" s="73" t="s">
-        <v>225</v>
-      </c>
-      <c r="H105" s="70" t="s">
+      <c r="D105" s="66"/>
+      <c r="E105" s="67"/>
+      <c r="F105" s="60"/>
+      <c r="G105" s="59" t="s">
+        <v>224</v>
+      </c>
+      <c r="H105" s="62" t="s">
+        <v>235</v>
+      </c>
+      <c r="I105" s="49" t="s">
         <v>236</v>
       </c>
-      <c r="I105" s="49" t="s">
+      <c r="J105" s="4" t="s">
         <v>237</v>
-      </c>
-      <c r="J105" s="4" t="s">
-        <v>238</v>
       </c>
       <c r="K105" s="5"/>
       <c r="L105" s="4"/>
     </row>
     <row r="106" spans="1:12">
-      <c r="A106" s="65"/>
-      <c r="B106" s="55"/>
+      <c r="A106" s="58"/>
+      <c r="B106" s="67"/>
       <c r="C106" s="38"/>
-      <c r="D106" s="88"/>
-      <c r="E106" s="55"/>
-      <c r="F106" s="74"/>
-      <c r="G106" s="74"/>
-      <c r="H106" s="71"/>
+      <c r="D106" s="66"/>
+      <c r="E106" s="67"/>
+      <c r="F106" s="60"/>
+      <c r="G106" s="60"/>
+      <c r="H106" s="63"/>
       <c r="I106" s="36" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="J106" s="4"/>
       <c r="K106" s="5"/>
       <c r="L106" s="4"/>
     </row>
     <row r="107" spans="1:12">
-      <c r="A107" s="65"/>
-      <c r="B107" s="55"/>
+      <c r="A107" s="58"/>
+      <c r="B107" s="67"/>
       <c r="C107" s="38"/>
-      <c r="D107" s="88"/>
-      <c r="E107" s="55"/>
-      <c r="F107" s="74"/>
-      <c r="G107" s="79"/>
-      <c r="H107" s="72"/>
+      <c r="D107" s="66"/>
+      <c r="E107" s="67"/>
+      <c r="F107" s="60"/>
+      <c r="G107" s="61"/>
+      <c r="H107" s="64"/>
       <c r="I107" s="36" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="J107" s="4"/>
       <c r="K107" s="5"/>
       <c r="L107" s="4"/>
     </row>
     <row r="108" spans="1:12" ht="69.599999999999994">
-      <c r="A108" s="65"/>
-      <c r="B108" s="55"/>
+      <c r="A108" s="58"/>
+      <c r="B108" s="67"/>
       <c r="C108" s="38"/>
-      <c r="D108" s="88"/>
-      <c r="E108" s="55"/>
-      <c r="F108" s="79"/>
+      <c r="D108" s="66"/>
+      <c r="E108" s="67"/>
+      <c r="F108" s="61"/>
       <c r="G108" s="42" t="s">
+        <v>225</v>
+      </c>
+      <c r="H108" s="49" t="s">
+        <v>240</v>
+      </c>
+      <c r="I108" s="4" t="s">
         <v>226</v>
-      </c>
-      <c r="H108" s="49" t="s">
-        <v>241</v>
-      </c>
-      <c r="I108" s="4" t="s">
-        <v>227</v>
       </c>
       <c r="J108" s="5"/>
       <c r="K108" s="5"/>
       <c r="L108" s="4"/>
     </row>
     <row r="109" spans="1:12">
-      <c r="A109" s="65"/>
-      <c r="B109" s="55"/>
-      <c r="C109" s="77" t="s">
+      <c r="A109" s="58"/>
+      <c r="B109" s="67"/>
+      <c r="C109" s="87" t="s">
         <v>165</v>
       </c>
-      <c r="D109" s="54" t="s">
+      <c r="D109" s="55" t="s">
         <v>66</v>
       </c>
       <c r="E109" s="14" t="s">
         <v>187</v>
       </c>
-      <c r="G109" s="78"/>
-      <c r="H109" s="63"/>
-      <c r="I109" s="63" t="s">
+      <c r="G109" s="70"/>
+      <c r="H109" s="54"/>
+      <c r="I109" s="54" t="s">
         <v>181</v>
       </c>
       <c r="K109" s="5"/>
     </row>
     <row r="110" spans="1:12" ht="51.6" customHeight="1">
-      <c r="A110" s="65"/>
-      <c r="B110" s="55"/>
-      <c r="C110" s="77"/>
-      <c r="D110" s="55"/>
+      <c r="A110" s="58"/>
+      <c r="B110" s="67"/>
+      <c r="C110" s="87"/>
+      <c r="D110" s="67"/>
       <c r="E110" s="11" t="s">
         <v>166</v>
       </c>
@@ -3733,43 +3733,43 @@
         <v>167</v>
       </c>
       <c r="H110" s="4"/>
-      <c r="I110" s="63"/>
+      <c r="I110" s="54"/>
       <c r="K110" s="5"/>
     </row>
     <row r="111" spans="1:12" ht="69.599999999999994">
-      <c r="A111" s="65"/>
-      <c r="B111" s="55"/>
-      <c r="C111" s="77"/>
-      <c r="D111" s="55"/>
+      <c r="A111" s="58"/>
+      <c r="B111" s="67"/>
+      <c r="C111" s="87"/>
+      <c r="D111" s="67"/>
       <c r="E111" s="10" t="s">
         <v>83</v>
       </c>
       <c r="F111" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="I111" s="63"/>
+      <c r="I111" s="54"/>
       <c r="J111" s="5"/>
     </row>
     <row r="112" spans="1:12" ht="87">
-      <c r="A112" s="65"/>
-      <c r="B112" s="55"/>
-      <c r="C112" s="77"/>
-      <c r="D112" s="55"/>
+      <c r="A112" s="58"/>
+      <c r="B112" s="67"/>
+      <c r="C112" s="87"/>
+      <c r="D112" s="67"/>
       <c r="E112" s="42" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F112" s="20" t="s">
+        <v>256</v>
+      </c>
+      <c r="G112" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="G112" s="4" t="s">
-        <v>258</v>
-      </c>
       <c r="H112" s="4"/>
-      <c r="I112" s="63"/>
+      <c r="I112" s="54"/>
       <c r="K112" s="5"/>
     </row>
     <row r="113" spans="1:11" ht="34.799999999999997">
-      <c r="A113" s="65"/>
+      <c r="A113" s="58"/>
       <c r="B113" s="56"/>
       <c r="C113" s="37" t="s">
         <v>116</v>
@@ -3786,7 +3786,7 @@
       <c r="K113" s="5"/>
     </row>
     <row r="114" spans="1:11">
-      <c r="A114" s="65"/>
+      <c r="A114" s="58"/>
       <c r="B114" s="40" t="s">
         <v>186</v>
       </c>
@@ -3801,8 +3801,8 @@
       <c r="K114" s="5"/>
     </row>
     <row r="115" spans="1:11" ht="34.799999999999997" customHeight="1">
-      <c r="A115" s="65"/>
-      <c r="B115" s="54" t="s">
+      <c r="A115" s="58"/>
+      <c r="B115" s="55" t="s">
         <v>162</v>
       </c>
       <c r="C115" s="35" t="s">
@@ -3816,7 +3816,7 @@
       <c r="I115" s="5"/>
     </row>
     <row r="116" spans="1:11" ht="34.799999999999997">
-      <c r="A116" s="66"/>
+      <c r="A116" s="84"/>
       <c r="B116" s="56"/>
       <c r="C116" s="10" t="s">
         <v>179</v>
@@ -3831,10 +3831,10 @@
       <c r="I116" s="5"/>
     </row>
     <row r="117" spans="1:11">
-      <c r="A117" s="66"/>
+      <c r="A117" s="84"/>
       <c r="B117" s="56"/>
       <c r="C117" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D117" s="3"/>
       <c r="E117" s="4"/>
@@ -3859,10 +3859,10 @@
       <c r="I118" s="5"/>
     </row>
     <row r="119" spans="1:11">
-      <c r="A119" s="64" t="s">
+      <c r="A119" s="57" t="s">
         <v>148</v>
       </c>
-      <c r="B119" s="64" t="s">
+      <c r="B119" s="57" t="s">
         <v>150</v>
       </c>
       <c r="C119" s="32" t="s">
@@ -3876,8 +3876,8 @@
       <c r="I119" s="5"/>
     </row>
     <row r="120" spans="1:11">
-      <c r="A120" s="65"/>
-      <c r="B120" s="65"/>
+      <c r="A120" s="58"/>
+      <c r="B120" s="58"/>
       <c r="C120" s="33" t="s">
         <v>145</v>
       </c>
@@ -3889,8 +3889,8 @@
       <c r="I120" s="5"/>
     </row>
     <row r="121" spans="1:11">
-      <c r="A121" s="65"/>
-      <c r="B121" s="65"/>
+      <c r="A121" s="58"/>
+      <c r="B121" s="58"/>
       <c r="C121" s="34" t="s">
         <v>146</v>
       </c>
@@ -3902,8 +3902,8 @@
       <c r="I121" s="5"/>
     </row>
     <row r="122" spans="1:11">
-      <c r="A122" s="65"/>
-      <c r="B122" s="65"/>
+      <c r="A122" s="58"/>
+      <c r="B122" s="58"/>
       <c r="C122" s="34" t="s">
         <v>152</v>
       </c>
@@ -3915,8 +3915,8 @@
       <c r="I122" s="5"/>
     </row>
     <row r="123" spans="1:11">
-      <c r="A123" s="65"/>
-      <c r="B123" s="65"/>
+      <c r="A123" s="58"/>
+      <c r="B123" s="58"/>
       <c r="C123" s="34" t="s">
         <v>151</v>
       </c>
@@ -3928,14 +3928,14 @@
       <c r="I123" s="5"/>
     </row>
     <row r="124" spans="1:11">
-      <c r="A124" s="75" t="s">
+      <c r="A124" s="72" t="s">
+        <v>268</v>
+      </c>
+      <c r="B124" s="41" t="s">
         <v>189</v>
       </c>
-      <c r="B124" s="41" t="s">
-        <v>190</v>
-      </c>
-      <c r="C124" s="86" t="s">
-        <v>235</v>
+      <c r="C124" s="80" t="s">
+        <v>234</v>
       </c>
       <c r="D124" s="4"/>
       <c r="E124" s="5"/>
@@ -3945,11 +3945,11 @@
       <c r="I124" s="5"/>
     </row>
     <row r="125" spans="1:11">
-      <c r="A125" s="76"/>
+      <c r="A125" s="73"/>
       <c r="B125" s="50" t="s">
-        <v>203</v>
-      </c>
-      <c r="C125" s="78"/>
+        <v>202</v>
+      </c>
+      <c r="C125" s="70"/>
       <c r="D125" s="4"/>
       <c r="E125" s="5"/>
       <c r="F125" s="5"/>
@@ -3958,11 +3958,11 @@
       <c r="I125" s="5"/>
     </row>
     <row r="126" spans="1:11">
-      <c r="A126" s="76"/>
+      <c r="A126" s="73"/>
       <c r="B126" s="47" t="s">
-        <v>208</v>
-      </c>
-      <c r="C126" s="78"/>
+        <v>207</v>
+      </c>
+      <c r="C126" s="70"/>
       <c r="D126" s="4"/>
       <c r="E126" s="5"/>
       <c r="F126" s="5"/>
@@ -3971,11 +3971,11 @@
       <c r="I126" s="5"/>
     </row>
     <row r="127" spans="1:11">
-      <c r="A127" s="76"/>
+      <c r="A127" s="73"/>
       <c r="B127" s="47" t="s">
-        <v>209</v>
-      </c>
-      <c r="C127" s="78"/>
+        <v>208</v>
+      </c>
+      <c r="C127" s="70"/>
       <c r="D127" s="4"/>
       <c r="E127" s="5"/>
       <c r="F127" s="5"/>
@@ -3984,11 +3984,11 @@
       <c r="I127" s="5"/>
     </row>
     <row r="128" spans="1:11">
-      <c r="A128" s="76"/>
+      <c r="A128" s="73"/>
       <c r="B128" s="47" t="s">
-        <v>210</v>
-      </c>
-      <c r="C128" s="78"/>
+        <v>209</v>
+      </c>
+      <c r="C128" s="70"/>
       <c r="D128" s="4"/>
       <c r="E128" s="5"/>
       <c r="F128" s="5"/>
@@ -3997,11 +3997,11 @@
       <c r="I128" s="5"/>
     </row>
     <row r="129" spans="1:9">
-      <c r="A129" s="81"/>
+      <c r="A129" s="73"/>
       <c r="B129" s="47" t="s">
-        <v>211</v>
-      </c>
-      <c r="C129" s="78"/>
+        <v>210</v>
+      </c>
+      <c r="C129" s="70"/>
       <c r="D129" s="4"/>
       <c r="E129" s="5"/>
       <c r="F129" s="5"/>
@@ -4010,11 +4010,11 @@
       <c r="I129" s="5"/>
     </row>
     <row r="130" spans="1:9">
-      <c r="A130" s="81"/>
+      <c r="A130" s="74"/>
       <c r="B130" s="48" t="s">
-        <v>229</v>
-      </c>
-      <c r="C130" s="78"/>
+        <v>228</v>
+      </c>
+      <c r="C130" s="70"/>
       <c r="D130" s="4"/>
       <c r="E130" s="5"/>
       <c r="F130" s="5"/>
@@ -4023,16 +4023,16 @@
       <c r="I130" s="5"/>
     </row>
     <row r="131" spans="1:9">
-      <c r="A131" s="57" t="s">
+      <c r="A131" s="68" t="s">
         <v>73</v>
       </c>
       <c r="B131" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="C131" s="78" t="s">
+      <c r="C131" s="70" t="s">
         <v>99</v>
       </c>
-      <c r="D131" s="63" t="s">
+      <c r="D131" s="54" t="s">
         <v>98</v>
       </c>
       <c r="E131" s="5"/>
@@ -4041,52 +4041,52 @@
       <c r="H131" s="5"/>
     </row>
     <row r="132" spans="1:9" ht="15" customHeight="1">
-      <c r="A132" s="58"/>
+      <c r="A132" s="69"/>
       <c r="B132" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="C132" s="78"/>
-      <c r="D132" s="63"/>
+      <c r="C132" s="70"/>
+      <c r="D132" s="54"/>
       <c r="E132" s="5"/>
       <c r="F132" s="5"/>
       <c r="G132" s="5"/>
       <c r="H132" s="5"/>
     </row>
     <row r="133" spans="1:9" ht="15" customHeight="1">
-      <c r="A133" s="58"/>
+      <c r="A133" s="69"/>
       <c r="B133" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="C133" s="78"/>
-      <c r="D133" s="63"/>
+      <c r="C133" s="70"/>
+      <c r="D133" s="54"/>
       <c r="E133" s="5"/>
       <c r="F133" s="5"/>
       <c r="G133" s="5"/>
       <c r="H133" s="5"/>
     </row>
     <row r="134" spans="1:9" ht="15" customHeight="1">
-      <c r="A134" s="58"/>
+      <c r="A134" s="69"/>
       <c r="B134" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="C134" s="78"/>
-      <c r="D134" s="63"/>
+      <c r="C134" s="70"/>
+      <c r="D134" s="54"/>
       <c r="E134" s="12"/>
       <c r="F134" s="5"/>
       <c r="G134" s="5"/>
       <c r="H134" s="5"/>
     </row>
     <row r="135" spans="1:9">
-      <c r="A135" s="80" t="s">
+      <c r="A135" s="71" t="s">
         <v>72</v>
       </c>
       <c r="B135" s="14" t="s">
         <v>184</v>
       </c>
-      <c r="C135" s="78" t="s">
+      <c r="C135" s="70" t="s">
         <v>97</v>
       </c>
-      <c r="D135" s="63"/>
+      <c r="D135" s="54"/>
       <c r="E135" s="12"/>
       <c r="F135" s="5"/>
       <c r="G135" s="5"/>
@@ -4094,12 +4094,12 @@
       <c r="I135" s="5"/>
     </row>
     <row r="136" spans="1:9">
-      <c r="A136" s="80"/>
+      <c r="A136" s="71"/>
       <c r="B136" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="C136" s="78"/>
-      <c r="D136" s="63"/>
+      <c r="C136" s="70"/>
+      <c r="D136" s="54"/>
       <c r="E136" s="12"/>
       <c r="F136" s="5"/>
       <c r="G136" s="5"/>
@@ -4107,12 +4107,12 @@
       <c r="I136" s="5"/>
     </row>
     <row r="137" spans="1:9">
-      <c r="A137" s="80"/>
+      <c r="A137" s="71"/>
       <c r="B137" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="C137" s="78"/>
-      <c r="D137" s="63"/>
+      <c r="C137" s="70"/>
+      <c r="D137" s="54"/>
       <c r="E137" s="12"/>
       <c r="F137" s="5"/>
       <c r="G137" s="5"/>
@@ -4120,12 +4120,12 @@
       <c r="I137" s="5"/>
     </row>
     <row r="138" spans="1:9">
-      <c r="A138" s="80"/>
+      <c r="A138" s="71"/>
       <c r="B138" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C138" s="78"/>
-      <c r="D138" s="63"/>
+      <c r="C138" s="70"/>
+      <c r="D138" s="54"/>
       <c r="E138" s="12"/>
       <c r="F138" s="5"/>
       <c r="G138" s="5"/>
@@ -4160,92 +4160,52 @@
     </row>
     <row r="144" spans="1:9">
       <c r="A144" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="145" spans="1:1">
       <c r="A145" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="146" spans="1:1">
       <c r="A146" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="147" spans="1:1">
       <c r="A147" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="148" spans="1:1">
       <c r="A148" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="149" spans="1:1">
       <c r="A149" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="150" spans="1:1">
       <c r="A150" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="151" spans="1:1">
       <c r="A151" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="66">
-    <mergeCell ref="I109:I112"/>
-    <mergeCell ref="B115:B117"/>
-    <mergeCell ref="A119:A123"/>
-    <mergeCell ref="B119:B123"/>
-    <mergeCell ref="G105:G107"/>
-    <mergeCell ref="H105:H107"/>
-    <mergeCell ref="D73:D108"/>
-    <mergeCell ref="E73:E108"/>
-    <mergeCell ref="A131:A134"/>
-    <mergeCell ref="C131:C134"/>
-    <mergeCell ref="D131:D138"/>
-    <mergeCell ref="A135:A138"/>
-    <mergeCell ref="C135:C138"/>
-    <mergeCell ref="A124:A130"/>
-    <mergeCell ref="G109:H109"/>
-    <mergeCell ref="G90:G92"/>
-    <mergeCell ref="H90:H92"/>
-    <mergeCell ref="G82:G87"/>
-    <mergeCell ref="H82:H87"/>
-    <mergeCell ref="C124:C130"/>
-    <mergeCell ref="F103:F108"/>
-    <mergeCell ref="G39:G41"/>
-    <mergeCell ref="B52:B68"/>
-    <mergeCell ref="C52:C68"/>
-    <mergeCell ref="D52:D68"/>
-    <mergeCell ref="E52:E53"/>
-    <mergeCell ref="G52:G53"/>
-    <mergeCell ref="E54:E68"/>
-    <mergeCell ref="G61:H61"/>
-    <mergeCell ref="M12:M13"/>
-    <mergeCell ref="J14:J16"/>
-    <mergeCell ref="J17:J19"/>
-    <mergeCell ref="J20:J22"/>
-    <mergeCell ref="J23:J25"/>
-    <mergeCell ref="J26:J28"/>
-    <mergeCell ref="G8:G10"/>
-    <mergeCell ref="H8:H10"/>
-    <mergeCell ref="K8:K10"/>
-    <mergeCell ref="G11:G37"/>
-    <mergeCell ref="H11:H37"/>
-    <mergeCell ref="I12:I37"/>
-    <mergeCell ref="J12:J13"/>
-    <mergeCell ref="K12:K13"/>
-    <mergeCell ref="J29:J31"/>
-    <mergeCell ref="J32:J34"/>
-    <mergeCell ref="J35:J37"/>
+    <mergeCell ref="J84:J86"/>
+    <mergeCell ref="I84:I86"/>
+    <mergeCell ref="F100:F102"/>
+    <mergeCell ref="G100:G102"/>
+    <mergeCell ref="G76:G78"/>
+    <mergeCell ref="G79:G80"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="D1:F1"/>
     <mergeCell ref="A2:A117"/>
@@ -4260,12 +4220,52 @@
     <mergeCell ref="F75:F89"/>
     <mergeCell ref="C109:C112"/>
     <mergeCell ref="D109:D112"/>
-    <mergeCell ref="J84:J86"/>
-    <mergeCell ref="I84:I86"/>
-    <mergeCell ref="F100:F102"/>
-    <mergeCell ref="G100:G102"/>
-    <mergeCell ref="G76:G78"/>
-    <mergeCell ref="G79:G80"/>
+    <mergeCell ref="J26:J28"/>
+    <mergeCell ref="G8:G10"/>
+    <mergeCell ref="H8:H10"/>
+    <mergeCell ref="K8:K10"/>
+    <mergeCell ref="G11:G37"/>
+    <mergeCell ref="H11:H37"/>
+    <mergeCell ref="I12:I37"/>
+    <mergeCell ref="J12:J13"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="J29:J31"/>
+    <mergeCell ref="J32:J34"/>
+    <mergeCell ref="J35:J37"/>
+    <mergeCell ref="M12:M13"/>
+    <mergeCell ref="J14:J16"/>
+    <mergeCell ref="J17:J19"/>
+    <mergeCell ref="J20:J22"/>
+    <mergeCell ref="J23:J25"/>
+    <mergeCell ref="G39:G41"/>
+    <mergeCell ref="B52:B68"/>
+    <mergeCell ref="C52:C68"/>
+    <mergeCell ref="D52:D68"/>
+    <mergeCell ref="E52:E53"/>
+    <mergeCell ref="G52:G53"/>
+    <mergeCell ref="E54:E68"/>
+    <mergeCell ref="G61:H61"/>
+    <mergeCell ref="G109:H109"/>
+    <mergeCell ref="G90:G92"/>
+    <mergeCell ref="H90:H92"/>
+    <mergeCell ref="G82:G87"/>
+    <mergeCell ref="H82:H87"/>
+    <mergeCell ref="C124:C130"/>
+    <mergeCell ref="F103:F108"/>
+    <mergeCell ref="A124:A130"/>
+    <mergeCell ref="A131:A134"/>
+    <mergeCell ref="C131:C134"/>
+    <mergeCell ref="D131:D138"/>
+    <mergeCell ref="A135:A138"/>
+    <mergeCell ref="C135:C138"/>
+    <mergeCell ref="I109:I112"/>
+    <mergeCell ref="B115:B117"/>
+    <mergeCell ref="A119:A123"/>
+    <mergeCell ref="B119:B123"/>
+    <mergeCell ref="G105:G107"/>
+    <mergeCell ref="H105:H107"/>
+    <mergeCell ref="D73:D108"/>
+    <mergeCell ref="E73:E108"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/ontology/Ontology.xlsx
+++ b/ontology/Ontology.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\home\doc\PLR\dist\schemata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DB8C890-6679-473C-A671-711CF3B3AEAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{882A336B-EFC9-49A0-8B8A-4EAD06066E61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="15576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="277">
   <si>
     <t>string</t>
     <phoneticPr fontId="1"/>
@@ -1056,6 +1056,34 @@
   <si>
     <t>retrieve</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>times</t>
+  </si>
+  <si>
+    <t>equal</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>greaterThan</t>
+  </si>
+  <si>
+    <t>greaterEqual</t>
+  </si>
+  <si>
+    <t>plus</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>divide</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>subsetOf</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>| builtInFunction</t>
   </si>
 </sst>
 </file>
@@ -1639,8 +1667,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFFFF66"/>
       <color rgb="FFFFFFCC"/>
-      <color rgb="FFFFFF66"/>
       <color rgb="FFCCFFFF"/>
       <color rgb="FFFFCCFF"/>
     </mruColors>
@@ -3453,8 +3481,12 @@
       <c r="G93" s="53" t="s">
         <v>259</v>
       </c>
-      <c r="H93" s="14"/>
-      <c r="I93" s="4"/>
+      <c r="H93" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="I93" s="52" t="s">
+        <v>270</v>
+      </c>
       <c r="J93" s="4"/>
     </row>
     <row r="94" spans="1:11">
@@ -3467,8 +3499,12 @@
       <c r="G94" s="53" t="s">
         <v>260</v>
       </c>
-      <c r="H94" s="14"/>
-      <c r="I94" s="4"/>
+      <c r="H94" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="I94" s="52" t="s">
+        <v>272</v>
+      </c>
       <c r="J94" s="4"/>
     </row>
     <row r="95" spans="1:11">
@@ -3481,8 +3517,12 @@
       <c r="G95" s="53" t="s">
         <v>261</v>
       </c>
-      <c r="H95" s="14"/>
-      <c r="I95" s="4"/>
+      <c r="H95" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="I95" s="52" t="s">
+        <v>271</v>
+      </c>
       <c r="J95" s="4"/>
     </row>
     <row r="96" spans="1:11">
@@ -3495,8 +3535,12 @@
       <c r="G96" s="53" t="s">
         <v>262</v>
       </c>
-      <c r="H96" s="14"/>
-      <c r="I96" s="4"/>
+      <c r="H96" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="I96" s="52" t="s">
+        <v>269</v>
+      </c>
       <c r="J96" s="4"/>
     </row>
     <row r="97" spans="1:12">
@@ -3509,8 +3553,12 @@
       <c r="G97" s="53" t="s">
         <v>263</v>
       </c>
-      <c r="H97" s="14"/>
-      <c r="I97" s="4"/>
+      <c r="H97" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="I97" s="52" t="s">
+        <v>273</v>
+      </c>
       <c r="J97" s="4"/>
     </row>
     <row r="98" spans="1:12">
@@ -3523,8 +3571,12 @@
       <c r="G98" s="53" t="s">
         <v>264</v>
       </c>
-      <c r="H98" s="14"/>
-      <c r="I98" s="4"/>
+      <c r="H98" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="I98" s="52" t="s">
+        <v>274</v>
+      </c>
       <c r="J98" s="4"/>
     </row>
     <row r="99" spans="1:12">
@@ -3537,8 +3589,12 @@
       <c r="G99" s="53" t="s">
         <v>265</v>
       </c>
-      <c r="H99" s="14"/>
-      <c r="I99" s="4"/>
+      <c r="H99" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="I99" s="52" t="s">
+        <v>275</v>
+      </c>
       <c r="J99" s="4"/>
     </row>
     <row r="100" spans="1:12">

--- a/ontology/Ontology.xlsx
+++ b/ontology/Ontology.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\home\doc\PLR\dist\schemata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{882A336B-EFC9-49A0-8B8A-4EAD06066E61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEE77467-3BCF-4803-8D62-84D6FBA621E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="15576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="286">
   <si>
     <t>string</t>
     <phoneticPr fontId="1"/>
@@ -655,10 +655,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>compensatesWith=1 ja:補償;compensates with</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Cancelable ja:取消可能タスク;Cancelable Task</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1084,6 +1080,40 @@
   </si>
   <si>
     <t>| builtInFunction</t>
+  </si>
+  <si>
+    <t>compensatesWith(1 ja:補償;compensates with</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>setting=1 ja:設定;setting</t>
+  </si>
+  <si>
+    <t>ONTOc</t>
+  </si>
+  <si>
+    <t>includesCoreBusiness</t>
+  </si>
+  <si>
+    <t>setting=1</t>
+  </si>
+  <si>
+    <t>person=1</t>
+  </si>
+  <si>
+    <t>channelCreator</t>
+  </si>
+  <si>
+    <t>ChannelCreator ja:チャネル作成者;channel creator</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>IncludesCoreBusiness ja:基幹業務を含む;includes core business</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>\チャネル設定が基幹業務のゴール節を含むときに真</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -1164,7 +1194,7 @@
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1223,6 +1253,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFCCFFFF"/>
         <bgColor rgb="FFCCFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCFFCC"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1390,7 +1426,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1595,27 +1631,30 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1631,9 +1670,6 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1657,6 +1693,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1667,10 +1706,11 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFCCFFCC"/>
       <color rgb="FFFFFF66"/>
       <color rgb="FFFFFFCC"/>
+      <color rgb="FFFFCCFF"/>
       <color rgb="FFCCFFFF"/>
-      <color rgb="FFFFCCFF"/>
     </mruColors>
   </colors>
   <extLst>
@@ -1882,7 +1922,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8EA5766-D00D-4E2A-A223-023E0CC1953B}">
-  <dimension ref="A1:M151"/>
+  <dimension ref="A1:M156"/>
   <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="17.399999999999999"/>
   <cols>
     <col min="1" max="1" width="15.296875" style="1" customWidth="1"/>
@@ -1907,7 +1947,7 @@
       <c r="B1" s="83"/>
       <c r="C1" s="83"/>
       <c r="D1" s="54" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E1" s="54"/>
       <c r="F1" s="54"/>
@@ -2020,7 +2060,7 @@
       <c r="D8" s="63"/>
       <c r="E8" s="60"/>
       <c r="F8" s="63"/>
-      <c r="G8" s="68" t="s">
+      <c r="G8" s="73" t="s">
         <v>33</v>
       </c>
       <c r="H8" s="62" t="s">
@@ -2032,7 +2072,7 @@
       <c r="J8" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="K8" s="70" t="s">
+      <c r="K8" s="69" t="s">
         <v>89</v>
       </c>
       <c r="L8" s="4"/>
@@ -2044,7 +2084,7 @@
       <c r="D9" s="63"/>
       <c r="E9" s="60"/>
       <c r="F9" s="63"/>
-      <c r="G9" s="69"/>
+      <c r="G9" s="74"/>
       <c r="H9" s="63"/>
       <c r="I9" s="10" t="s">
         <v>87</v>
@@ -2052,7 +2092,7 @@
       <c r="J9" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="K9" s="70"/>
+      <c r="K9" s="69"/>
       <c r="L9" s="4"/>
     </row>
     <row r="10" spans="1:13">
@@ -2070,7 +2110,7 @@
       <c r="J10" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="K10" s="70"/>
+      <c r="K10" s="69"/>
       <c r="L10" s="4"/>
     </row>
     <row r="11" spans="1:13" ht="15" customHeight="1">
@@ -2101,7 +2141,7 @@
       <c r="F12" s="63"/>
       <c r="G12" s="60"/>
       <c r="H12" s="63"/>
-      <c r="I12" s="76" t="s">
+      <c r="I12" s="77" t="s">
         <v>88</v>
       </c>
       <c r="J12" s="59" t="s">
@@ -2113,7 +2153,7 @@
       <c r="L12" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="M12" s="70" t="s">
+      <c r="M12" s="69" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2126,13 +2166,13 @@
       <c r="F13" s="63"/>
       <c r="G13" s="60"/>
       <c r="H13" s="63"/>
-      <c r="I13" s="76"/>
+      <c r="I13" s="77"/>
       <c r="J13" s="61"/>
       <c r="K13" s="82"/>
       <c r="L13" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="M13" s="70"/>
+      <c r="M13" s="69"/>
     </row>
     <row r="14" spans="1:13" s="17" customFormat="1" ht="15" customHeight="1">
       <c r="A14" s="58"/>
@@ -2143,7 +2183,7 @@
       <c r="F14" s="63"/>
       <c r="G14" s="60"/>
       <c r="H14" s="63"/>
-      <c r="I14" s="76"/>
+      <c r="I14" s="77"/>
       <c r="J14" s="62" t="s">
         <v>27</v>
       </c>
@@ -2163,7 +2203,7 @@
       <c r="F15" s="63"/>
       <c r="G15" s="60"/>
       <c r="H15" s="63"/>
-      <c r="I15" s="76"/>
+      <c r="I15" s="77"/>
       <c r="J15" s="63"/>
       <c r="K15" s="2" t="s">
         <v>11</v>
@@ -2181,7 +2221,7 @@
       <c r="F16" s="63"/>
       <c r="G16" s="60"/>
       <c r="H16" s="63"/>
-      <c r="I16" s="76"/>
+      <c r="I16" s="77"/>
       <c r="J16" s="64"/>
       <c r="K16" s="2" t="s">
         <v>39</v>
@@ -2199,7 +2239,7 @@
       <c r="F17" s="63"/>
       <c r="G17" s="60"/>
       <c r="H17" s="63"/>
-      <c r="I17" s="76"/>
+      <c r="I17" s="77"/>
       <c r="J17" s="62" t="s">
         <v>133</v>
       </c>
@@ -2219,7 +2259,7 @@
       <c r="F18" s="63"/>
       <c r="G18" s="60"/>
       <c r="H18" s="63"/>
-      <c r="I18" s="76"/>
+      <c r="I18" s="77"/>
       <c r="J18" s="63"/>
       <c r="K18" s="2" t="s">
         <v>127</v>
@@ -2237,7 +2277,7 @@
       <c r="F19" s="63"/>
       <c r="G19" s="60"/>
       <c r="H19" s="63"/>
-      <c r="I19" s="76"/>
+      <c r="I19" s="77"/>
       <c r="J19" s="64"/>
       <c r="K19" s="2" t="s">
         <v>128</v>
@@ -2255,7 +2295,7 @@
       <c r="F20" s="63"/>
       <c r="G20" s="60"/>
       <c r="H20" s="63"/>
-      <c r="I20" s="76"/>
+      <c r="I20" s="77"/>
       <c r="J20" s="62" t="s">
         <v>134</v>
       </c>
@@ -2275,7 +2315,7 @@
       <c r="F21" s="63"/>
       <c r="G21" s="60"/>
       <c r="H21" s="63"/>
-      <c r="I21" s="76"/>
+      <c r="I21" s="77"/>
       <c r="J21" s="63"/>
       <c r="K21" s="2" t="s">
         <v>131</v>
@@ -2293,7 +2333,7 @@
       <c r="F22" s="63"/>
       <c r="G22" s="60"/>
       <c r="H22" s="63"/>
-      <c r="I22" s="76"/>
+      <c r="I22" s="77"/>
       <c r="J22" s="64"/>
       <c r="K22" s="2" t="s">
         <v>132</v>
@@ -2311,7 +2351,7 @@
       <c r="F23" s="63"/>
       <c r="G23" s="60"/>
       <c r="H23" s="63"/>
-      <c r="I23" s="76"/>
+      <c r="I23" s="77"/>
       <c r="J23" s="62" t="s">
         <v>28</v>
       </c>
@@ -2331,7 +2371,7 @@
       <c r="F24" s="63"/>
       <c r="G24" s="60"/>
       <c r="H24" s="63"/>
-      <c r="I24" s="76"/>
+      <c r="I24" s="77"/>
       <c r="J24" s="63"/>
       <c r="K24" s="2" t="s">
         <v>13</v>
@@ -2349,7 +2389,7 @@
       <c r="F25" s="63"/>
       <c r="G25" s="60"/>
       <c r="H25" s="63"/>
-      <c r="I25" s="76"/>
+      <c r="I25" s="77"/>
       <c r="J25" s="64"/>
       <c r="K25" s="2" t="s">
         <v>40</v>
@@ -2367,7 +2407,7 @@
       <c r="F26" s="63"/>
       <c r="G26" s="60"/>
       <c r="H26" s="63"/>
-      <c r="I26" s="76"/>
+      <c r="I26" s="77"/>
       <c r="J26" s="62" t="s">
         <v>26</v>
       </c>
@@ -2388,7 +2428,7 @@
       <c r="F27" s="63"/>
       <c r="G27" s="60"/>
       <c r="H27" s="63"/>
-      <c r="I27" s="76"/>
+      <c r="I27" s="77"/>
       <c r="J27" s="63"/>
       <c r="K27" s="2" t="s">
         <v>15</v>
@@ -2407,7 +2447,7 @@
       <c r="F28" s="63"/>
       <c r="G28" s="60"/>
       <c r="H28" s="63"/>
-      <c r="I28" s="76"/>
+      <c r="I28" s="77"/>
       <c r="J28" s="64"/>
       <c r="K28" s="2" t="s">
         <v>41</v>
@@ -2425,7 +2465,7 @@
       <c r="F29" s="63"/>
       <c r="G29" s="60"/>
       <c r="H29" s="63"/>
-      <c r="I29" s="76"/>
+      <c r="I29" s="77"/>
       <c r="J29" s="62" t="s">
         <v>25</v>
       </c>
@@ -2445,7 +2485,7 @@
       <c r="F30" s="63"/>
       <c r="G30" s="60"/>
       <c r="H30" s="63"/>
-      <c r="I30" s="76"/>
+      <c r="I30" s="77"/>
       <c r="J30" s="63"/>
       <c r="K30" s="2" t="s">
         <v>80</v>
@@ -2463,7 +2503,7 @@
       <c r="F31" s="63"/>
       <c r="G31" s="60"/>
       <c r="H31" s="63"/>
-      <c r="I31" s="76"/>
+      <c r="I31" s="77"/>
       <c r="J31" s="64"/>
       <c r="K31" s="2" t="s">
         <v>42</v>
@@ -2481,7 +2521,7 @@
       <c r="F32" s="63"/>
       <c r="G32" s="60"/>
       <c r="H32" s="63"/>
-      <c r="I32" s="76"/>
+      <c r="I32" s="77"/>
       <c r="J32" s="62" t="s">
         <v>29</v>
       </c>
@@ -2501,7 +2541,7 @@
       <c r="F33" s="63"/>
       <c r="G33" s="60"/>
       <c r="H33" s="63"/>
-      <c r="I33" s="76"/>
+      <c r="I33" s="77"/>
       <c r="J33" s="63"/>
       <c r="K33" s="2" t="s">
         <v>76</v>
@@ -2519,7 +2559,7 @@
       <c r="F34" s="63"/>
       <c r="G34" s="60"/>
       <c r="H34" s="63"/>
-      <c r="I34" s="76"/>
+      <c r="I34" s="77"/>
       <c r="J34" s="64"/>
       <c r="K34" s="2" t="s">
         <v>43</v>
@@ -2537,7 +2577,7 @@
       <c r="F35" s="63"/>
       <c r="G35" s="60"/>
       <c r="H35" s="63"/>
-      <c r="I35" s="76"/>
+      <c r="I35" s="77"/>
       <c r="J35" s="62" t="s">
         <v>30</v>
       </c>
@@ -2557,7 +2597,7 @@
       <c r="F36" s="63"/>
       <c r="G36" s="60"/>
       <c r="H36" s="63"/>
-      <c r="I36" s="76"/>
+      <c r="I36" s="77"/>
       <c r="J36" s="63"/>
       <c r="K36" s="2" t="s">
         <v>78</v>
@@ -2575,7 +2615,7 @@
       <c r="F37" s="63"/>
       <c r="G37" s="61"/>
       <c r="H37" s="64"/>
-      <c r="I37" s="76"/>
+      <c r="I37" s="77"/>
       <c r="J37" s="64"/>
       <c r="K37" s="2" t="s">
         <v>44</v>
@@ -2592,7 +2632,7 @@
       <c r="E38" s="60"/>
       <c r="F38" s="63"/>
       <c r="G38" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>38</v>
@@ -2609,11 +2649,11 @@
       <c r="D39" s="63"/>
       <c r="E39" s="60"/>
       <c r="F39" s="63"/>
-      <c r="G39" s="68" t="s">
+      <c r="G39" s="73" t="s">
+        <v>172</v>
+      </c>
+      <c r="H39" s="36" t="s">
         <v>173</v>
-      </c>
-      <c r="H39" s="36" t="s">
-        <v>174</v>
       </c>
       <c r="I39" s="12"/>
       <c r="J39" s="12"/>
@@ -2627,9 +2667,9 @@
       <c r="D40" s="63"/>
       <c r="E40" s="60"/>
       <c r="F40" s="63"/>
-      <c r="G40" s="69"/>
+      <c r="G40" s="74"/>
       <c r="H40" s="36" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I40" s="12"/>
       <c r="J40" s="12"/>
@@ -2645,7 +2685,7 @@
       <c r="F41" s="63"/>
       <c r="G41" s="81"/>
       <c r="H41" s="36" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I41" s="12"/>
       <c r="J41" s="12"/>
@@ -2660,13 +2700,13 @@
       <c r="E42" s="60"/>
       <c r="F42" s="63"/>
       <c r="G42" s="28" t="s">
+        <v>175</v>
+      </c>
+      <c r="H42" s="36" t="s">
+        <v>170</v>
+      </c>
+      <c r="I42" s="4" t="s">
         <v>176</v>
-      </c>
-      <c r="H42" s="36" t="s">
-        <v>171</v>
-      </c>
-      <c r="I42" s="4" t="s">
-        <v>177</v>
       </c>
       <c r="J42" s="5"/>
       <c r="K42" s="5"/>
@@ -2740,7 +2780,7 @@
       <c r="A47" s="58"/>
       <c r="B47" s="82"/>
       <c r="C47" s="28" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D47" s="30" t="s">
         <v>32</v>
@@ -2755,7 +2795,7 @@
       <c r="A48" s="58"/>
       <c r="B48" s="82"/>
       <c r="C48" s="10" t="s">
-        <v>157</v>
+        <v>276</v>
       </c>
       <c r="D48" s="20" t="s">
         <v>20</v>
@@ -2810,7 +2850,7 @@
       <c r="B52" s="55" t="s">
         <v>59</v>
       </c>
-      <c r="C52" s="68" t="s">
+      <c r="C52" s="73" t="s">
         <v>69</v>
       </c>
       <c r="D52" s="55" t="s">
@@ -2822,29 +2862,29 @@
       <c r="F52" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G52" s="70" t="s">
-        <v>182</v>
+      <c r="G52" s="69" t="s">
+        <v>181</v>
       </c>
       <c r="H52" s="5"/>
     </row>
     <row r="53" spans="1:9">
       <c r="A53" s="58"/>
       <c r="B53" s="67"/>
-      <c r="C53" s="69"/>
+      <c r="C53" s="74"/>
       <c r="D53" s="67"/>
       <c r="E53" s="61"/>
       <c r="F53" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G53" s="70"/>
+      <c r="G53" s="69"/>
       <c r="H53" s="5"/>
     </row>
     <row r="54" spans="1:9" ht="34.799999999999997">
       <c r="A54" s="58"/>
       <c r="B54" s="67"/>
-      <c r="C54" s="69"/>
+      <c r="C54" s="74"/>
       <c r="D54" s="67"/>
-      <c r="E54" s="71" t="s">
+      <c r="E54" s="75" t="s">
         <v>60</v>
       </c>
       <c r="F54" s="18" t="s">
@@ -2859,9 +2899,9 @@
     <row r="55" spans="1:9" ht="52.2">
       <c r="A55" s="58"/>
       <c r="B55" s="67"/>
-      <c r="C55" s="69"/>
+      <c r="C55" s="74"/>
       <c r="D55" s="67"/>
-      <c r="E55" s="71"/>
+      <c r="E55" s="75"/>
       <c r="F55" s="16" t="s">
         <v>114</v>
       </c>
@@ -2874,9 +2914,9 @@
     <row r="56" spans="1:9" ht="52.2">
       <c r="A56" s="58"/>
       <c r="B56" s="67"/>
-      <c r="C56" s="69"/>
+      <c r="C56" s="74"/>
       <c r="D56" s="67"/>
-      <c r="E56" s="71"/>
+      <c r="E56" s="75"/>
       <c r="F56" s="16" t="s">
         <v>113</v>
       </c>
@@ -2889,9 +2929,9 @@
     <row r="57" spans="1:9">
       <c r="A57" s="58"/>
       <c r="B57" s="67"/>
-      <c r="C57" s="69"/>
+      <c r="C57" s="74"/>
       <c r="D57" s="67"/>
-      <c r="E57" s="71"/>
+      <c r="E57" s="75"/>
       <c r="F57" s="16" t="s">
         <v>100</v>
       </c>
@@ -2904,9 +2944,9 @@
     <row r="58" spans="1:9">
       <c r="A58" s="58"/>
       <c r="B58" s="67"/>
-      <c r="C58" s="69"/>
+      <c r="C58" s="74"/>
       <c r="D58" s="67"/>
-      <c r="E58" s="71"/>
+      <c r="E58" s="75"/>
       <c r="F58" s="16" t="s">
         <v>101</v>
       </c>
@@ -2919,9 +2959,9 @@
     <row r="59" spans="1:9">
       <c r="A59" s="58"/>
       <c r="B59" s="67"/>
-      <c r="C59" s="69"/>
+      <c r="C59" s="74"/>
       <c r="D59" s="67"/>
-      <c r="E59" s="71"/>
+      <c r="E59" s="75"/>
       <c r="F59" s="16" t="s">
         <v>102</v>
       </c>
@@ -2934,9 +2974,9 @@
     <row r="60" spans="1:9">
       <c r="A60" s="58"/>
       <c r="B60" s="67"/>
-      <c r="C60" s="69"/>
+      <c r="C60" s="74"/>
       <c r="D60" s="67"/>
-      <c r="E60" s="71"/>
+      <c r="E60" s="75"/>
       <c r="F60" s="16" t="s">
         <v>103</v>
       </c>
@@ -2949,13 +2989,13 @@
     <row r="61" spans="1:9">
       <c r="A61" s="58"/>
       <c r="B61" s="67"/>
-      <c r="C61" s="69"/>
+      <c r="C61" s="74"/>
       <c r="D61" s="67"/>
-      <c r="E61" s="71"/>
+      <c r="E61" s="75"/>
       <c r="F61" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="G61" s="70" t="s">
+      <c r="G61" s="69" t="s">
         <v>81</v>
       </c>
       <c r="H61" s="54"/>
@@ -2964,9 +3004,9 @@
     <row r="62" spans="1:9">
       <c r="A62" s="58"/>
       <c r="B62" s="67"/>
-      <c r="C62" s="69"/>
+      <c r="C62" s="74"/>
       <c r="D62" s="67"/>
-      <c r="E62" s="71"/>
+      <c r="E62" s="75"/>
       <c r="F62" s="16" t="s">
         <v>105</v>
       </c>
@@ -2979,9 +3019,9 @@
     <row r="63" spans="1:9">
       <c r="A63" s="58"/>
       <c r="B63" s="67"/>
-      <c r="C63" s="69"/>
+      <c r="C63" s="74"/>
       <c r="D63" s="67"/>
-      <c r="E63" s="71"/>
+      <c r="E63" s="75"/>
       <c r="F63" s="16" t="s">
         <v>106</v>
       </c>
@@ -2994,9 +3034,9 @@
     <row r="64" spans="1:9">
       <c r="A64" s="58"/>
       <c r="B64" s="67"/>
-      <c r="C64" s="69"/>
+      <c r="C64" s="74"/>
       <c r="D64" s="67"/>
-      <c r="E64" s="71"/>
+      <c r="E64" s="75"/>
       <c r="F64" s="16" t="s">
         <v>107</v>
       </c>
@@ -3009,9 +3049,9 @@
     <row r="65" spans="1:12">
       <c r="A65" s="58"/>
       <c r="B65" s="67"/>
-      <c r="C65" s="69"/>
+      <c r="C65" s="74"/>
       <c r="D65" s="67"/>
-      <c r="E65" s="71"/>
+      <c r="E65" s="75"/>
       <c r="F65" s="16" t="s">
         <v>108</v>
       </c>
@@ -3024,9 +3064,9 @@
     <row r="66" spans="1:12">
       <c r="A66" s="58"/>
       <c r="B66" s="67"/>
-      <c r="C66" s="69"/>
+      <c r="C66" s="74"/>
       <c r="D66" s="67"/>
-      <c r="E66" s="71"/>
+      <c r="E66" s="75"/>
       <c r="F66" s="16" t="s">
         <v>109</v>
       </c>
@@ -3039,9 +3079,9 @@
     <row r="67" spans="1:12" ht="69.599999999999994">
       <c r="A67" s="58"/>
       <c r="B67" s="67"/>
-      <c r="C67" s="69"/>
+      <c r="C67" s="74"/>
       <c r="D67" s="67"/>
-      <c r="E67" s="71"/>
+      <c r="E67" s="75"/>
       <c r="F67" s="16" t="s">
         <v>110</v>
       </c>
@@ -3056,7 +3096,7 @@
       <c r="B68" s="56"/>
       <c r="C68" s="81"/>
       <c r="D68" s="56"/>
-      <c r="E68" s="71"/>
+      <c r="E68" s="75"/>
       <c r="F68" s="16" t="s">
         <v>111</v>
       </c>
@@ -3069,16 +3109,16 @@
     <row r="69" spans="1:12" ht="52.2">
       <c r="A69" s="58"/>
       <c r="B69" s="55" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D69" s="20" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F69" s="4"/>
       <c r="G69" s="4"/>
@@ -3146,183 +3186,183 @@
     <row r="73" spans="1:12">
       <c r="A73" s="58"/>
       <c r="B73" s="67"/>
-      <c r="C73" s="72" t="s">
+      <c r="C73" s="70" t="s">
         <v>115</v>
       </c>
       <c r="D73" s="65" t="s">
         <v>156</v>
       </c>
       <c r="E73" s="55" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F73" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="G73" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="G73" s="6" t="s">
-        <v>171</v>
-      </c>
       <c r="H73" s="12" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I73" s="4"/>
     </row>
     <row r="74" spans="1:12" ht="52.2">
       <c r="A74" s="58"/>
       <c r="B74" s="67"/>
-      <c r="C74" s="72"/>
+      <c r="C74" s="70"/>
       <c r="D74" s="66"/>
       <c r="E74" s="67"/>
       <c r="F74" s="13" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G74" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H74" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="I74" s="4"/>
     </row>
     <row r="75" spans="1:12">
       <c r="A75" s="58"/>
       <c r="B75" s="67"/>
-      <c r="C75" s="73"/>
+      <c r="C75" s="71"/>
       <c r="D75" s="66"/>
       <c r="E75" s="67"/>
       <c r="F75" s="55" t="s">
         <v>142</v>
       </c>
       <c r="G75" s="51" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H75" s="23" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="I75" s="4"/>
     </row>
     <row r="76" spans="1:12" ht="69.599999999999994">
       <c r="A76" s="58"/>
       <c r="B76" s="67"/>
-      <c r="C76" s="73"/>
+      <c r="C76" s="71"/>
       <c r="D76" s="66"/>
       <c r="E76" s="67"/>
       <c r="F76" s="55"/>
-      <c r="G76" s="68" t="s">
+      <c r="G76" s="73" t="s">
+        <v>248</v>
+      </c>
+      <c r="H76" s="52" t="s">
         <v>249</v>
       </c>
-      <c r="H76" s="52" t="s">
+      <c r="I76" s="4" t="s">
         <v>250</v>
-      </c>
-      <c r="I76" s="4" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="77" spans="1:12" ht="34.799999999999997">
       <c r="A77" s="58"/>
       <c r="B77" s="67"/>
-      <c r="C77" s="73"/>
+      <c r="C77" s="71"/>
       <c r="D77" s="66"/>
       <c r="E77" s="67"/>
       <c r="F77" s="55"/>
       <c r="G77" s="88"/>
       <c r="H77" s="52" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="I77" s="4"/>
     </row>
     <row r="78" spans="1:12">
       <c r="A78" s="58"/>
       <c r="B78" s="67"/>
-      <c r="C78" s="73"/>
+      <c r="C78" s="71"/>
       <c r="D78" s="66"/>
       <c r="E78" s="67"/>
       <c r="F78" s="55"/>
       <c r="G78" s="88"/>
       <c r="H78" s="52" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="I78" s="4"/>
     </row>
     <row r="79" spans="1:12" ht="87">
       <c r="A79" s="58"/>
       <c r="B79" s="67"/>
-      <c r="C79" s="73"/>
+      <c r="C79" s="71"/>
       <c r="D79" s="66"/>
       <c r="E79" s="67"/>
       <c r="F79" s="67"/>
-      <c r="G79" s="68" t="s">
-        <v>191</v>
+      <c r="G79" s="73" t="s">
+        <v>190</v>
       </c>
       <c r="H79" s="52" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I79" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="80" spans="1:12" ht="139.19999999999999">
       <c r="A80" s="58"/>
       <c r="B80" s="67"/>
-      <c r="C80" s="73"/>
+      <c r="C80" s="71"/>
       <c r="D80" s="66"/>
       <c r="E80" s="67"/>
       <c r="F80" s="67"/>
-      <c r="G80" s="68"/>
+      <c r="G80" s="73"/>
       <c r="H80" s="52" t="s">
+        <v>253</v>
+      </c>
+      <c r="I80" s="4" t="s">
         <v>254</v>
-      </c>
-      <c r="I80" s="4" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="81" spans="1:11" ht="34.799999999999997">
       <c r="A81" s="58"/>
       <c r="B81" s="67"/>
-      <c r="C81" s="73"/>
+      <c r="C81" s="71"/>
       <c r="D81" s="66"/>
       <c r="E81" s="67"/>
       <c r="F81" s="67"/>
       <c r="G81" s="39" t="s">
+        <v>216</v>
+      </c>
+      <c r="H81" s="29" t="s">
         <v>217</v>
       </c>
-      <c r="H81" s="29" t="s">
+      <c r="I81" s="4" t="s">
         <v>218</v>
-      </c>
-      <c r="I81" s="4" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="82" spans="1:11" ht="34.799999999999997" customHeight="1">
       <c r="A82" s="58"/>
       <c r="B82" s="67"/>
-      <c r="C82" s="73"/>
+      <c r="C82" s="71"/>
       <c r="D82" s="66"/>
       <c r="E82" s="67"/>
       <c r="F82" s="67"/>
-      <c r="G82" s="77" t="s">
-        <v>158</v>
-      </c>
-      <c r="H82" s="76" t="s">
-        <v>206</v>
+      <c r="G82" s="78" t="s">
+        <v>157</v>
+      </c>
+      <c r="H82" s="77" t="s">
+        <v>205</v>
       </c>
       <c r="I82" s="28" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J82" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="83" spans="1:11">
       <c r="A83" s="58"/>
       <c r="B83" s="67"/>
-      <c r="C83" s="73"/>
+      <c r="C83" s="71"/>
       <c r="D83" s="66"/>
       <c r="E83" s="67"/>
       <c r="F83" s="67"/>
-      <c r="G83" s="78"/>
-      <c r="H83" s="76"/>
+      <c r="G83" s="79"/>
+      <c r="H83" s="77"/>
       <c r="I83" s="28" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J83" s="3" t="s">
         <v>20</v>
@@ -3331,89 +3371,89 @@
     <row r="84" spans="1:11" ht="33.6" customHeight="1">
       <c r="A84" s="58"/>
       <c r="B84" s="67"/>
-      <c r="C84" s="73"/>
+      <c r="C84" s="71"/>
       <c r="D84" s="66"/>
       <c r="E84" s="67"/>
       <c r="F84" s="67"/>
-      <c r="G84" s="78"/>
-      <c r="H84" s="76"/>
-      <c r="I84" s="68" t="s">
-        <v>211</v>
+      <c r="G84" s="79"/>
+      <c r="H84" s="77"/>
+      <c r="I84" s="73" t="s">
+        <v>210</v>
       </c>
       <c r="J84" s="55" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K84" s="21" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="85" spans="1:11">
       <c r="A85" s="58"/>
       <c r="B85" s="67"/>
-      <c r="C85" s="73"/>
+      <c r="C85" s="71"/>
       <c r="D85" s="66"/>
       <c r="E85" s="67"/>
       <c r="F85" s="67"/>
-      <c r="G85" s="78"/>
-      <c r="H85" s="76"/>
-      <c r="I85" s="69"/>
+      <c r="G85" s="79"/>
+      <c r="H85" s="77"/>
+      <c r="I85" s="74"/>
       <c r="J85" s="67"/>
       <c r="K85" s="21" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="86" spans="1:11">
       <c r="A86" s="58"/>
       <c r="B86" s="67"/>
-      <c r="C86" s="73"/>
+      <c r="C86" s="71"/>
       <c r="D86" s="66"/>
       <c r="E86" s="67"/>
       <c r="F86" s="67"/>
-      <c r="G86" s="78"/>
-      <c r="H86" s="76"/>
+      <c r="G86" s="79"/>
+      <c r="H86" s="77"/>
       <c r="I86" s="81"/>
       <c r="J86" s="56"/>
       <c r="K86" s="21" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="87" spans="1:11" ht="34.799999999999997">
       <c r="A87" s="58"/>
       <c r="B87" s="67"/>
-      <c r="C87" s="73"/>
+      <c r="C87" s="71"/>
       <c r="D87" s="66"/>
       <c r="E87" s="67"/>
       <c r="F87" s="67"/>
-      <c r="G87" s="79"/>
-      <c r="H87" s="76"/>
+      <c r="G87" s="80"/>
+      <c r="H87" s="77"/>
       <c r="I87" s="28" t="s">
+        <v>212</v>
+      </c>
+      <c r="J87" s="3" t="s">
         <v>213</v>
-      </c>
-      <c r="J87" s="3" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="88" spans="1:11" ht="34.799999999999997">
       <c r="A88" s="58"/>
       <c r="B88" s="67"/>
-      <c r="C88" s="73"/>
+      <c r="C88" s="71"/>
       <c r="D88" s="66"/>
       <c r="E88" s="67"/>
       <c r="F88" s="67"/>
       <c r="G88" s="31" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J88" s="4"/>
     </row>
     <row r="89" spans="1:11" ht="34.799999999999997">
       <c r="A89" s="58"/>
       <c r="B89" s="67"/>
-      <c r="C89" s="73"/>
+      <c r="C89" s="71"/>
       <c r="D89" s="66"/>
       <c r="E89" s="67"/>
       <c r="F89" s="67"/>
       <c r="G89" s="45" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H89" s="4"/>
       <c r="I89" s="12"/>
@@ -3422,20 +3462,20 @@
     <row r="90" spans="1:11" ht="34.799999999999997">
       <c r="A90" s="58"/>
       <c r="B90" s="67"/>
-      <c r="C90" s="73"/>
+      <c r="C90" s="71"/>
       <c r="D90" s="66"/>
       <c r="E90" s="67"/>
       <c r="F90" s="55" t="s">
         <v>143</v>
       </c>
-      <c r="G90" s="75" t="s">
-        <v>212</v>
-      </c>
-      <c r="H90" s="76" t="s">
+      <c r="G90" s="76" t="s">
+        <v>211</v>
+      </c>
+      <c r="H90" s="77" t="s">
+        <v>191</v>
+      </c>
+      <c r="I90" s="28" t="s">
         <v>192</v>
-      </c>
-      <c r="I90" s="28" t="s">
-        <v>193</v>
       </c>
       <c r="J90" s="3" t="s">
         <v>8</v>
@@ -3444,28 +3484,28 @@
     <row r="91" spans="1:11">
       <c r="A91" s="58"/>
       <c r="B91" s="67"/>
-      <c r="C91" s="73"/>
+      <c r="C91" s="71"/>
       <c r="D91" s="66"/>
       <c r="E91" s="67"/>
       <c r="F91" s="67"/>
-      <c r="G91" s="75"/>
-      <c r="H91" s="76"/>
+      <c r="G91" s="76"/>
+      <c r="H91" s="77"/>
       <c r="I91" s="28" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="J91" s="44"/>
     </row>
     <row r="92" spans="1:11" ht="34.799999999999997">
       <c r="A92" s="58"/>
       <c r="B92" s="67"/>
-      <c r="C92" s="73"/>
+      <c r="C92" s="71"/>
       <c r="D92" s="66"/>
       <c r="E92" s="67"/>
-      <c r="F92" s="56"/>
-      <c r="G92" s="75"/>
-      <c r="H92" s="76"/>
+      <c r="F92" s="67"/>
+      <c r="G92" s="76"/>
+      <c r="H92" s="77"/>
       <c r="I92" s="28" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J92" s="3" t="s">
         <v>8</v>
@@ -3474,234 +3514,228 @@
     <row r="93" spans="1:11">
       <c r="A93" s="58"/>
       <c r="B93" s="67"/>
-      <c r="C93" s="73"/>
+      <c r="C93" s="71"/>
       <c r="D93" s="66"/>
       <c r="E93" s="67"/>
-      <c r="F93" s="76"/>
+      <c r="F93" s="67"/>
       <c r="G93" s="53" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>276</v>
-      </c>
-      <c r="I93" s="52" t="s">
-        <v>270</v>
+        <v>275</v>
+      </c>
+      <c r="I93" s="89" t="s">
+        <v>269</v>
       </c>
       <c r="J93" s="4"/>
     </row>
     <row r="94" spans="1:11">
       <c r="A94" s="58"/>
       <c r="B94" s="67"/>
-      <c r="C94" s="73"/>
+      <c r="C94" s="71"/>
       <c r="D94" s="66"/>
       <c r="E94" s="67"/>
-      <c r="F94" s="76"/>
+      <c r="F94" s="67"/>
       <c r="G94" s="53" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H94" s="10" t="s">
-        <v>276</v>
-      </c>
-      <c r="I94" s="52" t="s">
-        <v>272</v>
+        <v>275</v>
+      </c>
+      <c r="I94" s="89" t="s">
+        <v>271</v>
       </c>
       <c r="J94" s="4"/>
     </row>
     <row r="95" spans="1:11">
       <c r="A95" s="58"/>
       <c r="B95" s="67"/>
-      <c r="C95" s="73"/>
+      <c r="C95" s="71"/>
       <c r="D95" s="66"/>
       <c r="E95" s="67"/>
-      <c r="F95" s="76"/>
+      <c r="F95" s="67"/>
       <c r="G95" s="53" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>276</v>
-      </c>
-      <c r="I95" s="52" t="s">
-        <v>271</v>
+        <v>275</v>
+      </c>
+      <c r="I95" s="89" t="s">
+        <v>270</v>
       </c>
       <c r="J95" s="4"/>
     </row>
     <row r="96" spans="1:11">
       <c r="A96" s="58"/>
       <c r="B96" s="67"/>
-      <c r="C96" s="73"/>
+      <c r="C96" s="71"/>
       <c r="D96" s="66"/>
       <c r="E96" s="67"/>
-      <c r="F96" s="76"/>
+      <c r="F96" s="67"/>
       <c r="G96" s="53" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H96" s="10" t="s">
-        <v>276</v>
-      </c>
-      <c r="I96" s="52" t="s">
-        <v>269</v>
+        <v>275</v>
+      </c>
+      <c r="I96" s="89" t="s">
+        <v>268</v>
       </c>
       <c r="J96" s="4"/>
     </row>
     <row r="97" spans="1:12">
       <c r="A97" s="58"/>
       <c r="B97" s="67"/>
-      <c r="C97" s="73"/>
+      <c r="C97" s="71"/>
       <c r="D97" s="66"/>
       <c r="E97" s="67"/>
-      <c r="F97" s="76"/>
+      <c r="F97" s="67"/>
       <c r="G97" s="53" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>276</v>
-      </c>
-      <c r="I97" s="52" t="s">
-        <v>273</v>
+        <v>275</v>
+      </c>
+      <c r="I97" s="89" t="s">
+        <v>272</v>
       </c>
       <c r="J97" s="4"/>
     </row>
     <row r="98" spans="1:12">
       <c r="A98" s="58"/>
       <c r="B98" s="67"/>
-      <c r="C98" s="73"/>
+      <c r="C98" s="71"/>
       <c r="D98" s="66"/>
       <c r="E98" s="67"/>
-      <c r="F98" s="76"/>
+      <c r="F98" s="67"/>
       <c r="G98" s="53" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H98" s="10" t="s">
-        <v>276</v>
-      </c>
-      <c r="I98" s="52" t="s">
-        <v>274</v>
+        <v>275</v>
+      </c>
+      <c r="I98" s="89" t="s">
+        <v>273</v>
       </c>
       <c r="J98" s="4"/>
     </row>
     <row r="99" spans="1:12">
       <c r="A99" s="58"/>
       <c r="B99" s="67"/>
-      <c r="C99" s="73"/>
+      <c r="C99" s="71"/>
       <c r="D99" s="66"/>
       <c r="E99" s="67"/>
-      <c r="F99" s="76"/>
+      <c r="F99" s="67"/>
       <c r="G99" s="53" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>276</v>
-      </c>
-      <c r="I99" s="52" t="s">
         <v>275</v>
+      </c>
+      <c r="I99" s="89" t="s">
+        <v>274</v>
       </c>
       <c r="J99" s="4"/>
     </row>
     <row r="100" spans="1:12">
       <c r="A100" s="58"/>
       <c r="B100" s="67"/>
-      <c r="C100" s="73"/>
+      <c r="C100" s="71"/>
       <c r="D100" s="66"/>
       <c r="E100" s="67"/>
-      <c r="F100" s="76" t="s">
-        <v>155</v>
-      </c>
-      <c r="G100" s="76" t="s">
-        <v>199</v>
-      </c>
-      <c r="H100" s="14" t="s">
-        <v>204</v>
-      </c>
-      <c r="I100" s="4"/>
-      <c r="J100" s="4"/>
+      <c r="F100" s="67"/>
+      <c r="G100" s="55" t="s">
+        <v>284</v>
+      </c>
+      <c r="H100" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="I100" s="29" t="s">
+        <v>278</v>
+      </c>
+      <c r="J100" s="69" t="s">
+        <v>285</v>
+      </c>
     </row>
     <row r="101" spans="1:12">
       <c r="A101" s="58"/>
       <c r="B101" s="67"/>
-      <c r="C101" s="38"/>
+      <c r="C101" s="71"/>
       <c r="D101" s="66"/>
       <c r="E101" s="67"/>
-      <c r="F101" s="76"/>
-      <c r="G101" s="76"/>
-      <c r="H101" s="14" t="s">
-        <v>203</v>
-      </c>
-      <c r="I101" s="46"/>
-      <c r="J101" s="4"/>
+      <c r="F101" s="67"/>
+      <c r="G101" s="56"/>
+      <c r="H101" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="I101" s="89" t="s">
+        <v>279</v>
+      </c>
+      <c r="J101" s="69"/>
     </row>
     <row r="102" spans="1:12">
       <c r="A102" s="58"/>
       <c r="B102" s="67"/>
-      <c r="C102" s="38"/>
+      <c r="C102" s="71"/>
       <c r="D102" s="66"/>
       <c r="E102" s="67"/>
-      <c r="F102" s="76"/>
-      <c r="G102" s="76"/>
+      <c r="F102" s="67"/>
+      <c r="G102" s="55" t="s">
+        <v>283</v>
+      </c>
       <c r="H102" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="I102" s="20" t="s">
-        <v>196</v>
-      </c>
+        <v>280</v>
+      </c>
+      <c r="I102" s="4"/>
       <c r="J102" s="4"/>
     </row>
-    <row r="103" spans="1:12" ht="87">
+    <row r="103" spans="1:12">
       <c r="A103" s="58"/>
       <c r="B103" s="67"/>
-      <c r="C103" s="38"/>
+      <c r="C103" s="71"/>
       <c r="D103" s="66"/>
       <c r="E103" s="67"/>
-      <c r="F103" s="59" t="s">
-        <v>230</v>
-      </c>
-      <c r="G103" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="I103" s="5"/>
-      <c r="J103" s="5"/>
-      <c r="K103" s="4"/>
-    </row>
-    <row r="104" spans="1:12" ht="34.799999999999997">
+      <c r="F103" s="67"/>
+      <c r="G103" s="67"/>
+      <c r="H103" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="I103" s="4"/>
+      <c r="J103" s="4"/>
+    </row>
+    <row r="104" spans="1:12">
       <c r="A104" s="58"/>
       <c r="B104" s="67"/>
-      <c r="C104" s="38"/>
+      <c r="C104" s="71"/>
       <c r="D104" s="66"/>
       <c r="E104" s="67"/>
-      <c r="F104" s="60"/>
-      <c r="G104" s="43" t="s">
-        <v>221</v>
-      </c>
-      <c r="H104" s="36" t="s">
-        <v>222</v>
-      </c>
-      <c r="I104" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="J104" s="5"/>
-      <c r="K104" s="5"/>
-      <c r="L104" s="4"/>
-    </row>
-    <row r="105" spans="1:12" ht="87">
+      <c r="F104" s="56"/>
+      <c r="G104" s="56"/>
+      <c r="H104" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="I104" s="89" t="s">
+        <v>282</v>
+      </c>
+      <c r="J104" s="4"/>
+    </row>
+    <row r="105" spans="1:12">
       <c r="A105" s="58"/>
       <c r="B105" s="67"/>
-      <c r="C105" s="38"/>
+      <c r="C105" s="71"/>
       <c r="D105" s="66"/>
       <c r="E105" s="67"/>
-      <c r="F105" s="60"/>
-      <c r="G105" s="59" t="s">
-        <v>224</v>
-      </c>
-      <c r="H105" s="62" t="s">
-        <v>235</v>
-      </c>
-      <c r="I105" s="49" t="s">
-        <v>236</v>
-      </c>
-      <c r="J105" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="K105" s="5"/>
-      <c r="L105" s="4"/>
+      <c r="F105" s="77" t="s">
+        <v>155</v>
+      </c>
+      <c r="G105" s="77" t="s">
+        <v>198</v>
+      </c>
+      <c r="H105" s="14" t="s">
+        <v>203</v>
+      </c>
+      <c r="I105" s="4"/>
+      <c r="J105" s="4"/>
     </row>
     <row r="106" spans="1:12">
       <c r="A106" s="58"/>
@@ -3709,15 +3743,13 @@
       <c r="C106" s="38"/>
       <c r="D106" s="66"/>
       <c r="E106" s="67"/>
-      <c r="F106" s="60"/>
-      <c r="G106" s="60"/>
-      <c r="H106" s="63"/>
-      <c r="I106" s="36" t="s">
-        <v>238</v>
-      </c>
+      <c r="F106" s="77"/>
+      <c r="G106" s="77"/>
+      <c r="H106" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="I106" s="46"/>
       <c r="J106" s="4"/>
-      <c r="K106" s="5"/>
-      <c r="L106" s="4"/>
     </row>
     <row r="107" spans="1:12">
       <c r="A107" s="58"/>
@@ -3725,326 +3757,347 @@
       <c r="C107" s="38"/>
       <c r="D107" s="66"/>
       <c r="E107" s="67"/>
-      <c r="F107" s="60"/>
-      <c r="G107" s="61"/>
-      <c r="H107" s="64"/>
-      <c r="I107" s="36" t="s">
-        <v>239</v>
+      <c r="F107" s="77"/>
+      <c r="G107" s="77"/>
+      <c r="H107" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="I107" s="20" t="s">
+        <v>195</v>
       </c>
       <c r="J107" s="4"/>
-      <c r="K107" s="5"/>
-      <c r="L107" s="4"/>
-    </row>
-    <row r="108" spans="1:12" ht="69.599999999999994">
+    </row>
+    <row r="108" spans="1:12" ht="87">
       <c r="A108" s="58"/>
       <c r="B108" s="67"/>
       <c r="C108" s="38"/>
       <c r="D108" s="66"/>
       <c r="E108" s="67"/>
-      <c r="F108" s="61"/>
-      <c r="G108" s="42" t="s">
-        <v>225</v>
-      </c>
-      <c r="H108" s="49" t="s">
-        <v>240</v>
-      </c>
-      <c r="I108" s="4" t="s">
-        <v>226</v>
-      </c>
+      <c r="F108" s="59" t="s">
+        <v>229</v>
+      </c>
+      <c r="G108" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="I108" s="5"/>
       <c r="J108" s="5"/>
-      <c r="K108" s="5"/>
-      <c r="L108" s="4"/>
-    </row>
-    <row r="109" spans="1:12">
+      <c r="K108" s="4"/>
+    </row>
+    <row r="109" spans="1:12" ht="34.799999999999997">
       <c r="A109" s="58"/>
       <c r="B109" s="67"/>
-      <c r="C109" s="87" t="s">
-        <v>165</v>
-      </c>
-      <c r="D109" s="55" t="s">
-        <v>66</v>
-      </c>
-      <c r="E109" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="G109" s="70"/>
-      <c r="H109" s="54"/>
-      <c r="I109" s="54" t="s">
-        <v>181</v>
-      </c>
+      <c r="C109" s="38"/>
+      <c r="D109" s="66"/>
+      <c r="E109" s="67"/>
+      <c r="F109" s="60"/>
+      <c r="G109" s="43" t="s">
+        <v>220</v>
+      </c>
+      <c r="H109" s="36" t="s">
+        <v>221</v>
+      </c>
+      <c r="I109" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="J109" s="5"/>
       <c r="K109" s="5"/>
-    </row>
-    <row r="110" spans="1:12" ht="51.6" customHeight="1">
+      <c r="L109" s="4"/>
+    </row>
+    <row r="110" spans="1:12" ht="87">
       <c r="A110" s="58"/>
       <c r="B110" s="67"/>
-      <c r="C110" s="87"/>
-      <c r="D110" s="67"/>
-      <c r="E110" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="F110" s="15" t="s">
-        <v>163</v>
-      </c>
-      <c r="G110" s="19" t="s">
-        <v>167</v>
-      </c>
-      <c r="H110" s="4"/>
-      <c r="I110" s="54"/>
+      <c r="C110" s="38"/>
+      <c r="D110" s="66"/>
+      <c r="E110" s="67"/>
+      <c r="F110" s="60"/>
+      <c r="G110" s="59" t="s">
+        <v>223</v>
+      </c>
+      <c r="H110" s="62" t="s">
+        <v>234</v>
+      </c>
+      <c r="I110" s="49" t="s">
+        <v>235</v>
+      </c>
+      <c r="J110" s="4" t="s">
+        <v>236</v>
+      </c>
       <c r="K110" s="5"/>
-    </row>
-    <row r="111" spans="1:12" ht="69.599999999999994">
+      <c r="L110" s="4"/>
+    </row>
+    <row r="111" spans="1:12">
       <c r="A111" s="58"/>
       <c r="B111" s="67"/>
-      <c r="C111" s="87"/>
-      <c r="D111" s="67"/>
-      <c r="E111" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="F111" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="I111" s="54"/>
-      <c r="J111" s="5"/>
-    </row>
-    <row r="112" spans="1:12" ht="87">
+      <c r="C111" s="38"/>
+      <c r="D111" s="66"/>
+      <c r="E111" s="67"/>
+      <c r="F111" s="60"/>
+      <c r="G111" s="60"/>
+      <c r="H111" s="63"/>
+      <c r="I111" s="36" t="s">
+        <v>237</v>
+      </c>
+      <c r="J111" s="4"/>
+      <c r="K111" s="5"/>
+      <c r="L111" s="4"/>
+    </row>
+    <row r="112" spans="1:12">
       <c r="A112" s="58"/>
       <c r="B112" s="67"/>
-      <c r="C112" s="87"/>
-      <c r="D112" s="67"/>
-      <c r="E112" s="42" t="s">
-        <v>266</v>
-      </c>
-      <c r="F112" s="20" t="s">
-        <v>256</v>
-      </c>
-      <c r="G112" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="H112" s="4"/>
-      <c r="I112" s="54"/>
+      <c r="C112" s="38"/>
+      <c r="D112" s="66"/>
+      <c r="E112" s="67"/>
+      <c r="F112" s="60"/>
+      <c r="G112" s="61"/>
+      <c r="H112" s="64"/>
+      <c r="I112" s="36" t="s">
+        <v>238</v>
+      </c>
+      <c r="J112" s="4"/>
       <c r="K112" s="5"/>
-    </row>
-    <row r="113" spans="1:11" ht="34.799999999999997">
+      <c r="L112" s="4"/>
+    </row>
+    <row r="113" spans="1:12" ht="69.599999999999994">
       <c r="A113" s="58"/>
-      <c r="B113" s="56"/>
-      <c r="C113" s="37" t="s">
-        <v>116</v>
-      </c>
-      <c r="D113" s="20" t="s">
-        <v>160</v>
-      </c>
-      <c r="E113" s="4"/>
-      <c r="F113" s="4"/>
-      <c r="G113" s="4"/>
-      <c r="H113" s="5"/>
-      <c r="I113" s="5"/>
+      <c r="B113" s="67"/>
+      <c r="C113" s="38"/>
+      <c r="D113" s="66"/>
+      <c r="E113" s="67"/>
+      <c r="F113" s="61"/>
+      <c r="G113" s="42" t="s">
+        <v>224</v>
+      </c>
+      <c r="H113" s="49" t="s">
+        <v>239</v>
+      </c>
+      <c r="I113" s="4" t="s">
+        <v>225</v>
+      </c>
       <c r="J113" s="5"/>
       <c r="K113" s="5"/>
-    </row>
-    <row r="114" spans="1:11">
+      <c r="L113" s="4"/>
+    </row>
+    <row r="114" spans="1:12">
       <c r="A114" s="58"/>
-      <c r="B114" s="40" t="s">
+      <c r="B114" s="67"/>
+      <c r="C114" s="87" t="s">
+        <v>164</v>
+      </c>
+      <c r="D114" s="55" t="s">
+        <v>66</v>
+      </c>
+      <c r="E114" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="C114" s="4"/>
-      <c r="D114" s="4"/>
-      <c r="E114" s="4"/>
-      <c r="F114" s="4"/>
-      <c r="G114" s="4"/>
-      <c r="H114" s="5"/>
-      <c r="I114" s="5"/>
-      <c r="J114" s="5"/>
+      <c r="G114" s="69"/>
+      <c r="H114" s="54"/>
+      <c r="I114" s="54" t="s">
+        <v>180</v>
+      </c>
       <c r="K114" s="5"/>
     </row>
-    <row r="115" spans="1:11" ht="34.799999999999997" customHeight="1">
+    <row r="115" spans="1:12" ht="51.6" customHeight="1">
       <c r="A115" s="58"/>
-      <c r="B115" s="55" t="s">
+      <c r="B115" s="67"/>
+      <c r="C115" s="87"/>
+      <c r="D115" s="67"/>
+      <c r="E115" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="F115" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="C115" s="35" t="s">
-        <v>168</v>
-      </c>
-      <c r="D115" s="4"/>
-      <c r="E115" s="4"/>
-      <c r="F115" s="4"/>
-      <c r="G115" s="5"/>
-      <c r="H115" s="5"/>
-      <c r="I115" s="5"/>
-    </row>
-    <row r="116" spans="1:11" ht="34.799999999999997">
-      <c r="A116" s="84"/>
-      <c r="B116" s="56"/>
-      <c r="C116" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="D116" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="E116" s="4"/>
-      <c r="F116" s="4"/>
-      <c r="G116" s="5"/>
-      <c r="H116" s="5"/>
-      <c r="I116" s="5"/>
-    </row>
-    <row r="117" spans="1:11">
-      <c r="A117" s="84"/>
-      <c r="B117" s="56"/>
-      <c r="C117" s="10" t="s">
-        <v>227</v>
-      </c>
-      <c r="D117" s="3"/>
-      <c r="E117" s="4"/>
-      <c r="F117" s="4"/>
-      <c r="G117" s="5"/>
-      <c r="H117" s="5"/>
-      <c r="I117" s="5"/>
-    </row>
-    <row r="118" spans="1:11">
-      <c r="A118" s="26" t="s">
-        <v>147</v>
-      </c>
-      <c r="B118" s="20" t="s">
-        <v>149</v>
-      </c>
-      <c r="C118" s="4"/>
-      <c r="D118" s="4"/>
+      <c r="G115" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="H115" s="4"/>
+      <c r="I115" s="54"/>
+      <c r="K115" s="5"/>
+    </row>
+    <row r="116" spans="1:12" ht="69.599999999999994">
+      <c r="A116" s="58"/>
+      <c r="B116" s="67"/>
+      <c r="C116" s="87"/>
+      <c r="D116" s="67"/>
+      <c r="E116" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="F116" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="I116" s="54"/>
+      <c r="J116" s="5"/>
+    </row>
+    <row r="117" spans="1:12" ht="87">
+      <c r="A117" s="58"/>
+      <c r="B117" s="67"/>
+      <c r="C117" s="87"/>
+      <c r="D117" s="67"/>
+      <c r="E117" s="42" t="s">
+        <v>265</v>
+      </c>
+      <c r="F117" s="20" t="s">
+        <v>255</v>
+      </c>
+      <c r="G117" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="H117" s="4"/>
+      <c r="I117" s="54"/>
+      <c r="K117" s="5"/>
+    </row>
+    <row r="118" spans="1:12" ht="34.799999999999997">
+      <c r="A118" s="58"/>
+      <c r="B118" s="56"/>
+      <c r="C118" s="37" t="s">
+        <v>116</v>
+      </c>
+      <c r="D118" s="20" t="s">
+        <v>159</v>
+      </c>
       <c r="E118" s="4"/>
-      <c r="F118" s="5"/>
-      <c r="G118" s="5"/>
+      <c r="F118" s="4"/>
+      <c r="G118" s="4"/>
       <c r="H118" s="5"/>
       <c r="I118" s="5"/>
-    </row>
-    <row r="119" spans="1:11">
-      <c r="A119" s="57" t="s">
-        <v>148</v>
-      </c>
-      <c r="B119" s="57" t="s">
-        <v>150</v>
-      </c>
-      <c r="C119" s="32" t="s">
-        <v>144</v>
-      </c>
+      <c r="J118" s="5"/>
+      <c r="K118" s="5"/>
+    </row>
+    <row r="119" spans="1:12">
+      <c r="A119" s="58"/>
+      <c r="B119" s="40" t="s">
+        <v>185</v>
+      </c>
+      <c r="C119" s="4"/>
       <c r="D119" s="4"/>
       <c r="E119" s="4"/>
-      <c r="F119" s="5"/>
-      <c r="G119" s="5"/>
+      <c r="F119" s="4"/>
+      <c r="G119" s="4"/>
       <c r="H119" s="5"/>
       <c r="I119" s="5"/>
-    </row>
-    <row r="120" spans="1:11">
+      <c r="J119" s="5"/>
+      <c r="K119" s="5"/>
+    </row>
+    <row r="120" spans="1:12" ht="34.799999999999997" customHeight="1">
       <c r="A120" s="58"/>
-      <c r="B120" s="58"/>
-      <c r="C120" s="33" t="s">
-        <v>145</v>
+      <c r="B120" s="55" t="s">
+        <v>161</v>
+      </c>
+      <c r="C120" s="35" t="s">
+        <v>167</v>
       </c>
       <c r="D120" s="4"/>
       <c r="E120" s="4"/>
-      <c r="F120" s="5"/>
+      <c r="F120" s="4"/>
       <c r="G120" s="5"/>
       <c r="H120" s="5"/>
       <c r="I120" s="5"/>
     </row>
-    <row r="121" spans="1:11">
-      <c r="A121" s="58"/>
-      <c r="B121" s="58"/>
-      <c r="C121" s="34" t="s">
-        <v>146</v>
-      </c>
-      <c r="D121" s="4"/>
+    <row r="121" spans="1:12" ht="34.799999999999997">
+      <c r="A121" s="84"/>
+      <c r="B121" s="56"/>
+      <c r="C121" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>160</v>
+      </c>
       <c r="E121" s="4"/>
-      <c r="F121" s="5"/>
+      <c r="F121" s="4"/>
       <c r="G121" s="5"/>
       <c r="H121" s="5"/>
       <c r="I121" s="5"/>
     </row>
-    <row r="122" spans="1:11">
-      <c r="A122" s="58"/>
-      <c r="B122" s="58"/>
-      <c r="C122" s="34" t="s">
-        <v>152</v>
-      </c>
-      <c r="D122" s="4"/>
+    <row r="122" spans="1:12">
+      <c r="A122" s="84"/>
+      <c r="B122" s="56"/>
+      <c r="C122" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="D122" s="3"/>
       <c r="E122" s="4"/>
-      <c r="F122" s="5"/>
+      <c r="F122" s="4"/>
       <c r="G122" s="5"/>
       <c r="H122" s="5"/>
       <c r="I122" s="5"/>
     </row>
-    <row r="123" spans="1:11">
-      <c r="A123" s="58"/>
-      <c r="B123" s="58"/>
-      <c r="C123" s="34" t="s">
-        <v>151</v>
-      </c>
+    <row r="123" spans="1:12">
+      <c r="A123" s="26" t="s">
+        <v>147</v>
+      </c>
+      <c r="B123" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="C123" s="4"/>
       <c r="D123" s="4"/>
-      <c r="E123" s="5"/>
+      <c r="E123" s="4"/>
       <c r="F123" s="5"/>
       <c r="G123" s="5"/>
       <c r="H123" s="5"/>
       <c r="I123" s="5"/>
     </row>
-    <row r="124" spans="1:11">
-      <c r="A124" s="72" t="s">
-        <v>268</v>
-      </c>
-      <c r="B124" s="41" t="s">
-        <v>189</v>
-      </c>
-      <c r="C124" s="80" t="s">
-        <v>234</v>
+    <row r="124" spans="1:12">
+      <c r="A124" s="57" t="s">
+        <v>148</v>
+      </c>
+      <c r="B124" s="57" t="s">
+        <v>150</v>
+      </c>
+      <c r="C124" s="32" t="s">
+        <v>144</v>
       </c>
       <c r="D124" s="4"/>
-      <c r="E124" s="5"/>
+      <c r="E124" s="4"/>
       <c r="F124" s="5"/>
       <c r="G124" s="5"/>
       <c r="H124" s="5"/>
       <c r="I124" s="5"/>
     </row>
-    <row r="125" spans="1:11">
-      <c r="A125" s="73"/>
-      <c r="B125" s="50" t="s">
-        <v>202</v>
-      </c>
-      <c r="C125" s="70"/>
+    <row r="125" spans="1:12">
+      <c r="A125" s="58"/>
+      <c r="B125" s="58"/>
+      <c r="C125" s="33" t="s">
+        <v>145</v>
+      </c>
       <c r="D125" s="4"/>
-      <c r="E125" s="5"/>
+      <c r="E125" s="4"/>
       <c r="F125" s="5"/>
       <c r="G125" s="5"/>
       <c r="H125" s="5"/>
       <c r="I125" s="5"/>
     </row>
-    <row r="126" spans="1:11">
-      <c r="A126" s="73"/>
-      <c r="B126" s="47" t="s">
-        <v>207</v>
-      </c>
-      <c r="C126" s="70"/>
+    <row r="126" spans="1:12">
+      <c r="A126" s="58"/>
+      <c r="B126" s="58"/>
+      <c r="C126" s="34" t="s">
+        <v>146</v>
+      </c>
       <c r="D126" s="4"/>
-      <c r="E126" s="5"/>
+      <c r="E126" s="4"/>
       <c r="F126" s="5"/>
       <c r="G126" s="5"/>
       <c r="H126" s="5"/>
       <c r="I126" s="5"/>
     </row>
-    <row r="127" spans="1:11">
-      <c r="A127" s="73"/>
-      <c r="B127" s="47" t="s">
-        <v>208</v>
-      </c>
-      <c r="C127" s="70"/>
+    <row r="127" spans="1:12">
+      <c r="A127" s="58"/>
+      <c r="B127" s="58"/>
+      <c r="C127" s="34" t="s">
+        <v>152</v>
+      </c>
       <c r="D127" s="4"/>
-      <c r="E127" s="5"/>
+      <c r="E127" s="4"/>
       <c r="F127" s="5"/>
       <c r="G127" s="5"/>
       <c r="H127" s="5"/>
       <c r="I127" s="5"/>
     </row>
-    <row r="128" spans="1:11">
-      <c r="A128" s="73"/>
-      <c r="B128" s="47" t="s">
-        <v>209</v>
-      </c>
-      <c r="C128" s="70"/>
+    <row r="128" spans="1:12">
+      <c r="A128" s="58"/>
+      <c r="B128" s="58"/>
+      <c r="C128" s="34" t="s">
+        <v>151</v>
+      </c>
       <c r="D128" s="4"/>
       <c r="E128" s="5"/>
       <c r="F128" s="5"/>
@@ -4053,11 +4106,15 @@
       <c r="I128" s="5"/>
     </row>
     <row r="129" spans="1:9">
-      <c r="A129" s="73"/>
-      <c r="B129" s="47" t="s">
-        <v>210</v>
-      </c>
-      <c r="C129" s="70"/>
+      <c r="A129" s="70" t="s">
+        <v>267</v>
+      </c>
+      <c r="B129" s="41" t="s">
+        <v>188</v>
+      </c>
+      <c r="C129" s="68" t="s">
+        <v>233</v>
+      </c>
       <c r="D129" s="4"/>
       <c r="E129" s="5"/>
       <c r="F129" s="5"/>
@@ -4066,11 +4123,11 @@
       <c r="I129" s="5"/>
     </row>
     <row r="130" spans="1:9">
-      <c r="A130" s="74"/>
-      <c r="B130" s="48" t="s">
-        <v>228</v>
-      </c>
-      <c r="C130" s="70"/>
+      <c r="A130" s="71"/>
+      <c r="B130" s="50" t="s">
+        <v>201</v>
+      </c>
+      <c r="C130" s="69"/>
       <c r="D130" s="4"/>
       <c r="E130" s="5"/>
       <c r="F130" s="5"/>
@@ -4079,203 +4136,271 @@
       <c r="I130" s="5"/>
     </row>
     <row r="131" spans="1:9">
-      <c r="A131" s="68" t="s">
-        <v>73</v>
-      </c>
-      <c r="B131" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="C131" s="70" t="s">
-        <v>99</v>
-      </c>
-      <c r="D131" s="54" t="s">
-        <v>98</v>
-      </c>
+      <c r="A131" s="71"/>
+      <c r="B131" s="47" t="s">
+        <v>206</v>
+      </c>
+      <c r="C131" s="69"/>
+      <c r="D131" s="4"/>
       <c r="E131" s="5"/>
       <c r="F131" s="5"/>
       <c r="G131" s="5"/>
       <c r="H131" s="5"/>
-    </row>
-    <row r="132" spans="1:9" ht="15" customHeight="1">
-      <c r="A132" s="69"/>
-      <c r="B132" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="C132" s="70"/>
-      <c r="D132" s="54"/>
+      <c r="I131" s="5"/>
+    </row>
+    <row r="132" spans="1:9">
+      <c r="A132" s="71"/>
+      <c r="B132" s="47" t="s">
+        <v>207</v>
+      </c>
+      <c r="C132" s="69"/>
+      <c r="D132" s="4"/>
       <c r="E132" s="5"/>
       <c r="F132" s="5"/>
       <c r="G132" s="5"/>
       <c r="H132" s="5"/>
-    </row>
-    <row r="133" spans="1:9" ht="15" customHeight="1">
-      <c r="A133" s="69"/>
-      <c r="B133" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="C133" s="70"/>
-      <c r="D133" s="54"/>
+      <c r="I132" s="5"/>
+    </row>
+    <row r="133" spans="1:9">
+      <c r="A133" s="71"/>
+      <c r="B133" s="47" t="s">
+        <v>208</v>
+      </c>
+      <c r="C133" s="69"/>
+      <c r="D133" s="4"/>
       <c r="E133" s="5"/>
       <c r="F133" s="5"/>
       <c r="G133" s="5"/>
       <c r="H133" s="5"/>
-    </row>
-    <row r="134" spans="1:9" ht="15" customHeight="1">
-      <c r="A134" s="69"/>
-      <c r="B134" s="22" t="s">
-        <v>96</v>
-      </c>
-      <c r="C134" s="70"/>
-      <c r="D134" s="54"/>
-      <c r="E134" s="12"/>
+      <c r="I133" s="5"/>
+    </row>
+    <row r="134" spans="1:9">
+      <c r="A134" s="71"/>
+      <c r="B134" s="47" t="s">
+        <v>209</v>
+      </c>
+      <c r="C134" s="69"/>
+      <c r="D134" s="4"/>
+      <c r="E134" s="5"/>
       <c r="F134" s="5"/>
       <c r="G134" s="5"/>
       <c r="H134" s="5"/>
+      <c r="I134" s="5"/>
     </row>
     <row r="135" spans="1:9">
-      <c r="A135" s="71" t="s">
-        <v>72</v>
-      </c>
-      <c r="B135" s="14" t="s">
-        <v>184</v>
-      </c>
-      <c r="C135" s="70" t="s">
-        <v>97</v>
-      </c>
-      <c r="D135" s="54"/>
-      <c r="E135" s="12"/>
+      <c r="A135" s="72"/>
+      <c r="B135" s="48" t="s">
+        <v>227</v>
+      </c>
+      <c r="C135" s="69"/>
+      <c r="D135" s="4"/>
+      <c r="E135" s="5"/>
       <c r="F135" s="5"/>
       <c r="G135" s="5"/>
       <c r="H135" s="5"/>
       <c r="I135" s="5"/>
     </row>
     <row r="136" spans="1:9">
-      <c r="A136" s="71"/>
-      <c r="B136" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="C136" s="70"/>
-      <c r="D136" s="54"/>
-      <c r="E136" s="12"/>
+      <c r="A136" s="73" t="s">
+        <v>73</v>
+      </c>
+      <c r="B136" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="C136" s="69" t="s">
+        <v>99</v>
+      </c>
+      <c r="D136" s="54" t="s">
+        <v>98</v>
+      </c>
+      <c r="E136" s="5"/>
       <c r="F136" s="5"/>
       <c r="G136" s="5"/>
       <c r="H136" s="5"/>
-      <c r="I136" s="5"/>
-    </row>
-    <row r="137" spans="1:9">
-      <c r="A137" s="71"/>
-      <c r="B137" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="C137" s="70"/>
+    </row>
+    <row r="137" spans="1:9" ht="15" customHeight="1">
+      <c r="A137" s="74"/>
+      <c r="B137" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="C137" s="69"/>
       <c r="D137" s="54"/>
-      <c r="E137" s="12"/>
+      <c r="E137" s="5"/>
       <c r="F137" s="5"/>
       <c r="G137" s="5"/>
       <c r="H137" s="5"/>
-      <c r="I137" s="5"/>
-    </row>
-    <row r="138" spans="1:9">
-      <c r="A138" s="71"/>
-      <c r="B138" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="C138" s="70"/>
+    </row>
+    <row r="138" spans="1:9" ht="15" customHeight="1">
+      <c r="A138" s="74"/>
+      <c r="B138" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="C138" s="69"/>
       <c r="D138" s="54"/>
-      <c r="E138" s="12"/>
+      <c r="E138" s="5"/>
       <c r="F138" s="5"/>
       <c r="G138" s="5"/>
       <c r="H138" s="5"/>
-      <c r="I138" s="5"/>
-    </row>
-    <row r="139" spans="1:9">
-      <c r="A139" s="1" t="s">
-        <v>22</v>
-      </c>
+    </row>
+    <row r="139" spans="1:9" ht="15" customHeight="1">
+      <c r="A139" s="74"/>
+      <c r="B139" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="C139" s="69"/>
+      <c r="D139" s="54"/>
+      <c r="E139" s="12"/>
+      <c r="F139" s="5"/>
+      <c r="G139" s="5"/>
+      <c r="H139" s="5"/>
     </row>
     <row r="140" spans="1:9">
-      <c r="A140" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="B140" s="5"/>
+      <c r="A140" s="75" t="s">
+        <v>72</v>
+      </c>
+      <c r="B140" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="C140" s="69" t="s">
+        <v>97</v>
+      </c>
+      <c r="D140" s="54"/>
+      <c r="E140" s="12"/>
+      <c r="F140" s="5"/>
+      <c r="G140" s="5"/>
+      <c r="H140" s="5"/>
+      <c r="I140" s="5"/>
     </row>
     <row r="141" spans="1:9">
-      <c r="A141" s="1" t="s">
-        <v>139</v>
-      </c>
+      <c r="A141" s="75"/>
+      <c r="B141" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="C141" s="69"/>
+      <c r="D141" s="54"/>
+      <c r="E141" s="12"/>
+      <c r="F141" s="5"/>
+      <c r="G141" s="5"/>
+      <c r="H141" s="5"/>
+      <c r="I141" s="5"/>
     </row>
     <row r="142" spans="1:9">
-      <c r="A142" s="1" t="s">
-        <v>140</v>
-      </c>
+      <c r="A142" s="75"/>
+      <c r="B142" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="C142" s="69"/>
+      <c r="D142" s="54"/>
+      <c r="E142" s="12"/>
+      <c r="F142" s="5"/>
+      <c r="G142" s="5"/>
+      <c r="H142" s="5"/>
+      <c r="I142" s="5"/>
     </row>
     <row r="143" spans="1:9">
-      <c r="A143" s="1" t="s">
-        <v>141</v>
-      </c>
+      <c r="A143" s="75"/>
+      <c r="B143" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="C143" s="69"/>
+      <c r="D143" s="54"/>
+      <c r="E143" s="12"/>
+      <c r="F143" s="5"/>
+      <c r="G143" s="5"/>
+      <c r="H143" s="5"/>
+      <c r="I143" s="5"/>
     </row>
     <row r="144" spans="1:9">
       <c r="A144" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B145" s="5"/>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150" s="1" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="145" spans="1:1">
-      <c r="A145" s="1" t="s">
+    <row r="151" spans="1:2">
+      <c r="A151" s="1" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="146" spans="1:1">
-      <c r="A146" s="1" t="s">
+    <row r="152" spans="1:2">
+      <c r="A152" s="1" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="147" spans="1:1">
-      <c r="A147" s="1" t="s">
+    <row r="153" spans="1:2">
+      <c r="A153" s="1" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="148" spans="1:1">
-      <c r="A148" s="1" t="s">
+    <row r="154" spans="1:2">
+      <c r="A154" s="1" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="149" spans="1:1">
-      <c r="A149" s="1" t="s">
+    <row r="155" spans="1:2">
+      <c r="A155" s="1" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="150" spans="1:1">
-      <c r="A150" s="1" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="151" spans="1:1">
-      <c r="A151" s="1" t="s">
-        <v>258</v>
+    <row r="156" spans="1:2">
+      <c r="A156" s="1" t="s">
+        <v>257</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="66">
+  <mergeCells count="69">
     <mergeCell ref="J84:J86"/>
     <mergeCell ref="I84:I86"/>
-    <mergeCell ref="F100:F102"/>
-    <mergeCell ref="G100:G102"/>
+    <mergeCell ref="F105:F107"/>
+    <mergeCell ref="G105:G107"/>
     <mergeCell ref="G76:G78"/>
     <mergeCell ref="G79:G80"/>
+    <mergeCell ref="F90:F104"/>
+    <mergeCell ref="G100:G101"/>
+    <mergeCell ref="G102:G104"/>
+    <mergeCell ref="J100:J101"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="D1:F1"/>
-    <mergeCell ref="A2:A117"/>
+    <mergeCell ref="A2:A122"/>
     <mergeCell ref="B6:B48"/>
     <mergeCell ref="C7:C44"/>
     <mergeCell ref="D7:D44"/>
     <mergeCell ref="E7:E42"/>
     <mergeCell ref="F7:F42"/>
-    <mergeCell ref="B69:B113"/>
-    <mergeCell ref="C73:C100"/>
-    <mergeCell ref="F90:F99"/>
+    <mergeCell ref="B69:B118"/>
+    <mergeCell ref="C73:C105"/>
     <mergeCell ref="F75:F89"/>
-    <mergeCell ref="C109:C112"/>
-    <mergeCell ref="D109:D112"/>
+    <mergeCell ref="C114:C117"/>
+    <mergeCell ref="D114:D117"/>
     <mergeCell ref="J26:J28"/>
     <mergeCell ref="G8:G10"/>
     <mergeCell ref="H8:H10"/>
@@ -4301,27 +4426,27 @@
     <mergeCell ref="G52:G53"/>
     <mergeCell ref="E54:E68"/>
     <mergeCell ref="G61:H61"/>
-    <mergeCell ref="G109:H109"/>
+    <mergeCell ref="C129:C135"/>
+    <mergeCell ref="F108:F113"/>
+    <mergeCell ref="A129:A135"/>
+    <mergeCell ref="A136:A139"/>
+    <mergeCell ref="C136:C139"/>
+    <mergeCell ref="D136:D143"/>
+    <mergeCell ref="A140:A143"/>
+    <mergeCell ref="C140:C143"/>
+    <mergeCell ref="I114:I117"/>
+    <mergeCell ref="B120:B122"/>
+    <mergeCell ref="A124:A128"/>
+    <mergeCell ref="B124:B128"/>
+    <mergeCell ref="G110:G112"/>
+    <mergeCell ref="H110:H112"/>
+    <mergeCell ref="D73:D113"/>
+    <mergeCell ref="E73:E113"/>
+    <mergeCell ref="G114:H114"/>
     <mergeCell ref="G90:G92"/>
     <mergeCell ref="H90:H92"/>
     <mergeCell ref="G82:G87"/>
     <mergeCell ref="H82:H87"/>
-    <mergeCell ref="C124:C130"/>
-    <mergeCell ref="F103:F108"/>
-    <mergeCell ref="A124:A130"/>
-    <mergeCell ref="A131:A134"/>
-    <mergeCell ref="C131:C134"/>
-    <mergeCell ref="D131:D138"/>
-    <mergeCell ref="A135:A138"/>
-    <mergeCell ref="C135:C138"/>
-    <mergeCell ref="I109:I112"/>
-    <mergeCell ref="B115:B117"/>
-    <mergeCell ref="A119:A123"/>
-    <mergeCell ref="B119:B123"/>
-    <mergeCell ref="G105:G107"/>
-    <mergeCell ref="H105:H107"/>
-    <mergeCell ref="D73:D108"/>
-    <mergeCell ref="E73:E108"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/ontology/Ontology.xlsx
+++ b/ontology/Ontology.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\home\doc\PLR\dist\schemata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEE77467-3BCF-4803-8D62-84D6FBA621E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EE5581E-A067-4CC3-9BCD-3CABC874DEBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="15576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="285">
   <si>
     <t>string</t>
     <phoneticPr fontId="1"/>
@@ -309,10 +309,6 @@
   </si>
   <si>
     <t>ONTOr ja:限定</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>reuse ja:再利用;reuse||ja:新規作成不可;no creation</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -415,10 +411,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>\値域が重なる他の属性の値を再利用</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>\プロフィールアイテムの再利用も同様?</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -945,10 +937,6 @@
     <t>\refersTo と同じ意味で向きが逆：existing はノードの側に、refersTo はリンクの側に書く。どちらも作らず既にあるものを検索する（追記R549）</t>
   </si>
   <si>
-    <t>\existing と同じ意味で向きが逆：refersTo は別ノードに、existing はノード自身に書く（追記R549）</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>CompletionValue ja:完成の値;Completion Value</t>
   </si>
   <si>
@@ -1113,6 +1101,14 @@
   </si>
   <si>
     <t>\チャネル設定が基幹業務のゴール節を含むときに真</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>\retrievedと同じ意味で向きが逆：retrieveは別ノードに、retrievedはノード自身に書く（追記R549）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>compensatesWith</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1589,113 +1585,113 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1922,7 +1918,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8EA5766-D00D-4E2A-A223-023E0CC1953B}">
-  <dimension ref="A1:M156"/>
+  <dimension ref="A1:M157"/>
   <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="17.399999999999999"/>
   <cols>
     <col min="1" max="1" width="15.296875" style="1" customWidth="1"/>
@@ -1941,26 +1937,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="69" customHeight="1">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="84" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="83"/>
-      <c r="C1" s="83"/>
-      <c r="D1" s="54" t="s">
-        <v>163</v>
-      </c>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
+      <c r="B1" s="84"/>
+      <c r="C1" s="84"/>
+      <c r="D1" s="55" t="s">
+        <v>161</v>
+      </c>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
       <c r="I1" s="5"/>
     </row>
     <row r="2" spans="1:13" ht="34.799999999999997">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="58" t="s">
         <v>19</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>0</v>
@@ -1973,7 +1969,7 @@
       <c r="I2" s="5"/>
     </row>
     <row r="3" spans="1:13" ht="34.799999999999997">
-      <c r="A3" s="58"/>
+      <c r="A3" s="59"/>
       <c r="B3" s="10" t="s">
         <v>16</v>
       </c>
@@ -1988,7 +1984,7 @@
       <c r="I3" s="5"/>
     </row>
     <row r="4" spans="1:13" ht="34.799999999999997">
-      <c r="A4" s="58"/>
+      <c r="A4" s="59"/>
       <c r="B4" s="10" t="s">
         <v>9</v>
       </c>
@@ -2003,7 +1999,7 @@
       <c r="I4" s="5"/>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="58"/>
+      <c r="A5" s="59"/>
       <c r="B5" s="2" t="s">
         <v>31</v>
       </c>
@@ -2016,12 +2012,12 @@
       <c r="I5" s="5"/>
     </row>
     <row r="6" spans="1:13">
-      <c r="A6" s="58"/>
-      <c r="B6" s="82" t="s">
+      <c r="A6" s="59"/>
+      <c r="B6" s="83" t="s">
         <v>36</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>0</v>
@@ -2031,22 +2027,22 @@
       <c r="I6" s="5"/>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1">
-      <c r="A7" s="58"/>
-      <c r="B7" s="82"/>
-      <c r="C7" s="85" t="s">
-        <v>135</v>
-      </c>
-      <c r="D7" s="62" t="s">
+      <c r="A7" s="59"/>
+      <c r="B7" s="83"/>
+      <c r="C7" s="86" t="s">
+        <v>133</v>
+      </c>
+      <c r="D7" s="63" t="s">
+        <v>134</v>
+      </c>
+      <c r="E7" s="60" t="s">
+        <v>151</v>
+      </c>
+      <c r="F7" s="63" t="s">
+        <v>118</v>
+      </c>
+      <c r="G7" s="14" t="s">
         <v>136</v>
-      </c>
-      <c r="E7" s="59" t="s">
-        <v>153</v>
-      </c>
-      <c r="F7" s="62" t="s">
-        <v>120</v>
-      </c>
-      <c r="G7" s="14" t="s">
-        <v>138</v>
       </c>
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
@@ -2054,40 +2050,40 @@
       <c r="K7" s="5"/>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="58"/>
-      <c r="B8" s="82"/>
-      <c r="C8" s="86"/>
-      <c r="D8" s="63"/>
-      <c r="E8" s="60"/>
-      <c r="F8" s="63"/>
-      <c r="G8" s="73" t="s">
+      <c r="A8" s="59"/>
+      <c r="B8" s="83"/>
+      <c r="C8" s="87"/>
+      <c r="D8" s="64"/>
+      <c r="E8" s="61"/>
+      <c r="F8" s="64"/>
+      <c r="G8" s="75" t="s">
         <v>33</v>
       </c>
-      <c r="H8" s="62" t="s">
+      <c r="H8" s="63" t="s">
         <v>34</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J8" s="7" t="s">
         <v>0</v>
       </c>
       <c r="K8" s="69" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L8" s="4"/>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" s="58"/>
-      <c r="B9" s="82"/>
-      <c r="C9" s="86"/>
-      <c r="D9" s="63"/>
-      <c r="E9" s="60"/>
-      <c r="F9" s="63"/>
-      <c r="G9" s="74"/>
-      <c r="H9" s="63"/>
+      <c r="A9" s="59"/>
+      <c r="B9" s="83"/>
+      <c r="C9" s="87"/>
+      <c r="D9" s="64"/>
+      <c r="E9" s="61"/>
+      <c r="F9" s="64"/>
+      <c r="G9" s="76"/>
+      <c r="H9" s="64"/>
       <c r="I9" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J9" s="7" t="s">
         <v>0</v>
@@ -2096,14 +2092,14 @@
       <c r="L9" s="4"/>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="58"/>
-      <c r="B10" s="82"/>
-      <c r="C10" s="86"/>
-      <c r="D10" s="63"/>
-      <c r="E10" s="60"/>
-      <c r="F10" s="63"/>
-      <c r="G10" s="81"/>
-      <c r="H10" s="64"/>
+      <c r="A10" s="59"/>
+      <c r="B10" s="83"/>
+      <c r="C10" s="87"/>
+      <c r="D10" s="64"/>
+      <c r="E10" s="61"/>
+      <c r="F10" s="64"/>
+      <c r="G10" s="77"/>
+      <c r="H10" s="65"/>
       <c r="I10" s="10" t="s">
         <v>35</v>
       </c>
@@ -2114,16 +2110,16 @@
       <c r="L10" s="4"/>
     </row>
     <row r="11" spans="1:13" ht="15" customHeight="1">
-      <c r="A11" s="58"/>
-      <c r="B11" s="82"/>
-      <c r="C11" s="86"/>
-      <c r="D11" s="63"/>
-      <c r="E11" s="60"/>
-      <c r="F11" s="63"/>
-      <c r="G11" s="59" t="s">
+      <c r="A11" s="59"/>
+      <c r="B11" s="83"/>
+      <c r="C11" s="87"/>
+      <c r="D11" s="64"/>
+      <c r="E11" s="61"/>
+      <c r="F11" s="64"/>
+      <c r="G11" s="60" t="s">
         <v>67</v>
       </c>
-      <c r="H11" s="62" t="s">
+      <c r="H11" s="63" t="s">
         <v>21</v>
       </c>
       <c r="I11" s="15" t="s">
@@ -2133,58 +2129,58 @@
       <c r="K11" s="5"/>
     </row>
     <row r="12" spans="1:13">
-      <c r="A12" s="58"/>
-      <c r="B12" s="82"/>
-      <c r="C12" s="86"/>
-      <c r="D12" s="63"/>
-      <c r="E12" s="60"/>
-      <c r="F12" s="63"/>
-      <c r="G12" s="60"/>
-      <c r="H12" s="63"/>
-      <c r="I12" s="77" t="s">
-        <v>88</v>
-      </c>
-      <c r="J12" s="59" t="s">
-        <v>121</v>
-      </c>
-      <c r="K12" s="82" t="s">
+      <c r="A12" s="59"/>
+      <c r="B12" s="83"/>
+      <c r="C12" s="87"/>
+      <c r="D12" s="64"/>
+      <c r="E12" s="61"/>
+      <c r="F12" s="64"/>
+      <c r="G12" s="61"/>
+      <c r="H12" s="64"/>
+      <c r="I12" s="71" t="s">
+        <v>87</v>
+      </c>
+      <c r="J12" s="60" t="s">
+        <v>119</v>
+      </c>
+      <c r="K12" s="83" t="s">
+        <v>91</v>
+      </c>
+      <c r="L12" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="M12" s="69" t="s">
         <v>92</v>
       </c>
-      <c r="L12" s="14" t="s">
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="59"/>
+      <c r="B13" s="83"/>
+      <c r="C13" s="87"/>
+      <c r="D13" s="64"/>
+      <c r="E13" s="61"/>
+      <c r="F13" s="64"/>
+      <c r="G13" s="61"/>
+      <c r="H13" s="64"/>
+      <c r="I13" s="71"/>
+      <c r="J13" s="62"/>
+      <c r="K13" s="83"/>
+      <c r="L13" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="M12" s="69" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13" s="58"/>
-      <c r="B13" s="82"/>
-      <c r="C13" s="86"/>
-      <c r="D13" s="63"/>
-      <c r="E13" s="60"/>
-      <c r="F13" s="63"/>
-      <c r="G13" s="60"/>
-      <c r="H13" s="63"/>
-      <c r="I13" s="77"/>
-      <c r="J13" s="61"/>
-      <c r="K13" s="82"/>
-      <c r="L13" s="14" t="s">
-        <v>91</v>
-      </c>
       <c r="M13" s="69"/>
     </row>
     <row r="14" spans="1:13" s="17" customFormat="1" ht="15" customHeight="1">
-      <c r="A14" s="58"/>
-      <c r="B14" s="82"/>
-      <c r="C14" s="86"/>
-      <c r="D14" s="63"/>
-      <c r="E14" s="60"/>
-      <c r="F14" s="63"/>
-      <c r="G14" s="60"/>
-      <c r="H14" s="63"/>
-      <c r="I14" s="77"/>
-      <c r="J14" s="62" t="s">
+      <c r="A14" s="59"/>
+      <c r="B14" s="83"/>
+      <c r="C14" s="87"/>
+      <c r="D14" s="64"/>
+      <c r="E14" s="61"/>
+      <c r="F14" s="64"/>
+      <c r="G14" s="61"/>
+      <c r="H14" s="64"/>
+      <c r="I14" s="71"/>
+      <c r="J14" s="63" t="s">
         <v>27</v>
       </c>
       <c r="K14" s="2" t="s">
@@ -2195,16 +2191,16 @@
       </c>
     </row>
     <row r="15" spans="1:13" s="17" customFormat="1" ht="15" customHeight="1">
-      <c r="A15" s="58"/>
-      <c r="B15" s="82"/>
-      <c r="C15" s="86"/>
-      <c r="D15" s="63"/>
-      <c r="E15" s="60"/>
-      <c r="F15" s="63"/>
-      <c r="G15" s="60"/>
-      <c r="H15" s="63"/>
-      <c r="I15" s="77"/>
-      <c r="J15" s="63"/>
+      <c r="A15" s="59"/>
+      <c r="B15" s="83"/>
+      <c r="C15" s="87"/>
+      <c r="D15" s="64"/>
+      <c r="E15" s="61"/>
+      <c r="F15" s="64"/>
+      <c r="G15" s="61"/>
+      <c r="H15" s="64"/>
+      <c r="I15" s="71"/>
+      <c r="J15" s="64"/>
       <c r="K15" s="2" t="s">
         <v>11</v>
       </c>
@@ -2213,16 +2209,16 @@
       </c>
     </row>
     <row r="16" spans="1:13" s="17" customFormat="1" ht="34.799999999999997">
-      <c r="A16" s="58"/>
-      <c r="B16" s="82"/>
-      <c r="C16" s="86"/>
-      <c r="D16" s="63"/>
-      <c r="E16" s="60"/>
-      <c r="F16" s="63"/>
-      <c r="G16" s="60"/>
-      <c r="H16" s="63"/>
-      <c r="I16" s="77"/>
-      <c r="J16" s="64"/>
+      <c r="A16" s="59"/>
+      <c r="B16" s="83"/>
+      <c r="C16" s="87"/>
+      <c r="D16" s="64"/>
+      <c r="E16" s="61"/>
+      <c r="F16" s="64"/>
+      <c r="G16" s="61"/>
+      <c r="H16" s="64"/>
+      <c r="I16" s="71"/>
+      <c r="J16" s="65"/>
       <c r="K16" s="2" t="s">
         <v>39</v>
       </c>
@@ -2231,128 +2227,128 @@
       </c>
     </row>
     <row r="17" spans="1:13" s="17" customFormat="1">
-      <c r="A17" s="58"/>
-      <c r="B17" s="82"/>
-      <c r="C17" s="86"/>
-      <c r="D17" s="63"/>
-      <c r="E17" s="60"/>
-      <c r="F17" s="63"/>
-      <c r="G17" s="60"/>
-      <c r="H17" s="63"/>
-      <c r="I17" s="77"/>
-      <c r="J17" s="62" t="s">
-        <v>133</v>
+      <c r="A17" s="59"/>
+      <c r="B17" s="83"/>
+      <c r="C17" s="87"/>
+      <c r="D17" s="64"/>
+      <c r="E17" s="61"/>
+      <c r="F17" s="64"/>
+      <c r="G17" s="61"/>
+      <c r="H17" s="64"/>
+      <c r="I17" s="71"/>
+      <c r="J17" s="63" t="s">
+        <v>131</v>
       </c>
       <c r="K17" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" s="17" customFormat="1">
+      <c r="A18" s="59"/>
+      <c r="B18" s="83"/>
+      <c r="C18" s="87"/>
+      <c r="D18" s="64"/>
+      <c r="E18" s="61"/>
+      <c r="F18" s="64"/>
+      <c r="G18" s="61"/>
+      <c r="H18" s="64"/>
+      <c r="I18" s="71"/>
+      <c r="J18" s="64"/>
+      <c r="K18" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" s="17" customFormat="1" ht="34.799999999999997">
+      <c r="A19" s="59"/>
+      <c r="B19" s="83"/>
+      <c r="C19" s="87"/>
+      <c r="D19" s="64"/>
+      <c r="E19" s="61"/>
+      <c r="F19" s="64"/>
+      <c r="G19" s="61"/>
+      <c r="H19" s="64"/>
+      <c r="I19" s="71"/>
+      <c r="J19" s="65"/>
+      <c r="K19" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="L17" s="16" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" s="17" customFormat="1">
-      <c r="A18" s="58"/>
-      <c r="B18" s="82"/>
-      <c r="C18" s="86"/>
-      <c r="D18" s="63"/>
-      <c r="E18" s="60"/>
-      <c r="F18" s="63"/>
-      <c r="G18" s="60"/>
-      <c r="H18" s="63"/>
-      <c r="I18" s="77"/>
-      <c r="J18" s="63"/>
-      <c r="K18" s="2" t="s">
+      <c r="L19" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="L18" s="16" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" s="17" customFormat="1" ht="34.799999999999997">
-      <c r="A19" s="58"/>
-      <c r="B19" s="82"/>
-      <c r="C19" s="86"/>
-      <c r="D19" s="63"/>
-      <c r="E19" s="60"/>
-      <c r="F19" s="63"/>
-      <c r="G19" s="60"/>
-      <c r="H19" s="63"/>
-      <c r="I19" s="77"/>
-      <c r="J19" s="64"/>
-      <c r="K19" s="2" t="s">
+    </row>
+    <row r="20" spans="1:13" s="17" customFormat="1">
+      <c r="A20" s="59"/>
+      <c r="B20" s="83"/>
+      <c r="C20" s="87"/>
+      <c r="D20" s="64"/>
+      <c r="E20" s="61"/>
+      <c r="F20" s="64"/>
+      <c r="G20" s="61"/>
+      <c r="H20" s="64"/>
+      <c r="I20" s="71"/>
+      <c r="J20" s="63" t="s">
+        <v>132</v>
+      </c>
+      <c r="K20" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="L19" s="16" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" s="17" customFormat="1">
-      <c r="A20" s="58"/>
-      <c r="B20" s="82"/>
-      <c r="C20" s="86"/>
-      <c r="D20" s="63"/>
-      <c r="E20" s="60"/>
-      <c r="F20" s="63"/>
-      <c r="G20" s="60"/>
-      <c r="H20" s="63"/>
-      <c r="I20" s="77"/>
-      <c r="J20" s="62" t="s">
-        <v>134</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>130</v>
       </c>
       <c r="L20" s="16" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:13" s="17" customFormat="1">
-      <c r="A21" s="58"/>
-      <c r="B21" s="82"/>
-      <c r="C21" s="86"/>
-      <c r="D21" s="63"/>
-      <c r="E21" s="60"/>
-      <c r="F21" s="63"/>
-      <c r="G21" s="60"/>
-      <c r="H21" s="63"/>
-      <c r="I21" s="77"/>
-      <c r="J21" s="63"/>
+      <c r="A21" s="59"/>
+      <c r="B21" s="83"/>
+      <c r="C21" s="87"/>
+      <c r="D21" s="64"/>
+      <c r="E21" s="61"/>
+      <c r="F21" s="64"/>
+      <c r="G21" s="61"/>
+      <c r="H21" s="64"/>
+      <c r="I21" s="71"/>
+      <c r="J21" s="64"/>
       <c r="K21" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="L21" s="16" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:13" s="17" customFormat="1" ht="34.799999999999997">
-      <c r="A22" s="58"/>
-      <c r="B22" s="82"/>
-      <c r="C22" s="86"/>
-      <c r="D22" s="63"/>
-      <c r="E22" s="60"/>
-      <c r="F22" s="63"/>
-      <c r="G22" s="60"/>
-      <c r="H22" s="63"/>
-      <c r="I22" s="77"/>
-      <c r="J22" s="64"/>
+      <c r="A22" s="59"/>
+      <c r="B22" s="83"/>
+      <c r="C22" s="87"/>
+      <c r="D22" s="64"/>
+      <c r="E22" s="61"/>
+      <c r="F22" s="64"/>
+      <c r="G22" s="61"/>
+      <c r="H22" s="64"/>
+      <c r="I22" s="71"/>
+      <c r="J22" s="65"/>
       <c r="K22" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="L22" s="16" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:13" s="17" customFormat="1" ht="15" customHeight="1">
-      <c r="A23" s="58"/>
-      <c r="B23" s="82"/>
-      <c r="C23" s="86"/>
-      <c r="D23" s="63"/>
-      <c r="E23" s="60"/>
-      <c r="F23" s="63"/>
-      <c r="G23" s="60"/>
-      <c r="H23" s="63"/>
-      <c r="I23" s="77"/>
-      <c r="J23" s="62" t="s">
+      <c r="A23" s="59"/>
+      <c r="B23" s="83"/>
+      <c r="C23" s="87"/>
+      <c r="D23" s="64"/>
+      <c r="E23" s="61"/>
+      <c r="F23" s="64"/>
+      <c r="G23" s="61"/>
+      <c r="H23" s="64"/>
+      <c r="I23" s="71"/>
+      <c r="J23" s="63" t="s">
         <v>28</v>
       </c>
       <c r="K23" s="2" t="s">
@@ -2363,16 +2359,16 @@
       </c>
     </row>
     <row r="24" spans="1:13" s="17" customFormat="1" ht="15" customHeight="1">
-      <c r="A24" s="58"/>
-      <c r="B24" s="82"/>
-      <c r="C24" s="86"/>
-      <c r="D24" s="63"/>
-      <c r="E24" s="60"/>
-      <c r="F24" s="63"/>
-      <c r="G24" s="60"/>
-      <c r="H24" s="63"/>
-      <c r="I24" s="77"/>
-      <c r="J24" s="63"/>
+      <c r="A24" s="59"/>
+      <c r="B24" s="83"/>
+      <c r="C24" s="87"/>
+      <c r="D24" s="64"/>
+      <c r="E24" s="61"/>
+      <c r="F24" s="64"/>
+      <c r="G24" s="61"/>
+      <c r="H24" s="64"/>
+      <c r="I24" s="71"/>
+      <c r="J24" s="64"/>
       <c r="K24" s="2" t="s">
         <v>13</v>
       </c>
@@ -2381,16 +2377,16 @@
       </c>
     </row>
     <row r="25" spans="1:13" s="17" customFormat="1" ht="34.799999999999997">
-      <c r="A25" s="58"/>
-      <c r="B25" s="82"/>
-      <c r="C25" s="86"/>
-      <c r="D25" s="63"/>
-      <c r="E25" s="60"/>
-      <c r="F25" s="63"/>
-      <c r="G25" s="60"/>
-      <c r="H25" s="63"/>
-      <c r="I25" s="77"/>
-      <c r="J25" s="64"/>
+      <c r="A25" s="59"/>
+      <c r="B25" s="83"/>
+      <c r="C25" s="87"/>
+      <c r="D25" s="64"/>
+      <c r="E25" s="61"/>
+      <c r="F25" s="64"/>
+      <c r="G25" s="61"/>
+      <c r="H25" s="64"/>
+      <c r="I25" s="71"/>
+      <c r="J25" s="65"/>
       <c r="K25" s="2" t="s">
         <v>40</v>
       </c>
@@ -2399,16 +2395,16 @@
       </c>
     </row>
     <row r="26" spans="1:13" s="17" customFormat="1">
-      <c r="A26" s="58"/>
-      <c r="B26" s="82"/>
-      <c r="C26" s="86"/>
-      <c r="D26" s="63"/>
-      <c r="E26" s="60"/>
-      <c r="F26" s="63"/>
-      <c r="G26" s="60"/>
-      <c r="H26" s="63"/>
-      <c r="I26" s="77"/>
-      <c r="J26" s="62" t="s">
+      <c r="A26" s="59"/>
+      <c r="B26" s="83"/>
+      <c r="C26" s="87"/>
+      <c r="D26" s="64"/>
+      <c r="E26" s="61"/>
+      <c r="F26" s="64"/>
+      <c r="G26" s="61"/>
+      <c r="H26" s="64"/>
+      <c r="I26" s="71"/>
+      <c r="J26" s="63" t="s">
         <v>26</v>
       </c>
       <c r="K26" s="2" t="s">
@@ -2420,16 +2416,16 @@
       <c r="M26" s="1"/>
     </row>
     <row r="27" spans="1:13" s="17" customFormat="1">
-      <c r="A27" s="58"/>
-      <c r="B27" s="82"/>
-      <c r="C27" s="86"/>
-      <c r="D27" s="63"/>
-      <c r="E27" s="60"/>
-      <c r="F27" s="63"/>
-      <c r="G27" s="60"/>
-      <c r="H27" s="63"/>
-      <c r="I27" s="77"/>
-      <c r="J27" s="63"/>
+      <c r="A27" s="59"/>
+      <c r="B27" s="83"/>
+      <c r="C27" s="87"/>
+      <c r="D27" s="64"/>
+      <c r="E27" s="61"/>
+      <c r="F27" s="64"/>
+      <c r="G27" s="61"/>
+      <c r="H27" s="64"/>
+      <c r="I27" s="71"/>
+      <c r="J27" s="64"/>
       <c r="K27" s="2" t="s">
         <v>15</v>
       </c>
@@ -2439,16 +2435,16 @@
       <c r="M27" s="1"/>
     </row>
     <row r="28" spans="1:13" ht="34.799999999999997">
-      <c r="A28" s="58"/>
-      <c r="B28" s="82"/>
-      <c r="C28" s="86"/>
-      <c r="D28" s="63"/>
-      <c r="E28" s="60"/>
-      <c r="F28" s="63"/>
-      <c r="G28" s="60"/>
-      <c r="H28" s="63"/>
-      <c r="I28" s="77"/>
-      <c r="J28" s="64"/>
+      <c r="A28" s="59"/>
+      <c r="B28" s="83"/>
+      <c r="C28" s="87"/>
+      <c r="D28" s="64"/>
+      <c r="E28" s="61"/>
+      <c r="F28" s="64"/>
+      <c r="G28" s="61"/>
+      <c r="H28" s="64"/>
+      <c r="I28" s="71"/>
+      <c r="J28" s="65"/>
       <c r="K28" s="2" t="s">
         <v>41</v>
       </c>
@@ -2457,54 +2453,54 @@
       </c>
     </row>
     <row r="29" spans="1:13">
-      <c r="A29" s="58"/>
-      <c r="B29" s="82"/>
-      <c r="C29" s="86"/>
-      <c r="D29" s="63"/>
-      <c r="E29" s="60"/>
-      <c r="F29" s="63"/>
-      <c r="G29" s="60"/>
-      <c r="H29" s="63"/>
-      <c r="I29" s="77"/>
-      <c r="J29" s="62" t="s">
+      <c r="A29" s="59"/>
+      <c r="B29" s="83"/>
+      <c r="C29" s="87"/>
+      <c r="D29" s="64"/>
+      <c r="E29" s="61"/>
+      <c r="F29" s="64"/>
+      <c r="G29" s="61"/>
+      <c r="H29" s="64"/>
+      <c r="I29" s="71"/>
+      <c r="J29" s="63" t="s">
         <v>25</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L29" s="16" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:13">
-      <c r="A30" s="58"/>
-      <c r="B30" s="82"/>
-      <c r="C30" s="86"/>
-      <c r="D30" s="63"/>
-      <c r="E30" s="60"/>
-      <c r="F30" s="63"/>
-      <c r="G30" s="60"/>
-      <c r="H30" s="63"/>
-      <c r="I30" s="77"/>
-      <c r="J30" s="63"/>
+      <c r="A30" s="59"/>
+      <c r="B30" s="83"/>
+      <c r="C30" s="87"/>
+      <c r="D30" s="64"/>
+      <c r="E30" s="61"/>
+      <c r="F30" s="64"/>
+      <c r="G30" s="61"/>
+      <c r="H30" s="64"/>
+      <c r="I30" s="71"/>
+      <c r="J30" s="64"/>
       <c r="K30" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L30" s="16" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="34.799999999999997">
-      <c r="A31" s="58"/>
-      <c r="B31" s="82"/>
-      <c r="C31" s="86"/>
-      <c r="D31" s="63"/>
-      <c r="E31" s="60"/>
-      <c r="F31" s="63"/>
-      <c r="G31" s="60"/>
-      <c r="H31" s="63"/>
-      <c r="I31" s="77"/>
-      <c r="J31" s="64"/>
+      <c r="A31" s="59"/>
+      <c r="B31" s="83"/>
+      <c r="C31" s="87"/>
+      <c r="D31" s="64"/>
+      <c r="E31" s="61"/>
+      <c r="F31" s="64"/>
+      <c r="G31" s="61"/>
+      <c r="H31" s="64"/>
+      <c r="I31" s="71"/>
+      <c r="J31" s="65"/>
       <c r="K31" s="2" t="s">
         <v>42</v>
       </c>
@@ -2513,54 +2509,54 @@
       </c>
     </row>
     <row r="32" spans="1:13">
-      <c r="A32" s="58"/>
-      <c r="B32" s="82"/>
-      <c r="C32" s="86"/>
-      <c r="D32" s="63"/>
-      <c r="E32" s="60"/>
-      <c r="F32" s="63"/>
-      <c r="G32" s="60"/>
-      <c r="H32" s="63"/>
-      <c r="I32" s="77"/>
-      <c r="J32" s="62" t="s">
+      <c r="A32" s="59"/>
+      <c r="B32" s="83"/>
+      <c r="C32" s="87"/>
+      <c r="D32" s="64"/>
+      <c r="E32" s="61"/>
+      <c r="F32" s="64"/>
+      <c r="G32" s="61"/>
+      <c r="H32" s="64"/>
+      <c r="I32" s="71"/>
+      <c r="J32" s="63" t="s">
         <v>29</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L32" s="16" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:12">
-      <c r="A33" s="58"/>
-      <c r="B33" s="82"/>
-      <c r="C33" s="86"/>
-      <c r="D33" s="63"/>
-      <c r="E33" s="60"/>
-      <c r="F33" s="63"/>
-      <c r="G33" s="60"/>
-      <c r="H33" s="63"/>
-      <c r="I33" s="77"/>
-      <c r="J33" s="63"/>
+      <c r="A33" s="59"/>
+      <c r="B33" s="83"/>
+      <c r="C33" s="87"/>
+      <c r="D33" s="64"/>
+      <c r="E33" s="61"/>
+      <c r="F33" s="64"/>
+      <c r="G33" s="61"/>
+      <c r="H33" s="64"/>
+      <c r="I33" s="71"/>
+      <c r="J33" s="64"/>
       <c r="K33" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L33" s="16" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:12" ht="34.799999999999997">
-      <c r="A34" s="58"/>
-      <c r="B34" s="82"/>
-      <c r="C34" s="86"/>
-      <c r="D34" s="63"/>
-      <c r="E34" s="60"/>
-      <c r="F34" s="63"/>
-      <c r="G34" s="60"/>
-      <c r="H34" s="63"/>
-      <c r="I34" s="77"/>
-      <c r="J34" s="64"/>
+      <c r="A34" s="59"/>
+      <c r="B34" s="83"/>
+      <c r="C34" s="87"/>
+      <c r="D34" s="64"/>
+      <c r="E34" s="61"/>
+      <c r="F34" s="64"/>
+      <c r="G34" s="61"/>
+      <c r="H34" s="64"/>
+      <c r="I34" s="71"/>
+      <c r="J34" s="65"/>
       <c r="K34" s="2" t="s">
         <v>43</v>
       </c>
@@ -2569,54 +2565,54 @@
       </c>
     </row>
     <row r="35" spans="1:12">
-      <c r="A35" s="58"/>
-      <c r="B35" s="82"/>
-      <c r="C35" s="86"/>
-      <c r="D35" s="63"/>
-      <c r="E35" s="60"/>
-      <c r="F35" s="63"/>
-      <c r="G35" s="60"/>
-      <c r="H35" s="63"/>
-      <c r="I35" s="77"/>
-      <c r="J35" s="62" t="s">
+      <c r="A35" s="59"/>
+      <c r="B35" s="83"/>
+      <c r="C35" s="87"/>
+      <c r="D35" s="64"/>
+      <c r="E35" s="61"/>
+      <c r="F35" s="64"/>
+      <c r="G35" s="61"/>
+      <c r="H35" s="64"/>
+      <c r="I35" s="71"/>
+      <c r="J35" s="63" t="s">
         <v>30</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L35" s="16" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:12">
-      <c r="A36" s="58"/>
-      <c r="B36" s="82"/>
-      <c r="C36" s="86"/>
-      <c r="D36" s="63"/>
-      <c r="E36" s="60"/>
-      <c r="F36" s="63"/>
-      <c r="G36" s="60"/>
-      <c r="H36" s="63"/>
-      <c r="I36" s="77"/>
-      <c r="J36" s="63"/>
+      <c r="A36" s="59"/>
+      <c r="B36" s="83"/>
+      <c r="C36" s="87"/>
+      <c r="D36" s="64"/>
+      <c r="E36" s="61"/>
+      <c r="F36" s="64"/>
+      <c r="G36" s="61"/>
+      <c r="H36" s="64"/>
+      <c r="I36" s="71"/>
+      <c r="J36" s="64"/>
       <c r="K36" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L36" s="16" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:12" ht="34.799999999999997">
-      <c r="A37" s="58"/>
-      <c r="B37" s="82"/>
-      <c r="C37" s="86"/>
-      <c r="D37" s="63"/>
-      <c r="E37" s="60"/>
-      <c r="F37" s="63"/>
-      <c r="G37" s="61"/>
-      <c r="H37" s="64"/>
-      <c r="I37" s="77"/>
-      <c r="J37" s="64"/>
+      <c r="A37" s="59"/>
+      <c r="B37" s="83"/>
+      <c r="C37" s="87"/>
+      <c r="D37" s="64"/>
+      <c r="E37" s="61"/>
+      <c r="F37" s="64"/>
+      <c r="G37" s="62"/>
+      <c r="H37" s="65"/>
+      <c r="I37" s="71"/>
+      <c r="J37" s="65"/>
       <c r="K37" s="2" t="s">
         <v>44</v>
       </c>
@@ -2625,14 +2621,14 @@
       </c>
     </row>
     <row r="38" spans="1:12">
-      <c r="A38" s="58"/>
-      <c r="B38" s="82"/>
-      <c r="C38" s="86"/>
-      <c r="D38" s="63"/>
-      <c r="E38" s="60"/>
-      <c r="F38" s="63"/>
+      <c r="A38" s="59"/>
+      <c r="B38" s="83"/>
+      <c r="C38" s="87"/>
+      <c r="D38" s="64"/>
+      <c r="E38" s="61"/>
+      <c r="F38" s="64"/>
       <c r="G38" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>38</v>
@@ -2643,17 +2639,17 @@
       <c r="L38" s="4"/>
     </row>
     <row r="39" spans="1:12">
-      <c r="A39" s="58"/>
-      <c r="B39" s="82"/>
-      <c r="C39" s="86"/>
-      <c r="D39" s="63"/>
-      <c r="E39" s="60"/>
-      <c r="F39" s="63"/>
-      <c r="G39" s="73" t="s">
-        <v>172</v>
+      <c r="A39" s="59"/>
+      <c r="B39" s="83"/>
+      <c r="C39" s="87"/>
+      <c r="D39" s="64"/>
+      <c r="E39" s="61"/>
+      <c r="F39" s="64"/>
+      <c r="G39" s="75" t="s">
+        <v>170</v>
       </c>
       <c r="H39" s="36" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I39" s="12"/>
       <c r="J39" s="12"/>
@@ -2661,15 +2657,15 @@
       <c r="L39" s="4"/>
     </row>
     <row r="40" spans="1:12">
-      <c r="A40" s="58"/>
-      <c r="B40" s="82"/>
-      <c r="C40" s="86"/>
-      <c r="D40" s="63"/>
-      <c r="E40" s="60"/>
-      <c r="F40" s="63"/>
-      <c r="G40" s="74"/>
+      <c r="A40" s="59"/>
+      <c r="B40" s="83"/>
+      <c r="C40" s="87"/>
+      <c r="D40" s="64"/>
+      <c r="E40" s="61"/>
+      <c r="F40" s="64"/>
+      <c r="G40" s="76"/>
       <c r="H40" s="36" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I40" s="12"/>
       <c r="J40" s="12"/>
@@ -2677,15 +2673,15 @@
       <c r="L40" s="4"/>
     </row>
     <row r="41" spans="1:12">
-      <c r="A41" s="58"/>
-      <c r="B41" s="82"/>
-      <c r="C41" s="86"/>
-      <c r="D41" s="63"/>
-      <c r="E41" s="60"/>
-      <c r="F41" s="63"/>
-      <c r="G41" s="81"/>
+      <c r="A41" s="59"/>
+      <c r="B41" s="83"/>
+      <c r="C41" s="87"/>
+      <c r="D41" s="64"/>
+      <c r="E41" s="61"/>
+      <c r="F41" s="64"/>
+      <c r="G41" s="77"/>
       <c r="H41" s="36" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I41" s="12"/>
       <c r="J41" s="12"/>
@@ -2693,32 +2689,32 @@
       <c r="L41" s="4"/>
     </row>
     <row r="42" spans="1:12" ht="34.799999999999997">
-      <c r="A42" s="58"/>
-      <c r="B42" s="82"/>
-      <c r="C42" s="86"/>
-      <c r="D42" s="63"/>
-      <c r="E42" s="60"/>
-      <c r="F42" s="63"/>
+      <c r="A42" s="59"/>
+      <c r="B42" s="83"/>
+      <c r="C42" s="87"/>
+      <c r="D42" s="64"/>
+      <c r="E42" s="61"/>
+      <c r="F42" s="64"/>
       <c r="G42" s="28" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H42" s="36" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="J42" s="5"/>
       <c r="K42" s="5"/>
       <c r="L42" s="5"/>
     </row>
     <row r="43" spans="1:12" ht="34.799999999999997">
-      <c r="A43" s="58"/>
-      <c r="B43" s="82"/>
-      <c r="C43" s="86"/>
-      <c r="D43" s="63"/>
+      <c r="A43" s="59"/>
+      <c r="B43" s="83"/>
+      <c r="C43" s="87"/>
+      <c r="D43" s="64"/>
       <c r="E43" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F43" s="6" t="s">
         <v>4</v>
@@ -2729,12 +2725,12 @@
       <c r="L43" s="5"/>
     </row>
     <row r="44" spans="1:12" ht="34.799999999999997">
-      <c r="A44" s="58"/>
-      <c r="B44" s="82"/>
-      <c r="C44" s="86"/>
-      <c r="D44" s="64"/>
+      <c r="A44" s="59"/>
+      <c r="B44" s="83"/>
+      <c r="C44" s="87"/>
+      <c r="D44" s="65"/>
       <c r="E44" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>4</v>
@@ -2747,8 +2743,8 @@
       <c r="L44" s="5"/>
     </row>
     <row r="45" spans="1:12" ht="34.799999999999997">
-      <c r="A45" s="58"/>
-      <c r="B45" s="82"/>
+      <c r="A45" s="59"/>
+      <c r="B45" s="83"/>
       <c r="C45" s="13" t="s">
         <v>56</v>
       </c>
@@ -2762,10 +2758,10 @@
       <c r="I45" s="5"/>
     </row>
     <row r="46" spans="1:12" ht="34.799999999999997">
-      <c r="A46" s="58"/>
-      <c r="B46" s="82"/>
+      <c r="A46" s="59"/>
+      <c r="B46" s="83"/>
       <c r="C46" s="13" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>20</v>
@@ -2777,10 +2773,10 @@
       <c r="I46" s="5"/>
     </row>
     <row r="47" spans="1:12" ht="34.799999999999997">
-      <c r="A47" s="58"/>
-      <c r="B47" s="82"/>
+      <c r="A47" s="59"/>
+      <c r="B47" s="83"/>
       <c r="C47" s="28" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D47" s="30" t="s">
         <v>32</v>
@@ -2792,10 +2788,10 @@
       <c r="I47" s="5"/>
     </row>
     <row r="48" spans="1:12" ht="34.799999999999997">
-      <c r="A48" s="58"/>
-      <c r="B48" s="82"/>
+      <c r="A48" s="59"/>
+      <c r="B48" s="83"/>
       <c r="C48" s="10" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="D48" s="20" t="s">
         <v>20</v>
@@ -2807,9 +2803,9 @@
       <c r="I48" s="5"/>
     </row>
     <row r="49" spans="1:9">
-      <c r="A49" s="58"/>
+      <c r="A49" s="59"/>
       <c r="B49" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C49" s="5"/>
       <c r="D49" s="5"/>
@@ -2820,9 +2816,9 @@
       <c r="I49" s="5"/>
     </row>
     <row r="50" spans="1:9">
-      <c r="A50" s="58"/>
+      <c r="A50" s="59"/>
       <c r="B50" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C50" s="5"/>
       <c r="D50" s="5"/>
@@ -2833,9 +2829,9 @@
       <c r="I50" s="5"/>
     </row>
     <row r="51" spans="1:9">
-      <c r="A51" s="58"/>
+      <c r="A51" s="59"/>
       <c r="B51" s="25" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C51" s="5"/>
       <c r="D51" s="5"/>
@@ -2846,33 +2842,33 @@
       <c r="I51" s="5"/>
     </row>
     <row r="52" spans="1:9">
-      <c r="A52" s="58"/>
-      <c r="B52" s="55" t="s">
+      <c r="A52" s="59"/>
+      <c r="B52" s="56" t="s">
         <v>59</v>
       </c>
-      <c r="C52" s="73" t="s">
+      <c r="C52" s="75" t="s">
         <v>69</v>
       </c>
-      <c r="D52" s="55" t="s">
+      <c r="D52" s="56" t="s">
         <v>70</v>
       </c>
-      <c r="E52" s="59" t="s">
+      <c r="E52" s="60" t="s">
         <v>61</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G52" s="69" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H52" s="5"/>
     </row>
     <row r="53" spans="1:9">
-      <c r="A53" s="58"/>
-      <c r="B53" s="67"/>
-      <c r="C53" s="74"/>
-      <c r="D53" s="67"/>
-      <c r="E53" s="61"/>
+      <c r="A53" s="59"/>
+      <c r="B53" s="68"/>
+      <c r="C53" s="76"/>
+      <c r="D53" s="68"/>
+      <c r="E53" s="62"/>
       <c r="F53" s="3" t="s">
         <v>18</v>
       </c>
@@ -2880,15 +2876,15 @@
       <c r="H53" s="5"/>
     </row>
     <row r="54" spans="1:9" ht="34.799999999999997">
-      <c r="A54" s="58"/>
-      <c r="B54" s="67"/>
-      <c r="C54" s="74"/>
-      <c r="D54" s="67"/>
-      <c r="E54" s="75" t="s">
+      <c r="A54" s="59"/>
+      <c r="B54" s="68"/>
+      <c r="C54" s="76"/>
+      <c r="D54" s="68"/>
+      <c r="E54" s="82" t="s">
         <v>60</v>
       </c>
       <c r="F54" s="18" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G54" s="4" t="s">
         <v>45</v>
@@ -2897,13 +2893,13 @@
       <c r="I54" s="5"/>
     </row>
     <row r="55" spans="1:9" ht="52.2">
-      <c r="A55" s="58"/>
-      <c r="B55" s="67"/>
-      <c r="C55" s="74"/>
-      <c r="D55" s="67"/>
-      <c r="E55" s="75"/>
+      <c r="A55" s="59"/>
+      <c r="B55" s="68"/>
+      <c r="C55" s="76"/>
+      <c r="D55" s="68"/>
+      <c r="E55" s="82"/>
       <c r="F55" s="16" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G55" s="4" t="s">
         <v>46</v>
@@ -2912,13 +2908,13 @@
       <c r="I55" s="5"/>
     </row>
     <row r="56" spans="1:9" ht="52.2">
-      <c r="A56" s="58"/>
-      <c r="B56" s="67"/>
-      <c r="C56" s="74"/>
-      <c r="D56" s="67"/>
-      <c r="E56" s="75"/>
+      <c r="A56" s="59"/>
+      <c r="B56" s="68"/>
+      <c r="C56" s="76"/>
+      <c r="D56" s="68"/>
+      <c r="E56" s="82"/>
       <c r="F56" s="16" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G56" s="4" t="s">
         <v>47</v>
@@ -2927,13 +2923,13 @@
       <c r="I56" s="5"/>
     </row>
     <row r="57" spans="1:9">
-      <c r="A57" s="58"/>
-      <c r="B57" s="67"/>
-      <c r="C57" s="74"/>
-      <c r="D57" s="67"/>
-      <c r="E57" s="75"/>
+      <c r="A57" s="59"/>
+      <c r="B57" s="68"/>
+      <c r="C57" s="76"/>
+      <c r="D57" s="68"/>
+      <c r="E57" s="82"/>
       <c r="F57" s="16" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G57" s="4" t="s">
         <v>48</v>
@@ -2942,13 +2938,13 @@
       <c r="I57" s="5"/>
     </row>
     <row r="58" spans="1:9">
-      <c r="A58" s="58"/>
-      <c r="B58" s="67"/>
-      <c r="C58" s="74"/>
-      <c r="D58" s="67"/>
-      <c r="E58" s="75"/>
+      <c r="A58" s="59"/>
+      <c r="B58" s="68"/>
+      <c r="C58" s="76"/>
+      <c r="D58" s="68"/>
+      <c r="E58" s="82"/>
       <c r="F58" s="16" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G58" s="4" t="s">
         <v>49</v>
@@ -2957,13 +2953,13 @@
       <c r="I58" s="5"/>
     </row>
     <row r="59" spans="1:9">
-      <c r="A59" s="58"/>
-      <c r="B59" s="67"/>
-      <c r="C59" s="74"/>
-      <c r="D59" s="67"/>
-      <c r="E59" s="75"/>
+      <c r="A59" s="59"/>
+      <c r="B59" s="68"/>
+      <c r="C59" s="76"/>
+      <c r="D59" s="68"/>
+      <c r="E59" s="82"/>
       <c r="F59" s="16" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G59" s="19" t="s">
         <v>50</v>
@@ -2972,13 +2968,13 @@
       <c r="I59" s="5"/>
     </row>
     <row r="60" spans="1:9">
-      <c r="A60" s="58"/>
-      <c r="B60" s="67"/>
-      <c r="C60" s="74"/>
-      <c r="D60" s="67"/>
-      <c r="E60" s="75"/>
+      <c r="A60" s="59"/>
+      <c r="B60" s="68"/>
+      <c r="C60" s="76"/>
+      <c r="D60" s="68"/>
+      <c r="E60" s="82"/>
       <c r="F60" s="16" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G60" s="19" t="s">
         <v>51</v>
@@ -2987,43 +2983,43 @@
       <c r="I60" s="5"/>
     </row>
     <row r="61" spans="1:9">
-      <c r="A61" s="58"/>
-      <c r="B61" s="67"/>
-      <c r="C61" s="74"/>
-      <c r="D61" s="67"/>
-      <c r="E61" s="75"/>
+      <c r="A61" s="59"/>
+      <c r="B61" s="68"/>
+      <c r="C61" s="76"/>
+      <c r="D61" s="68"/>
+      <c r="E61" s="82"/>
       <c r="F61" s="16" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G61" s="69" t="s">
+        <v>80</v>
+      </c>
+      <c r="H61" s="55"/>
+      <c r="I61" s="5"/>
+    </row>
+    <row r="62" spans="1:9">
+      <c r="A62" s="59"/>
+      <c r="B62" s="68"/>
+      <c r="C62" s="76"/>
+      <c r="D62" s="68"/>
+      <c r="E62" s="82"/>
+      <c r="F62" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="G62" s="4" t="s">
         <v>81</v>
-      </c>
-      <c r="H61" s="54"/>
-      <c r="I61" s="5"/>
-    </row>
-    <row r="62" spans="1:9">
-      <c r="A62" s="58"/>
-      <c r="B62" s="67"/>
-      <c r="C62" s="74"/>
-      <c r="D62" s="67"/>
-      <c r="E62" s="75"/>
-      <c r="F62" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="G62" s="4" t="s">
-        <v>82</v>
       </c>
       <c r="H62" s="19"/>
       <c r="I62" s="5"/>
     </row>
     <row r="63" spans="1:9">
-      <c r="A63" s="58"/>
-      <c r="B63" s="67"/>
-      <c r="C63" s="74"/>
-      <c r="D63" s="67"/>
-      <c r="E63" s="75"/>
+      <c r="A63" s="59"/>
+      <c r="B63" s="68"/>
+      <c r="C63" s="76"/>
+      <c r="D63" s="68"/>
+      <c r="E63" s="82"/>
       <c r="F63" s="16" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G63" s="4" t="s">
         <v>52</v>
@@ -3032,13 +3028,13 @@
       <c r="I63" s="5"/>
     </row>
     <row r="64" spans="1:9">
-      <c r="A64" s="58"/>
-      <c r="B64" s="67"/>
-      <c r="C64" s="74"/>
-      <c r="D64" s="67"/>
-      <c r="E64" s="75"/>
+      <c r="A64" s="59"/>
+      <c r="B64" s="68"/>
+      <c r="C64" s="76"/>
+      <c r="D64" s="68"/>
+      <c r="E64" s="82"/>
       <c r="F64" s="16" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G64" s="4" t="s">
         <v>53</v>
@@ -3047,13 +3043,13 @@
       <c r="I64" s="5"/>
     </row>
     <row r="65" spans="1:12">
-      <c r="A65" s="58"/>
-      <c r="B65" s="67"/>
-      <c r="C65" s="74"/>
-      <c r="D65" s="67"/>
-      <c r="E65" s="75"/>
+      <c r="A65" s="59"/>
+      <c r="B65" s="68"/>
+      <c r="C65" s="76"/>
+      <c r="D65" s="68"/>
+      <c r="E65" s="82"/>
       <c r="F65" s="16" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G65" s="4" t="s">
         <v>54</v>
@@ -3062,13 +3058,13 @@
       <c r="I65" s="5"/>
     </row>
     <row r="66" spans="1:12">
-      <c r="A66" s="58"/>
-      <c r="B66" s="67"/>
-      <c r="C66" s="74"/>
-      <c r="D66" s="67"/>
-      <c r="E66" s="75"/>
+      <c r="A66" s="59"/>
+      <c r="B66" s="68"/>
+      <c r="C66" s="76"/>
+      <c r="D66" s="68"/>
+      <c r="E66" s="82"/>
       <c r="F66" s="16" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G66" s="4" t="s">
         <v>55</v>
@@ -3077,48 +3073,48 @@
       <c r="I66" s="5"/>
     </row>
     <row r="67" spans="1:12" ht="69.599999999999994">
-      <c r="A67" s="58"/>
-      <c r="B67" s="67"/>
-      <c r="C67" s="74"/>
-      <c r="D67" s="67"/>
-      <c r="E67" s="75"/>
+      <c r="A67" s="59"/>
+      <c r="B67" s="68"/>
+      <c r="C67" s="76"/>
+      <c r="D67" s="68"/>
+      <c r="E67" s="82"/>
       <c r="F67" s="16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H67" s="19"/>
       <c r="I67" s="5"/>
     </row>
     <row r="68" spans="1:12" ht="34.799999999999997">
-      <c r="A68" s="58"/>
-      <c r="B68" s="56"/>
-      <c r="C68" s="81"/>
-      <c r="D68" s="56"/>
-      <c r="E68" s="75"/>
+      <c r="A68" s="59"/>
+      <c r="B68" s="57"/>
+      <c r="C68" s="77"/>
+      <c r="D68" s="57"/>
+      <c r="E68" s="82"/>
       <c r="F68" s="16" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H68" s="19"/>
       <c r="I68" s="5"/>
     </row>
     <row r="69" spans="1:12" ht="52.2">
-      <c r="A69" s="58"/>
-      <c r="B69" s="55" t="s">
-        <v>179</v>
+      <c r="A69" s="59"/>
+      <c r="B69" s="56" t="s">
+        <v>177</v>
       </c>
       <c r="C69" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="D69" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="E69" s="4" t="s">
         <v>182</v>
-      </c>
-      <c r="D69" s="20" t="s">
-        <v>179</v>
-      </c>
-      <c r="E69" s="4" t="s">
-        <v>184</v>
       </c>
       <c r="F69" s="4"/>
       <c r="G69" s="4"/>
@@ -3129,8 +3125,8 @@
       <c r="L69" s="19"/>
     </row>
     <row r="70" spans="1:12" ht="52.2">
-      <c r="A70" s="58"/>
-      <c r="B70" s="67"/>
+      <c r="A70" s="59"/>
+      <c r="B70" s="68"/>
       <c r="C70" s="13" t="s">
         <v>24</v>
       </c>
@@ -3149,8 +3145,8 @@
       <c r="L70" s="19"/>
     </row>
     <row r="71" spans="1:12" ht="34.799999999999997" customHeight="1">
-      <c r="A71" s="58"/>
-      <c r="B71" s="67"/>
+      <c r="A71" s="59"/>
+      <c r="B71" s="68"/>
       <c r="C71" s="22" t="s">
         <v>57</v>
       </c>
@@ -3167,8 +3163,8 @@
       <c r="L71" s="19"/>
     </row>
     <row r="72" spans="1:12" ht="34.799999999999997">
-      <c r="A72" s="58"/>
-      <c r="B72" s="67"/>
+      <c r="A72" s="59"/>
+      <c r="B72" s="68"/>
       <c r="C72" s="11" t="s">
         <v>58</v>
       </c>
@@ -3184,776 +3180,776 @@
       <c r="L72" s="19"/>
     </row>
     <row r="73" spans="1:12">
-      <c r="A73" s="58"/>
-      <c r="B73" s="67"/>
-      <c r="C73" s="70" t="s">
-        <v>115</v>
-      </c>
-      <c r="D73" s="65" t="s">
-        <v>156</v>
-      </c>
-      <c r="E73" s="55" t="s">
-        <v>171</v>
+      <c r="A73" s="59"/>
+      <c r="B73" s="68"/>
+      <c r="C73" s="78" t="s">
+        <v>113</v>
+      </c>
+      <c r="D73" s="66" t="s">
+        <v>154</v>
+      </c>
+      <c r="E73" s="56" t="s">
+        <v>169</v>
       </c>
       <c r="F73" s="13" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G73" s="6" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H73" s="12" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="I73" s="4"/>
     </row>
     <row r="74" spans="1:12" ht="52.2">
-      <c r="A74" s="58"/>
-      <c r="B74" s="67"/>
-      <c r="C74" s="70"/>
-      <c r="D74" s="66"/>
-      <c r="E74" s="67"/>
+      <c r="A74" s="59"/>
+      <c r="B74" s="68"/>
+      <c r="C74" s="78"/>
+      <c r="D74" s="67"/>
+      <c r="E74" s="68"/>
       <c r="F74" s="13" t="s">
+        <v>226</v>
+      </c>
+      <c r="G74" s="16" t="s">
+        <v>229</v>
+      </c>
+      <c r="H74" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="G74" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="H74" s="4" t="s">
+      <c r="I74" s="4"/>
+    </row>
+    <row r="75" spans="1:12">
+      <c r="A75" s="59"/>
+      <c r="B75" s="68"/>
+      <c r="C75" s="79"/>
+      <c r="D75" s="67"/>
+      <c r="E75" s="68"/>
+      <c r="F75" s="56" t="s">
+        <v>140</v>
+      </c>
+      <c r="G75" s="51" t="s">
+        <v>212</v>
+      </c>
+      <c r="H75" s="23" t="s">
+        <v>244</v>
+      </c>
+      <c r="I75" s="4"/>
+    </row>
+    <row r="76" spans="1:12" ht="69.599999999999994">
+      <c r="A76" s="59"/>
+      <c r="B76" s="68"/>
+      <c r="C76" s="79"/>
+      <c r="D76" s="67"/>
+      <c r="E76" s="68"/>
+      <c r="F76" s="56"/>
+      <c r="G76" s="75" t="s">
+        <v>245</v>
+      </c>
+      <c r="H76" s="52" t="s">
+        <v>246</v>
+      </c>
+      <c r="I76" s="4" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" ht="34.799999999999997">
+      <c r="A77" s="59"/>
+      <c r="B77" s="68"/>
+      <c r="C77" s="79"/>
+      <c r="D77" s="67"/>
+      <c r="E77" s="68"/>
+      <c r="F77" s="56"/>
+      <c r="G77" s="89"/>
+      <c r="H77" s="52" t="s">
+        <v>248</v>
+      </c>
+      <c r="I77" s="4"/>
+    </row>
+    <row r="78" spans="1:12">
+      <c r="A78" s="59"/>
+      <c r="B78" s="68"/>
+      <c r="C78" s="79"/>
+      <c r="D78" s="67"/>
+      <c r="E78" s="68"/>
+      <c r="F78" s="56"/>
+      <c r="G78" s="89"/>
+      <c r="H78" s="52" t="s">
+        <v>249</v>
+      </c>
+      <c r="I78" s="4"/>
+    </row>
+    <row r="79" spans="1:12" ht="87">
+      <c r="A79" s="59"/>
+      <c r="B79" s="68"/>
+      <c r="C79" s="79"/>
+      <c r="D79" s="67"/>
+      <c r="E79" s="68"/>
+      <c r="F79" s="68"/>
+      <c r="G79" s="75" t="s">
+        <v>188</v>
+      </c>
+      <c r="H79" s="52" t="s">
+        <v>234</v>
+      </c>
+      <c r="I79" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="I74" s="4"/>
-    </row>
-    <row r="75" spans="1:12">
-      <c r="A75" s="58"/>
-      <c r="B75" s="67"/>
-      <c r="C75" s="71"/>
-      <c r="D75" s="66"/>
-      <c r="E75" s="67"/>
-      <c r="F75" s="55" t="s">
-        <v>142</v>
-      </c>
-      <c r="G75" s="51" t="s">
+    </row>
+    <row r="80" spans="1:12" ht="139.19999999999999">
+      <c r="A80" s="59"/>
+      <c r="B80" s="68"/>
+      <c r="C80" s="79"/>
+      <c r="D80" s="67"/>
+      <c r="E80" s="68"/>
+      <c r="F80" s="68"/>
+      <c r="G80" s="75"/>
+      <c r="H80" s="52" t="s">
+        <v>250</v>
+      </c>
+      <c r="I80" s="4" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" ht="34.799999999999997">
+      <c r="A81" s="59"/>
+      <c r="B81" s="68"/>
+      <c r="C81" s="79"/>
+      <c r="D81" s="67"/>
+      <c r="E81" s="68"/>
+      <c r="F81" s="68"/>
+      <c r="G81" s="39" t="s">
         <v>214</v>
       </c>
-      <c r="H75" s="23" t="s">
-        <v>247</v>
-      </c>
-      <c r="I75" s="4"/>
-    </row>
-    <row r="76" spans="1:12" ht="69.599999999999994">
-      <c r="A76" s="58"/>
-      <c r="B76" s="67"/>
-      <c r="C76" s="71"/>
-      <c r="D76" s="66"/>
-      <c r="E76" s="67"/>
-      <c r="F76" s="55"/>
-      <c r="G76" s="73" t="s">
-        <v>248</v>
-      </c>
-      <c r="H76" s="52" t="s">
-        <v>249</v>
-      </c>
-      <c r="I76" s="4" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12" ht="34.799999999999997">
-      <c r="A77" s="58"/>
-      <c r="B77" s="67"/>
-      <c r="C77" s="71"/>
-      <c r="D77" s="66"/>
-      <c r="E77" s="67"/>
-      <c r="F77" s="55"/>
-      <c r="G77" s="88"/>
-      <c r="H77" s="52" t="s">
-        <v>251</v>
-      </c>
-      <c r="I77" s="4"/>
-    </row>
-    <row r="78" spans="1:12">
-      <c r="A78" s="58"/>
-      <c r="B78" s="67"/>
-      <c r="C78" s="71"/>
-      <c r="D78" s="66"/>
-      <c r="E78" s="67"/>
-      <c r="F78" s="55"/>
-      <c r="G78" s="88"/>
-      <c r="H78" s="52" t="s">
-        <v>252</v>
-      </c>
-      <c r="I78" s="4"/>
-    </row>
-    <row r="79" spans="1:12" ht="87">
-      <c r="A79" s="58"/>
-      <c r="B79" s="67"/>
-      <c r="C79" s="71"/>
-      <c r="D79" s="66"/>
-      <c r="E79" s="67"/>
-      <c r="F79" s="67"/>
-      <c r="G79" s="73" t="s">
-        <v>190</v>
-      </c>
-      <c r="H79" s="52" t="s">
-        <v>237</v>
-      </c>
-      <c r="I79" s="4" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" ht="139.19999999999999">
-      <c r="A80" s="58"/>
-      <c r="B80" s="67"/>
-      <c r="C80" s="71"/>
-      <c r="D80" s="66"/>
-      <c r="E80" s="67"/>
-      <c r="F80" s="67"/>
-      <c r="G80" s="73"/>
-      <c r="H80" s="52" t="s">
-        <v>253</v>
-      </c>
-      <c r="I80" s="4" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="81" spans="1:11" ht="34.799999999999997">
-      <c r="A81" s="58"/>
-      <c r="B81" s="67"/>
-      <c r="C81" s="71"/>
-      <c r="D81" s="66"/>
-      <c r="E81" s="67"/>
-      <c r="F81" s="67"/>
-      <c r="G81" s="39" t="s">
+      <c r="H81" s="29" t="s">
+        <v>215</v>
+      </c>
+      <c r="I81" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="H81" s="29" t="s">
-        <v>217</v>
-      </c>
-      <c r="I81" s="4" t="s">
-        <v>218</v>
-      </c>
     </row>
     <row r="82" spans="1:11" ht="34.799999999999997" customHeight="1">
-      <c r="A82" s="58"/>
-      <c r="B82" s="67"/>
-      <c r="C82" s="71"/>
-      <c r="D82" s="66"/>
-      <c r="E82" s="67"/>
-      <c r="F82" s="67"/>
-      <c r="G82" s="78" t="s">
-        <v>157</v>
-      </c>
-      <c r="H82" s="77" t="s">
-        <v>205</v>
+      <c r="A82" s="59"/>
+      <c r="B82" s="68"/>
+      <c r="C82" s="79"/>
+      <c r="D82" s="67"/>
+      <c r="E82" s="68"/>
+      <c r="F82" s="68"/>
+      <c r="G82" s="72" t="s">
+        <v>155</v>
+      </c>
+      <c r="H82" s="71" t="s">
+        <v>203</v>
       </c>
       <c r="I82" s="28" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="J82" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="83" spans="1:11">
-      <c r="A83" s="58"/>
-      <c r="B83" s="67"/>
-      <c r="C83" s="71"/>
-      <c r="D83" s="66"/>
-      <c r="E83" s="67"/>
-      <c r="F83" s="67"/>
-      <c r="G83" s="79"/>
-      <c r="H83" s="77"/>
+      <c r="A83" s="59"/>
+      <c r="B83" s="68"/>
+      <c r="C83" s="79"/>
+      <c r="D83" s="67"/>
+      <c r="E83" s="68"/>
+      <c r="F83" s="68"/>
+      <c r="G83" s="73"/>
+      <c r="H83" s="71"/>
       <c r="I83" s="28" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="J83" s="3" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="84" spans="1:11" ht="33.6" customHeight="1">
-      <c r="A84" s="58"/>
-      <c r="B84" s="67"/>
-      <c r="C84" s="71"/>
-      <c r="D84" s="66"/>
-      <c r="E84" s="67"/>
-      <c r="F84" s="67"/>
-      <c r="G84" s="79"/>
-      <c r="H84" s="77"/>
-      <c r="I84" s="73" t="s">
+      <c r="A84" s="59"/>
+      <c r="B84" s="68"/>
+      <c r="C84" s="79"/>
+      <c r="D84" s="67"/>
+      <c r="E84" s="68"/>
+      <c r="F84" s="68"/>
+      <c r="G84" s="73"/>
+      <c r="H84" s="71"/>
+      <c r="I84" s="75" t="s">
+        <v>208</v>
+      </c>
+      <c r="J84" s="56" t="s">
+        <v>213</v>
+      </c>
+      <c r="K84" s="21" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11">
+      <c r="A85" s="59"/>
+      <c r="B85" s="68"/>
+      <c r="C85" s="79"/>
+      <c r="D85" s="67"/>
+      <c r="E85" s="68"/>
+      <c r="F85" s="68"/>
+      <c r="G85" s="73"/>
+      <c r="H85" s="71"/>
+      <c r="I85" s="76"/>
+      <c r="J85" s="68"/>
+      <c r="K85" s="21" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11">
+      <c r="A86" s="59"/>
+      <c r="B86" s="68"/>
+      <c r="C86" s="79"/>
+      <c r="D86" s="67"/>
+      <c r="E86" s="68"/>
+      <c r="F86" s="68"/>
+      <c r="G86" s="73"/>
+      <c r="H86" s="71"/>
+      <c r="I86" s="77"/>
+      <c r="J86" s="57"/>
+      <c r="K86" s="21" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" ht="34.799999999999997">
+      <c r="A87" s="59"/>
+      <c r="B87" s="68"/>
+      <c r="C87" s="79"/>
+      <c r="D87" s="67"/>
+      <c r="E87" s="68"/>
+      <c r="F87" s="68"/>
+      <c r="G87" s="74"/>
+      <c r="H87" s="71"/>
+      <c r="I87" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="J84" s="55" t="s">
-        <v>215</v>
-      </c>
-      <c r="K84" s="21" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11">
-      <c r="A85" s="58"/>
-      <c r="B85" s="67"/>
-      <c r="C85" s="71"/>
-      <c r="D85" s="66"/>
-      <c r="E85" s="67"/>
-      <c r="F85" s="67"/>
-      <c r="G85" s="79"/>
-      <c r="H85" s="77"/>
-      <c r="I85" s="74"/>
-      <c r="J85" s="67"/>
-      <c r="K85" s="21" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11">
-      <c r="A86" s="58"/>
-      <c r="B86" s="67"/>
-      <c r="C86" s="71"/>
-      <c r="D86" s="66"/>
-      <c r="E86" s="67"/>
-      <c r="F86" s="67"/>
-      <c r="G86" s="79"/>
-      <c r="H86" s="77"/>
-      <c r="I86" s="81"/>
-      <c r="J86" s="56"/>
-      <c r="K86" s="21" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="87" spans="1:11" ht="34.799999999999997">
-      <c r="A87" s="58"/>
-      <c r="B87" s="67"/>
-      <c r="C87" s="71"/>
-      <c r="D87" s="66"/>
-      <c r="E87" s="67"/>
-      <c r="F87" s="67"/>
-      <c r="G87" s="80"/>
-      <c r="H87" s="77"/>
-      <c r="I87" s="28" t="s">
-        <v>212</v>
-      </c>
       <c r="J87" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="88" spans="1:11" ht="34.799999999999997">
-      <c r="A88" s="58"/>
-      <c r="B88" s="67"/>
-      <c r="C88" s="71"/>
-      <c r="D88" s="66"/>
-      <c r="E88" s="67"/>
-      <c r="F88" s="67"/>
+      <c r="A88" s="59"/>
+      <c r="B88" s="68"/>
+      <c r="C88" s="79"/>
+      <c r="D88" s="67"/>
+      <c r="E88" s="68"/>
+      <c r="F88" s="68"/>
       <c r="G88" s="31" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="J88" s="4"/>
     </row>
     <row r="89" spans="1:11" ht="34.799999999999997">
-      <c r="A89" s="58"/>
-      <c r="B89" s="67"/>
-      <c r="C89" s="71"/>
-      <c r="D89" s="66"/>
-      <c r="E89" s="67"/>
-      <c r="F89" s="67"/>
+      <c r="A89" s="59"/>
+      <c r="B89" s="68"/>
+      <c r="C89" s="79"/>
+      <c r="D89" s="67"/>
+      <c r="E89" s="68"/>
+      <c r="F89" s="68"/>
       <c r="G89" s="45" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H89" s="4"/>
       <c r="I89" s="12"/>
       <c r="J89" s="4"/>
     </row>
     <row r="90" spans="1:11" ht="34.799999999999997">
-      <c r="A90" s="58"/>
-      <c r="B90" s="67"/>
-      <c r="C90" s="71"/>
-      <c r="D90" s="66"/>
-      <c r="E90" s="67"/>
-      <c r="F90" s="55" t="s">
-        <v>143</v>
-      </c>
-      <c r="G90" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H90" s="77" t="s">
-        <v>191</v>
+      <c r="A90" s="59"/>
+      <c r="B90" s="68"/>
+      <c r="C90" s="79"/>
+      <c r="D90" s="67"/>
+      <c r="E90" s="68"/>
+      <c r="F90" s="56" t="s">
+        <v>141</v>
+      </c>
+      <c r="G90" s="70" t="s">
+        <v>209</v>
+      </c>
+      <c r="H90" s="71" t="s">
+        <v>189</v>
       </c>
       <c r="I90" s="28" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="J90" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="91" spans="1:11">
-      <c r="A91" s="58"/>
-      <c r="B91" s="67"/>
-      <c r="C91" s="71"/>
-      <c r="D91" s="66"/>
-      <c r="E91" s="67"/>
-      <c r="F91" s="67"/>
-      <c r="G91" s="76"/>
-      <c r="H91" s="77"/>
+      <c r="A91" s="59"/>
+      <c r="B91" s="68"/>
+      <c r="C91" s="79"/>
+      <c r="D91" s="67"/>
+      <c r="E91" s="68"/>
+      <c r="F91" s="68"/>
+      <c r="G91" s="70"/>
+      <c r="H91" s="71"/>
       <c r="I91" s="28" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="J91" s="44"/>
     </row>
     <row r="92" spans="1:11" ht="34.799999999999997">
-      <c r="A92" s="58"/>
-      <c r="B92" s="67"/>
-      <c r="C92" s="71"/>
-      <c r="D92" s="66"/>
-      <c r="E92" s="67"/>
-      <c r="F92" s="67"/>
-      <c r="G92" s="76"/>
-      <c r="H92" s="77"/>
+      <c r="A92" s="59"/>
+      <c r="B92" s="68"/>
+      <c r="C92" s="79"/>
+      <c r="D92" s="67"/>
+      <c r="E92" s="68"/>
+      <c r="F92" s="68"/>
+      <c r="G92" s="70"/>
+      <c r="H92" s="71"/>
       <c r="I92" s="28" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="J92" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="93" spans="1:11">
-      <c r="A93" s="58"/>
-      <c r="B93" s="67"/>
-      <c r="C93" s="71"/>
-      <c r="D93" s="66"/>
-      <c r="E93" s="67"/>
-      <c r="F93" s="67"/>
+      <c r="A93" s="59"/>
+      <c r="B93" s="68"/>
+      <c r="C93" s="79"/>
+      <c r="D93" s="67"/>
+      <c r="E93" s="68"/>
+      <c r="F93" s="68"/>
       <c r="G93" s="53" t="s">
+        <v>255</v>
+      </c>
+      <c r="H93" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="I93" s="54" t="s">
+        <v>266</v>
+      </c>
+      <c r="J93" s="4"/>
+    </row>
+    <row r="94" spans="1:11">
+      <c r="A94" s="59"/>
+      <c r="B94" s="68"/>
+      <c r="C94" s="79"/>
+      <c r="D94" s="67"/>
+      <c r="E94" s="68"/>
+      <c r="F94" s="68"/>
+      <c r="G94" s="53" t="s">
+        <v>256</v>
+      </c>
+      <c r="H94" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="I94" s="54" t="s">
+        <v>268</v>
+      </c>
+      <c r="J94" s="4"/>
+    </row>
+    <row r="95" spans="1:11">
+      <c r="A95" s="59"/>
+      <c r="B95" s="68"/>
+      <c r="C95" s="79"/>
+      <c r="D95" s="67"/>
+      <c r="E95" s="68"/>
+      <c r="F95" s="68"/>
+      <c r="G95" s="53" t="s">
+        <v>257</v>
+      </c>
+      <c r="H95" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="I95" s="54" t="s">
+        <v>267</v>
+      </c>
+      <c r="J95" s="4"/>
+    </row>
+    <row r="96" spans="1:11">
+      <c r="A96" s="59"/>
+      <c r="B96" s="68"/>
+      <c r="C96" s="79"/>
+      <c r="D96" s="67"/>
+      <c r="E96" s="68"/>
+      <c r="F96" s="68"/>
+      <c r="G96" s="53" t="s">
         <v>258</v>
       </c>
-      <c r="H93" s="10" t="s">
+      <c r="H96" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="I96" s="54" t="s">
+        <v>265</v>
+      </c>
+      <c r="J96" s="4"/>
+    </row>
+    <row r="97" spans="1:12">
+      <c r="A97" s="59"/>
+      <c r="B97" s="68"/>
+      <c r="C97" s="79"/>
+      <c r="D97" s="67"/>
+      <c r="E97" s="68"/>
+      <c r="F97" s="68"/>
+      <c r="G97" s="53" t="s">
+        <v>259</v>
+      </c>
+      <c r="H97" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="I97" s="54" t="s">
+        <v>269</v>
+      </c>
+      <c r="J97" s="4"/>
+    </row>
+    <row r="98" spans="1:12">
+      <c r="A98" s="59"/>
+      <c r="B98" s="68"/>
+      <c r="C98" s="79"/>
+      <c r="D98" s="67"/>
+      <c r="E98" s="68"/>
+      <c r="F98" s="68"/>
+      <c r="G98" s="53" t="s">
+        <v>260</v>
+      </c>
+      <c r="H98" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="I98" s="54" t="s">
+        <v>270</v>
+      </c>
+      <c r="J98" s="4"/>
+    </row>
+    <row r="99" spans="1:12">
+      <c r="A99" s="59"/>
+      <c r="B99" s="68"/>
+      <c r="C99" s="79"/>
+      <c r="D99" s="67"/>
+      <c r="E99" s="68"/>
+      <c r="F99" s="68"/>
+      <c r="G99" s="53" t="s">
+        <v>261</v>
+      </c>
+      <c r="H99" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="I99" s="54" t="s">
+        <v>271</v>
+      </c>
+      <c r="J99" s="4"/>
+    </row>
+    <row r="100" spans="1:12">
+      <c r="A100" s="59"/>
+      <c r="B100" s="68"/>
+      <c r="C100" s="79"/>
+      <c r="D100" s="67"/>
+      <c r="E100" s="68"/>
+      <c r="F100" s="68"/>
+      <c r="G100" s="56" t="s">
+        <v>281</v>
+      </c>
+      <c r="H100" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="I100" s="29" t="s">
         <v>275</v>
       </c>
-      <c r="I93" s="89" t="s">
-        <v>269</v>
-      </c>
-      <c r="J93" s="4"/>
-    </row>
-    <row r="94" spans="1:11">
-      <c r="A94" s="58"/>
-      <c r="B94" s="67"/>
-      <c r="C94" s="71"/>
-      <c r="D94" s="66"/>
-      <c r="E94" s="67"/>
-      <c r="F94" s="67"/>
-      <c r="G94" s="53" t="s">
-        <v>259</v>
-      </c>
-      <c r="H94" s="10" t="s">
-        <v>275</v>
-      </c>
-      <c r="I94" s="89" t="s">
-        <v>271</v>
-      </c>
-      <c r="J94" s="4"/>
-    </row>
-    <row r="95" spans="1:11">
-      <c r="A95" s="58"/>
-      <c r="B95" s="67"/>
-      <c r="C95" s="71"/>
-      <c r="D95" s="66"/>
-      <c r="E95" s="67"/>
-      <c r="F95" s="67"/>
-      <c r="G95" s="53" t="s">
-        <v>260</v>
-      </c>
-      <c r="H95" s="10" t="s">
-        <v>275</v>
-      </c>
-      <c r="I95" s="89" t="s">
-        <v>270</v>
-      </c>
-      <c r="J95" s="4"/>
-    </row>
-    <row r="96" spans="1:11">
-      <c r="A96" s="58"/>
-      <c r="B96" s="67"/>
-      <c r="C96" s="71"/>
-      <c r="D96" s="66"/>
-      <c r="E96" s="67"/>
-      <c r="F96" s="67"/>
-      <c r="G96" s="53" t="s">
-        <v>261</v>
-      </c>
-      <c r="H96" s="10" t="s">
-        <v>275</v>
-      </c>
-      <c r="I96" s="89" t="s">
-        <v>268</v>
-      </c>
-      <c r="J96" s="4"/>
-    </row>
-    <row r="97" spans="1:12">
-      <c r="A97" s="58"/>
-      <c r="B97" s="67"/>
-      <c r="C97" s="71"/>
-      <c r="D97" s="66"/>
-      <c r="E97" s="67"/>
-      <c r="F97" s="67"/>
-      <c r="G97" s="53" t="s">
-        <v>262</v>
-      </c>
-      <c r="H97" s="10" t="s">
-        <v>275</v>
-      </c>
-      <c r="I97" s="89" t="s">
+      <c r="J100" s="69" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12">
+      <c r="A101" s="59"/>
+      <c r="B101" s="68"/>
+      <c r="C101" s="79"/>
+      <c r="D101" s="67"/>
+      <c r="E101" s="68"/>
+      <c r="F101" s="68"/>
+      <c r="G101" s="57"/>
+      <c r="H101" s="10" t="s">
         <v>272</v>
       </c>
-      <c r="J97" s="4"/>
-    </row>
-    <row r="98" spans="1:12">
-      <c r="A98" s="58"/>
-      <c r="B98" s="67"/>
-      <c r="C98" s="71"/>
-      <c r="D98" s="66"/>
-      <c r="E98" s="67"/>
-      <c r="F98" s="67"/>
-      <c r="G98" s="53" t="s">
-        <v>263</v>
-      </c>
-      <c r="H98" s="10" t="s">
-        <v>275</v>
-      </c>
-      <c r="I98" s="89" t="s">
-        <v>273</v>
-      </c>
-      <c r="J98" s="4"/>
-    </row>
-    <row r="99" spans="1:12">
-      <c r="A99" s="58"/>
-      <c r="B99" s="67"/>
-      <c r="C99" s="71"/>
-      <c r="D99" s="66"/>
-      <c r="E99" s="67"/>
-      <c r="F99" s="67"/>
-      <c r="G99" s="53" t="s">
-        <v>264</v>
-      </c>
-      <c r="H99" s="10" t="s">
-        <v>275</v>
-      </c>
-      <c r="I99" s="89" t="s">
-        <v>274</v>
-      </c>
-      <c r="J99" s="4"/>
-    </row>
-    <row r="100" spans="1:12">
-      <c r="A100" s="58"/>
-      <c r="B100" s="67"/>
-      <c r="C100" s="71"/>
-      <c r="D100" s="66"/>
-      <c r="E100" s="67"/>
-      <c r="F100" s="67"/>
-      <c r="G100" s="55" t="s">
-        <v>284</v>
-      </c>
-      <c r="H100" s="10" t="s">
+      <c r="I101" s="54" t="s">
+        <v>276</v>
+      </c>
+      <c r="J101" s="69"/>
+    </row>
+    <row r="102" spans="1:12">
+      <c r="A102" s="59"/>
+      <c r="B102" s="68"/>
+      <c r="C102" s="79"/>
+      <c r="D102" s="67"/>
+      <c r="E102" s="68"/>
+      <c r="F102" s="68"/>
+      <c r="G102" s="56" t="s">
+        <v>280</v>
+      </c>
+      <c r="H102" s="10" t="s">
         <v>277</v>
-      </c>
-      <c r="I100" s="29" t="s">
-        <v>278</v>
-      </c>
-      <c r="J100" s="69" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="101" spans="1:12">
-      <c r="A101" s="58"/>
-      <c r="B101" s="67"/>
-      <c r="C101" s="71"/>
-      <c r="D101" s="66"/>
-      <c r="E101" s="67"/>
-      <c r="F101" s="67"/>
-      <c r="G101" s="56"/>
-      <c r="H101" s="10" t="s">
-        <v>275</v>
-      </c>
-      <c r="I101" s="89" t="s">
-        <v>279</v>
-      </c>
-      <c r="J101" s="69"/>
-    </row>
-    <row r="102" spans="1:12">
-      <c r="A102" s="58"/>
-      <c r="B102" s="67"/>
-      <c r="C102" s="71"/>
-      <c r="D102" s="66"/>
-      <c r="E102" s="67"/>
-      <c r="F102" s="67"/>
-      <c r="G102" s="55" t="s">
-        <v>283</v>
-      </c>
-      <c r="H102" s="10" t="s">
-        <v>280</v>
       </c>
       <c r="I102" s="4"/>
       <c r="J102" s="4"/>
     </row>
     <row r="103" spans="1:12">
-      <c r="A103" s="58"/>
-      <c r="B103" s="67"/>
-      <c r="C103" s="71"/>
-      <c r="D103" s="66"/>
-      <c r="E103" s="67"/>
-      <c r="F103" s="67"/>
-      <c r="G103" s="67"/>
+      <c r="A103" s="59"/>
+      <c r="B103" s="68"/>
+      <c r="C103" s="79"/>
+      <c r="D103" s="67"/>
+      <c r="E103" s="68"/>
+      <c r="F103" s="68"/>
+      <c r="G103" s="68"/>
       <c r="H103" s="10" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="I103" s="4"/>
       <c r="J103" s="4"/>
     </row>
     <row r="104" spans="1:12">
-      <c r="A104" s="58"/>
-      <c r="B104" s="67"/>
-      <c r="C104" s="71"/>
-      <c r="D104" s="66"/>
-      <c r="E104" s="67"/>
-      <c r="F104" s="56"/>
-      <c r="G104" s="56"/>
+      <c r="A104" s="59"/>
+      <c r="B104" s="68"/>
+      <c r="C104" s="79"/>
+      <c r="D104" s="67"/>
+      <c r="E104" s="68"/>
+      <c r="F104" s="57"/>
+      <c r="G104" s="57"/>
       <c r="H104" s="10" t="s">
-        <v>275</v>
-      </c>
-      <c r="I104" s="89" t="s">
-        <v>282</v>
+        <v>272</v>
+      </c>
+      <c r="I104" s="54" t="s">
+        <v>279</v>
       </c>
       <c r="J104" s="4"/>
     </row>
     <row r="105" spans="1:12">
-      <c r="A105" s="58"/>
-      <c r="B105" s="67"/>
-      <c r="C105" s="71"/>
-      <c r="D105" s="66"/>
-      <c r="E105" s="67"/>
-      <c r="F105" s="77" t="s">
-        <v>155</v>
-      </c>
-      <c r="G105" s="77" t="s">
-        <v>198</v>
+      <c r="A105" s="59"/>
+      <c r="B105" s="68"/>
+      <c r="C105" s="79"/>
+      <c r="D105" s="67"/>
+      <c r="E105" s="68"/>
+      <c r="F105" s="71" t="s">
+        <v>153</v>
+      </c>
+      <c r="G105" s="71" t="s">
+        <v>196</v>
       </c>
       <c r="H105" s="14" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="I105" s="4"/>
       <c r="J105" s="4"/>
     </row>
     <row r="106" spans="1:12">
-      <c r="A106" s="58"/>
-      <c r="B106" s="67"/>
+      <c r="A106" s="59"/>
+      <c r="B106" s="68"/>
       <c r="C106" s="38"/>
-      <c r="D106" s="66"/>
-      <c r="E106" s="67"/>
-      <c r="F106" s="77"/>
-      <c r="G106" s="77"/>
+      <c r="D106" s="67"/>
+      <c r="E106" s="68"/>
+      <c r="F106" s="71"/>
+      <c r="G106" s="71"/>
       <c r="H106" s="14" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I106" s="46"/>
       <c r="J106" s="4"/>
     </row>
     <row r="107" spans="1:12">
-      <c r="A107" s="58"/>
-      <c r="B107" s="67"/>
+      <c r="A107" s="59"/>
+      <c r="B107" s="68"/>
       <c r="C107" s="38"/>
-      <c r="D107" s="66"/>
-      <c r="E107" s="67"/>
-      <c r="F107" s="77"/>
-      <c r="G107" s="77"/>
+      <c r="D107" s="67"/>
+      <c r="E107" s="68"/>
+      <c r="F107" s="71"/>
+      <c r="G107" s="71"/>
       <c r="H107" s="10" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I107" s="20" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="J107" s="4"/>
     </row>
     <row r="108" spans="1:12" ht="87">
-      <c r="A108" s="58"/>
-      <c r="B108" s="67"/>
+      <c r="A108" s="59"/>
+      <c r="B108" s="68"/>
       <c r="C108" s="38"/>
-      <c r="D108" s="66"/>
-      <c r="E108" s="67"/>
-      <c r="F108" s="59" t="s">
-        <v>229</v>
+      <c r="D108" s="67"/>
+      <c r="E108" s="68"/>
+      <c r="F108" s="60" t="s">
+        <v>227</v>
       </c>
       <c r="G108" s="4" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="I108" s="5"/>
       <c r="J108" s="5"/>
       <c r="K108" s="4"/>
     </row>
     <row r="109" spans="1:12" ht="34.799999999999997">
-      <c r="A109" s="58"/>
-      <c r="B109" s="67"/>
+      <c r="A109" s="59"/>
+      <c r="B109" s="68"/>
       <c r="C109" s="38"/>
-      <c r="D109" s="66"/>
-      <c r="E109" s="67"/>
-      <c r="F109" s="60"/>
+      <c r="D109" s="67"/>
+      <c r="E109" s="68"/>
+      <c r="F109" s="61"/>
       <c r="G109" s="43" t="s">
+        <v>218</v>
+      </c>
+      <c r="H109" s="36" t="s">
+        <v>219</v>
+      </c>
+      <c r="I109" s="4" t="s">
         <v>220</v>
-      </c>
-      <c r="H109" s="36" t="s">
-        <v>221</v>
-      </c>
-      <c r="I109" s="4" t="s">
-        <v>222</v>
       </c>
       <c r="J109" s="5"/>
       <c r="K109" s="5"/>
       <c r="L109" s="4"/>
     </row>
     <row r="110" spans="1:12" ht="87">
-      <c r="A110" s="58"/>
-      <c r="B110" s="67"/>
+      <c r="A110" s="59"/>
+      <c r="B110" s="68"/>
       <c r="C110" s="38"/>
-      <c r="D110" s="66"/>
-      <c r="E110" s="67"/>
-      <c r="F110" s="60"/>
-      <c r="G110" s="59" t="s">
-        <v>223</v>
-      </c>
-      <c r="H110" s="62" t="s">
-        <v>234</v>
+      <c r="D110" s="67"/>
+      <c r="E110" s="68"/>
+      <c r="F110" s="61"/>
+      <c r="G110" s="60" t="s">
+        <v>221</v>
+      </c>
+      <c r="H110" s="63" t="s">
+        <v>231</v>
       </c>
       <c r="I110" s="49" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="J110" s="4" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="K110" s="5"/>
       <c r="L110" s="4"/>
     </row>
     <row r="111" spans="1:12">
-      <c r="A111" s="58"/>
-      <c r="B111" s="67"/>
+      <c r="A111" s="59"/>
+      <c r="B111" s="68"/>
       <c r="C111" s="38"/>
-      <c r="D111" s="66"/>
-      <c r="E111" s="67"/>
-      <c r="F111" s="60"/>
-      <c r="G111" s="60"/>
-      <c r="H111" s="63"/>
+      <c r="D111" s="67"/>
+      <c r="E111" s="68"/>
+      <c r="F111" s="61"/>
+      <c r="G111" s="61"/>
+      <c r="H111" s="64"/>
       <c r="I111" s="36" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="J111" s="4"/>
       <c r="K111" s="5"/>
       <c r="L111" s="4"/>
     </row>
     <row r="112" spans="1:12">
-      <c r="A112" s="58"/>
-      <c r="B112" s="67"/>
+      <c r="A112" s="59"/>
+      <c r="B112" s="68"/>
       <c r="C112" s="38"/>
-      <c r="D112" s="66"/>
-      <c r="E112" s="67"/>
-      <c r="F112" s="60"/>
-      <c r="G112" s="61"/>
-      <c r="H112" s="64"/>
+      <c r="D112" s="67"/>
+      <c r="E112" s="68"/>
+      <c r="F112" s="61"/>
+      <c r="G112" s="62"/>
+      <c r="H112" s="65"/>
       <c r="I112" s="36" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="J112" s="4"/>
       <c r="K112" s="5"/>
       <c r="L112" s="4"/>
     </row>
     <row r="113" spans="1:12" ht="69.599999999999994">
-      <c r="A113" s="58"/>
-      <c r="B113" s="67"/>
+      <c r="A113" s="59"/>
+      <c r="B113" s="68"/>
       <c r="C113" s="38"/>
-      <c r="D113" s="66"/>
-      <c r="E113" s="67"/>
-      <c r="F113" s="61"/>
+      <c r="D113" s="67"/>
+      <c r="E113" s="68"/>
+      <c r="F113" s="62"/>
       <c r="G113" s="42" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="H113" s="49" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="I113" s="4" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="J113" s="5"/>
       <c r="K113" s="5"/>
       <c r="L113" s="4"/>
     </row>
     <row r="114" spans="1:12">
-      <c r="A114" s="58"/>
-      <c r="B114" s="67"/>
-      <c r="C114" s="87" t="s">
+      <c r="A114" s="59"/>
+      <c r="B114" s="68"/>
+      <c r="C114" s="88" t="s">
+        <v>162</v>
+      </c>
+      <c r="D114" s="56" t="s">
+        <v>66</v>
+      </c>
+      <c r="E114" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="G114" s="69"/>
+      <c r="H114" s="55"/>
+      <c r="I114" s="55" t="s">
+        <v>178</v>
+      </c>
+      <c r="K114" s="5"/>
+    </row>
+    <row r="115" spans="1:12" ht="51.6" customHeight="1">
+      <c r="A115" s="59"/>
+      <c r="B115" s="68"/>
+      <c r="C115" s="88"/>
+      <c r="D115" s="68"/>
+      <c r="E115" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="F115" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="G115" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="D114" s="55" t="s">
-        <v>66</v>
-      </c>
-      <c r="E114" s="14" t="s">
-        <v>186</v>
-      </c>
-      <c r="G114" s="69"/>
-      <c r="H114" s="54"/>
-      <c r="I114" s="54" t="s">
-        <v>180</v>
-      </c>
-      <c r="K114" s="5"/>
-    </row>
-    <row r="115" spans="1:12" ht="51.6" customHeight="1">
-      <c r="A115" s="58"/>
-      <c r="B115" s="67"/>
-      <c r="C115" s="87"/>
-      <c r="D115" s="67"/>
-      <c r="E115" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="F115" s="15" t="s">
-        <v>162</v>
-      </c>
-      <c r="G115" s="19" t="s">
-        <v>166</v>
-      </c>
       <c r="H115" s="4"/>
-      <c r="I115" s="54"/>
+      <c r="I115" s="55"/>
       <c r="K115" s="5"/>
     </row>
     <row r="116" spans="1:12" ht="69.599999999999994">
-      <c r="A116" s="58"/>
-      <c r="B116" s="67"/>
-      <c r="C116" s="87"/>
-      <c r="D116" s="67"/>
+      <c r="A116" s="59"/>
+      <c r="B116" s="68"/>
+      <c r="C116" s="88"/>
+      <c r="D116" s="68"/>
       <c r="E116" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F116" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="I116" s="54"/>
+      <c r="I116" s="55"/>
       <c r="J116" s="5"/>
     </row>
     <row r="117" spans="1:12" ht="87">
-      <c r="A117" s="58"/>
-      <c r="B117" s="67"/>
-      <c r="C117" s="87"/>
-      <c r="D117" s="67"/>
+      <c r="A117" s="59"/>
+      <c r="B117" s="68"/>
+      <c r="C117" s="88"/>
+      <c r="D117" s="68"/>
       <c r="E117" s="42" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="F117" s="20" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="H117" s="4"/>
-      <c r="I117" s="54"/>
+      <c r="I117" s="55"/>
       <c r="K117" s="5"/>
     </row>
     <row r="118" spans="1:12" ht="34.799999999999997">
-      <c r="A118" s="58"/>
-      <c r="B118" s="56"/>
+      <c r="A118" s="59"/>
+      <c r="B118" s="57"/>
       <c r="C118" s="37" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D118" s="20" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E118" s="4"/>
       <c r="F118" s="4"/>
@@ -3964,9 +3960,9 @@
       <c r="K118" s="5"/>
     </row>
     <row r="119" spans="1:12">
-      <c r="A119" s="58"/>
+      <c r="A119" s="59"/>
       <c r="B119" s="40" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C119" s="4"/>
       <c r="D119" s="4"/>
@@ -3979,12 +3975,12 @@
       <c r="K119" s="5"/>
     </row>
     <row r="120" spans="1:12" ht="34.799999999999997" customHeight="1">
-      <c r="A120" s="58"/>
-      <c r="B120" s="55" t="s">
-        <v>161</v>
+      <c r="A120" s="59"/>
+      <c r="B120" s="56" t="s">
+        <v>159</v>
       </c>
       <c r="C120" s="35" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D120" s="4"/>
       <c r="E120" s="4"/>
@@ -3994,13 +3990,13 @@
       <c r="I120" s="5"/>
     </row>
     <row r="121" spans="1:12" ht="34.799999999999997">
-      <c r="A121" s="84"/>
-      <c r="B121" s="56"/>
+      <c r="A121" s="85"/>
+      <c r="B121" s="57"/>
       <c r="C121" s="10" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E121" s="4"/>
       <c r="F121" s="4"/>
@@ -4009,10 +4005,10 @@
       <c r="I121" s="5"/>
     </row>
     <row r="122" spans="1:12">
-      <c r="A122" s="84"/>
-      <c r="B122" s="56"/>
+      <c r="A122" s="85"/>
+      <c r="B122" s="57"/>
       <c r="C122" s="10" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D122" s="3"/>
       <c r="E122" s="4"/>
@@ -4023,10 +4019,10 @@
     </row>
     <row r="123" spans="1:12">
       <c r="A123" s="26" t="s">
+        <v>145</v>
+      </c>
+      <c r="B123" s="20" t="s">
         <v>147</v>
-      </c>
-      <c r="B123" s="20" t="s">
-        <v>149</v>
       </c>
       <c r="C123" s="4"/>
       <c r="D123" s="4"/>
@@ -4037,14 +4033,14 @@
       <c r="I123" s="5"/>
     </row>
     <row r="124" spans="1:12">
-      <c r="A124" s="57" t="s">
+      <c r="A124" s="58" t="s">
+        <v>146</v>
+      </c>
+      <c r="B124" s="58" t="s">
         <v>148</v>
       </c>
-      <c r="B124" s="57" t="s">
-        <v>150</v>
-      </c>
       <c r="C124" s="32" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D124" s="4"/>
       <c r="E124" s="4"/>
@@ -4054,10 +4050,10 @@
       <c r="I124" s="5"/>
     </row>
     <row r="125" spans="1:12">
-      <c r="A125" s="58"/>
-      <c r="B125" s="58"/>
+      <c r="A125" s="59"/>
+      <c r="B125" s="59"/>
       <c r="C125" s="33" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D125" s="4"/>
       <c r="E125" s="4"/>
@@ -4067,10 +4063,10 @@
       <c r="I125" s="5"/>
     </row>
     <row r="126" spans="1:12">
-      <c r="A126" s="58"/>
-      <c r="B126" s="58"/>
+      <c r="A126" s="59"/>
+      <c r="B126" s="59"/>
       <c r="C126" s="34" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D126" s="4"/>
       <c r="E126" s="4"/>
@@ -4080,10 +4076,10 @@
       <c r="I126" s="5"/>
     </row>
     <row r="127" spans="1:12">
-      <c r="A127" s="58"/>
-      <c r="B127" s="58"/>
+      <c r="A127" s="59"/>
+      <c r="B127" s="59"/>
       <c r="C127" s="34" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D127" s="4"/>
       <c r="E127" s="4"/>
@@ -4093,10 +4089,10 @@
       <c r="I127" s="5"/>
     </row>
     <row r="128" spans="1:12">
-      <c r="A128" s="58"/>
-      <c r="B128" s="58"/>
+      <c r="A128" s="59"/>
+      <c r="B128" s="59"/>
       <c r="C128" s="34" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D128" s="4"/>
       <c r="E128" s="5"/>
@@ -4105,15 +4101,15 @@
       <c r="H128" s="5"/>
       <c r="I128" s="5"/>
     </row>
-    <row r="129" spans="1:9">
-      <c r="A129" s="70" t="s">
-        <v>267</v>
+    <row r="129" spans="1:9" ht="17.399999999999999" customHeight="1">
+      <c r="A129" s="78" t="s">
+        <v>264</v>
       </c>
       <c r="B129" s="41" t="s">
-        <v>188</v>
-      </c>
-      <c r="C129" s="68" t="s">
-        <v>233</v>
+        <v>186</v>
+      </c>
+      <c r="C129" s="81" t="s">
+        <v>283</v>
       </c>
       <c r="D129" s="4"/>
       <c r="E129" s="5"/>
@@ -4123,9 +4119,9 @@
       <c r="I129" s="5"/>
     </row>
     <row r="130" spans="1:9">
-      <c r="A130" s="71"/>
+      <c r="A130" s="79"/>
       <c r="B130" s="50" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C130" s="69"/>
       <c r="D130" s="4"/>
@@ -4136,9 +4132,9 @@
       <c r="I130" s="5"/>
     </row>
     <row r="131" spans="1:9">
-      <c r="A131" s="71"/>
+      <c r="A131" s="79"/>
       <c r="B131" s="47" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C131" s="69"/>
       <c r="D131" s="4"/>
@@ -4149,9 +4145,9 @@
       <c r="I131" s="5"/>
     </row>
     <row r="132" spans="1:9">
-      <c r="A132" s="71"/>
+      <c r="A132" s="79"/>
       <c r="B132" s="47" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C132" s="69"/>
       <c r="D132" s="4"/>
@@ -4162,9 +4158,9 @@
       <c r="I132" s="5"/>
     </row>
     <row r="133" spans="1:9">
-      <c r="A133" s="71"/>
+      <c r="A133" s="79"/>
       <c r="B133" s="47" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C133" s="69"/>
       <c r="D133" s="4"/>
@@ -4175,9 +4171,9 @@
       <c r="I133" s="5"/>
     </row>
     <row r="134" spans="1:9">
-      <c r="A134" s="71"/>
+      <c r="A134" s="79"/>
       <c r="B134" s="47" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C134" s="69"/>
       <c r="D134" s="4"/>
@@ -4188,9 +4184,9 @@
       <c r="I134" s="5"/>
     </row>
     <row r="135" spans="1:9">
-      <c r="A135" s="72"/>
+      <c r="A135" s="79"/>
       <c r="B135" s="48" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C135" s="69"/>
       <c r="D135" s="4"/>
@@ -4201,70 +4197,64 @@
       <c r="I135" s="5"/>
     </row>
     <row r="136" spans="1:9">
-      <c r="A136" s="73" t="s">
-        <v>73</v>
-      </c>
-      <c r="B136" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="C136" s="69" t="s">
-        <v>99</v>
-      </c>
-      <c r="D136" s="54" t="s">
-        <v>98</v>
-      </c>
+      <c r="A136" s="79"/>
+      <c r="B136" s="48" t="s">
+        <v>284</v>
+      </c>
+      <c r="C136" s="69"/>
+      <c r="D136" s="4"/>
       <c r="E136" s="5"/>
       <c r="F136" s="5"/>
       <c r="G136" s="5"/>
       <c r="H136" s="5"/>
-    </row>
-    <row r="137" spans="1:9" ht="15" customHeight="1">
-      <c r="A137" s="74"/>
-      <c r="B137" s="22" t="s">
-        <v>62</v>
+      <c r="I136" s="5"/>
+    </row>
+    <row r="137" spans="1:9" ht="17.399999999999999" customHeight="1">
+      <c r="A137" s="79"/>
+      <c r="B137" s="14" t="s">
+        <v>181</v>
       </c>
       <c r="C137" s="69"/>
-      <c r="D137" s="54"/>
-      <c r="E137" s="5"/>
+      <c r="D137" s="4"/>
+      <c r="E137" s="12"/>
       <c r="F137" s="5"/>
       <c r="G137" s="5"/>
       <c r="H137" s="5"/>
-    </row>
-    <row r="138" spans="1:9" ht="15" customHeight="1">
-      <c r="A138" s="74"/>
-      <c r="B138" s="22" t="s">
-        <v>85</v>
+      <c r="I137" s="5"/>
+    </row>
+    <row r="138" spans="1:9">
+      <c r="A138" s="79"/>
+      <c r="B138" s="14" t="s">
+        <v>63</v>
       </c>
       <c r="C138" s="69"/>
-      <c r="D138" s="54"/>
-      <c r="E138" s="5"/>
+      <c r="D138" s="4"/>
+      <c r="E138" s="12"/>
       <c r="F138" s="5"/>
       <c r="G138" s="5"/>
       <c r="H138" s="5"/>
-    </row>
-    <row r="139" spans="1:9" ht="15" customHeight="1">
-      <c r="A139" s="74"/>
-      <c r="B139" s="22" t="s">
-        <v>96</v>
+      <c r="I138" s="5"/>
+    </row>
+    <row r="139" spans="1:9">
+      <c r="A139" s="79"/>
+      <c r="B139" s="14" t="s">
+        <v>83</v>
       </c>
       <c r="C139" s="69"/>
-      <c r="D139" s="54"/>
+      <c r="D139" s="4"/>
       <c r="E139" s="12"/>
       <c r="F139" s="5"/>
       <c r="G139" s="5"/>
       <c r="H139" s="5"/>
+      <c r="I139" s="5"/>
     </row>
     <row r="140" spans="1:9">
-      <c r="A140" s="75" t="s">
-        <v>72</v>
-      </c>
+      <c r="A140" s="80"/>
       <c r="B140" s="14" t="s">
-        <v>183</v>
-      </c>
-      <c r="C140" s="69" t="s">
-        <v>97</v>
-      </c>
-      <c r="D140" s="54"/>
+        <v>121</v>
+      </c>
+      <c r="C140" s="69"/>
+      <c r="D140" s="4"/>
       <c r="E140" s="12"/>
       <c r="F140" s="5"/>
       <c r="G140" s="5"/>
@@ -4272,112 +4262,127 @@
       <c r="I140" s="5"/>
     </row>
     <row r="141" spans="1:9">
-      <c r="A141" s="75"/>
-      <c r="B141" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="C141" s="69"/>
-      <c r="D141" s="54"/>
-      <c r="E141" s="12"/>
+      <c r="A141" s="75" t="s">
+        <v>72</v>
+      </c>
+      <c r="B141" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="C141" s="69" t="s">
+        <v>97</v>
+      </c>
+      <c r="D141" s="55" t="s">
+        <v>96</v>
+      </c>
+      <c r="E141" s="5"/>
       <c r="F141" s="5"/>
       <c r="G141" s="5"/>
       <c r="H141" s="5"/>
-      <c r="I141" s="5"/>
-    </row>
-    <row r="142" spans="1:9">
-      <c r="A142" s="75"/>
-      <c r="B142" s="14" t="s">
-        <v>84</v>
+    </row>
+    <row r="142" spans="1:9" ht="15" customHeight="1">
+      <c r="A142" s="76"/>
+      <c r="B142" s="22" t="s">
+        <v>62</v>
       </c>
       <c r="C142" s="69"/>
-      <c r="D142" s="54"/>
-      <c r="E142" s="12"/>
+      <c r="D142" s="55"/>
+      <c r="E142" s="5"/>
       <c r="F142" s="5"/>
       <c r="G142" s="5"/>
       <c r="H142" s="5"/>
-      <c r="I142" s="5"/>
-    </row>
-    <row r="143" spans="1:9">
-      <c r="A143" s="75"/>
-      <c r="B143" s="14" t="s">
-        <v>123</v>
+    </row>
+    <row r="143" spans="1:9" ht="15" customHeight="1">
+      <c r="A143" s="76"/>
+      <c r="B143" s="22" t="s">
+        <v>84</v>
       </c>
       <c r="C143" s="69"/>
-      <c r="D143" s="54"/>
-      <c r="E143" s="12"/>
+      <c r="D143" s="55"/>
+      <c r="E143" s="5"/>
       <c r="F143" s="5"/>
       <c r="G143" s="5"/>
       <c r="H143" s="5"/>
-      <c r="I143" s="5"/>
-    </row>
-    <row r="144" spans="1:9">
-      <c r="A144" s="1" t="s">
+    </row>
+    <row r="144" spans="1:9" ht="15" customHeight="1">
+      <c r="A144" s="77"/>
+      <c r="B144" s="22" t="s">
+        <v>95</v>
+      </c>
+      <c r="C144" s="69"/>
+      <c r="D144" s="55"/>
+      <c r="E144" s="12"/>
+      <c r="F144" s="5"/>
+      <c r="G144" s="5"/>
+      <c r="H144" s="5"/>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="145" spans="1:2">
-      <c r="A145" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="B145" s="5"/>
-    </row>
     <row r="146" spans="1:2">
-      <c r="A146" s="1" t="s">
-        <v>139</v>
-      </c>
+      <c r="A146" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="B146" s="5"/>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" s="1" t="s">
-        <v>240</v>
+        <v>139</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" s="1" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" s="1" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" s="1" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" s="1" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" s="1" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" s="1" t="s">
-        <v>257</v>
+        <v>243</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157" s="1" t="s">
+        <v>254</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="69">
+  <mergeCells count="67">
     <mergeCell ref="J84:J86"/>
     <mergeCell ref="I84:I86"/>
     <mergeCell ref="F105:F107"/>
@@ -4426,14 +4431,11 @@
     <mergeCell ref="G52:G53"/>
     <mergeCell ref="E54:E68"/>
     <mergeCell ref="G61:H61"/>
-    <mergeCell ref="C129:C135"/>
-    <mergeCell ref="F108:F113"/>
-    <mergeCell ref="A129:A135"/>
-    <mergeCell ref="A136:A139"/>
-    <mergeCell ref="C136:C139"/>
-    <mergeCell ref="D136:D143"/>
-    <mergeCell ref="A140:A143"/>
-    <mergeCell ref="C140:C143"/>
+    <mergeCell ref="A141:A144"/>
+    <mergeCell ref="C141:C144"/>
+    <mergeCell ref="D141:D144"/>
+    <mergeCell ref="A129:A140"/>
+    <mergeCell ref="C129:C140"/>
     <mergeCell ref="I114:I117"/>
     <mergeCell ref="B120:B122"/>
     <mergeCell ref="A124:A128"/>
@@ -4447,6 +4449,7 @@
     <mergeCell ref="H90:H92"/>
     <mergeCell ref="G82:G87"/>
     <mergeCell ref="H82:H87"/>
+    <mergeCell ref="F108:F113"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
